--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -2405,19 +2405,19 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
-        <v>6157000</v>
+        <v>6033800</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>23500</v>
+        <v>23030</v>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="B3" s="12" t="inlineStr">
         <is>
-          <t>6 套</t>
+          <t>5 套</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -15168,7 +15168,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>300 套</t>
+          <t>301 套</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -15550,12 +15550,12 @@
 (已售)</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="16" t="inlineStr">
         <is>
           <t>A7 | 262呎 (1房)
-$616万
-$23,500/呎
-(在售)</t>
+$603万
+$23,030/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="南首 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -938,7 +799,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -984,7 +845,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1122,7 +983,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1168,7 +1029,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1214,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1260,7 +1121,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1398,7 +1259,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-27</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1444,7 +1305,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1490,7 +1351,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1536,7 +1397,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1582,7 +1443,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1766,7 +1627,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1812,7 +1673,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-03</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1858,7 +1719,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1904,7 +1765,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -1950,7 +1811,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1996,7 +1857,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2088,7 +1949,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2134,7 +1995,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2180,7 +2041,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2272,7 +2133,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2318,7 +2179,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2456,7 +2317,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2502,7 +2363,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2548,7 +2409,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-11</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2594,7 +2455,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2640,7 +2501,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2686,7 +2547,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2732,7 +2593,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2778,7 +2639,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2824,7 +2685,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-16</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2870,7 +2731,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2916,7 +2777,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2962,7 +2823,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3008,7 +2869,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3100,7 +2961,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3146,7 +3007,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3192,7 +3053,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3238,7 +3099,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3284,7 +3145,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3330,7 +3191,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3376,7 +3237,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3422,7 +3283,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3468,7 +3329,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3514,7 +3375,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3560,7 +3421,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3606,7 +3467,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3652,7 +3513,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3698,7 +3559,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-19</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3790,7 +3651,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3836,7 +3697,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3882,7 +3743,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3928,7 +3789,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3974,7 +3835,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4020,7 +3881,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4066,7 +3927,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4112,7 +3973,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4158,7 +4019,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4204,7 +4065,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4250,7 +4111,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4296,7 +4157,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4342,7 +4203,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4388,7 +4249,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4480,7 +4341,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4526,7 +4387,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4572,7 +4433,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4618,7 +4479,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -4664,7 +4525,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -4710,7 +4571,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -4756,7 +4617,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -4802,7 +4663,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -4848,7 +4709,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -4894,7 +4755,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -4940,7 +4801,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -4986,7 +4847,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -5032,7 +4893,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -5078,7 +4939,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -5170,7 +5031,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -5216,7 +5077,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -5262,7 +5123,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -5308,7 +5169,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -5354,7 +5215,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -5400,7 +5261,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -5446,7 +5307,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -5492,7 +5353,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -5538,7 +5399,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -5584,7 +5445,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -5630,7 +5491,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -5676,7 +5537,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -5722,7 +5583,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -5768,7 +5629,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -5860,7 +5721,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -5906,7 +5767,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-09</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -5952,7 +5813,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -5998,7 +5859,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -6044,7 +5905,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -6090,7 +5951,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -6136,7 +5997,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -6182,7 +6043,7 @@
       </c>
       <c r="G122" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H122" s="5" t="n">
@@ -6228,7 +6089,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -6274,7 +6135,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -6320,7 +6181,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -6412,7 +6273,7 @@
       </c>
       <c r="G127" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H127" s="5" t="n">
@@ -6458,7 +6319,7 @@
       </c>
       <c r="G128" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H128" s="5" t="n">
@@ -6504,7 +6365,7 @@
       </c>
       <c r="G129" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H129" s="5" t="n">
@@ -6550,7 +6411,7 @@
       </c>
       <c r="G130" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H130" s="5" t="n">
@@ -6596,7 +6457,7 @@
       </c>
       <c r="G131" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H131" s="5" t="n">
@@ -6642,7 +6503,7 @@
       </c>
       <c r="G132" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H132" s="5" t="n">
@@ -6688,7 +6549,7 @@
       </c>
       <c r="G133" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H133" s="5" t="n">
@@ -6734,7 +6595,7 @@
       </c>
       <c r="G134" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H134" s="5" t="n">
@@ -6780,7 +6641,7 @@
       </c>
       <c r="G135" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H135" s="5" t="n">
@@ -6826,7 +6687,7 @@
       </c>
       <c r="G136" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H136" s="5" t="n">
@@ -6872,7 +6733,7 @@
       </c>
       <c r="G137" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H137" s="5" t="n">
@@ -6918,7 +6779,7 @@
       </c>
       <c r="G138" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-14</t>
         </is>
       </c>
       <c r="H138" s="5" t="n">
@@ -6964,7 +6825,7 @@
       </c>
       <c r="G139" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H139" s="5" t="n">
@@ -7010,7 +6871,7 @@
       </c>
       <c r="G140" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H140" s="5" t="n">
@@ -7056,7 +6917,7 @@
       </c>
       <c r="G141" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H141" s="5" t="n">
@@ -7102,7 +6963,7 @@
       </c>
       <c r="G142" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H142" s="5" t="n">
@@ -7148,7 +7009,7 @@
       </c>
       <c r="G143" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H143" s="5" t="n">
@@ -7194,7 +7055,7 @@
       </c>
       <c r="G144" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H144" s="5" t="n">
@@ -7240,7 +7101,7 @@
       </c>
       <c r="G145" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H145" s="5" t="n">
@@ -7286,7 +7147,7 @@
       </c>
       <c r="G146" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H146" s="5" t="n">
@@ -7332,7 +7193,7 @@
       </c>
       <c r="G147" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H147" s="5" t="n">
@@ -7424,7 +7285,7 @@
       </c>
       <c r="G149" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H149" s="5" t="n">
@@ -7470,7 +7331,7 @@
       </c>
       <c r="G150" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H150" s="5" t="n">
@@ -7516,7 +7377,7 @@
       </c>
       <c r="G151" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H151" s="5" t="n">
@@ -7562,7 +7423,7 @@
       </c>
       <c r="G152" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H152" s="5" t="n">
@@ -7608,7 +7469,7 @@
       </c>
       <c r="G153" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="H153" s="5" t="n">
@@ -7654,7 +7515,7 @@
       </c>
       <c r="G154" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H154" s="5" t="n">
@@ -7700,7 +7561,7 @@
       </c>
       <c r="G155" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H155" s="5" t="n">
@@ -7746,7 +7607,7 @@
       </c>
       <c r="G156" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H156" s="5" t="n">
@@ -7792,7 +7653,7 @@
       </c>
       <c r="G157" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H157" s="5" t="n">
@@ -7838,7 +7699,7 @@
       </c>
       <c r="G158" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H158" s="5" t="n">
@@ -7884,7 +7745,7 @@
       </c>
       <c r="G159" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H159" s="5" t="n">
@@ -7930,7 +7791,7 @@
       </c>
       <c r="G160" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H160" s="5" t="n">
@@ -7976,7 +7837,7 @@
       </c>
       <c r="G161" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-06</t>
         </is>
       </c>
       <c r="H161" s="5" t="n">
@@ -8022,7 +7883,7 @@
       </c>
       <c r="G162" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H162" s="5" t="n">
@@ -8068,7 +7929,7 @@
       </c>
       <c r="G163" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H163" s="5" t="n">
@@ -8114,7 +7975,7 @@
       </c>
       <c r="G164" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H164" s="5" t="n">
@@ -8160,7 +8021,7 @@
       </c>
       <c r="G165" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H165" s="5" t="n">
@@ -8206,7 +8067,7 @@
       </c>
       <c r="G166" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H166" s="5" t="n">
@@ -8252,7 +8113,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -8298,7 +8159,7 @@
       </c>
       <c r="G168" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H168" s="5" t="n">
@@ -8344,7 +8205,7 @@
       </c>
       <c r="G169" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H169" s="5" t="n">
@@ -8390,7 +8251,7 @@
       </c>
       <c r="G170" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H170" s="5" t="n">
@@ -8436,7 +8297,7 @@
       </c>
       <c r="G171" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H171" s="5" t="n">
@@ -8482,7 +8343,7 @@
       </c>
       <c r="G172" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H172" s="5" t="n">
@@ -8528,7 +8389,7 @@
       </c>
       <c r="G173" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H173" s="5" t="n">
@@ -8620,7 +8481,7 @@
       </c>
       <c r="G175" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="H175" s="5" t="n">
@@ -8666,7 +8527,7 @@
       </c>
       <c r="G176" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="H176" s="5" t="n">
@@ -8712,7 +8573,7 @@
       </c>
       <c r="G177" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H177" s="5" t="n">
@@ -8758,7 +8619,7 @@
       </c>
       <c r="G178" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H178" s="5" t="n">
@@ -8850,7 +8711,7 @@
       </c>
       <c r="G180" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H180" s="5" t="n">
@@ -8896,7 +8757,7 @@
       </c>
       <c r="G181" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H181" s="5" t="n">
@@ -8942,7 +8803,7 @@
       </c>
       <c r="G182" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H182" s="5" t="n">
@@ -8988,7 +8849,7 @@
       </c>
       <c r="G183" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H183" s="5" t="n">
@@ -9034,7 +8895,7 @@
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H184" s="5" t="n">
@@ -9080,7 +8941,7 @@
       </c>
       <c r="G185" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H185" s="5" t="n">
@@ -9126,7 +8987,7 @@
       </c>
       <c r="G186" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H186" s="5" t="n">
@@ -9172,7 +9033,7 @@
       </c>
       <c r="G187" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H187" s="5" t="n">
@@ -9218,7 +9079,7 @@
       </c>
       <c r="G188" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H188" s="5" t="n">
@@ -9264,7 +9125,7 @@
       </c>
       <c r="G189" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H189" s="5" t="n">
@@ -9310,7 +9171,7 @@
       </c>
       <c r="G190" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H190" s="5" t="n">
@@ -9356,7 +9217,7 @@
       </c>
       <c r="G191" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H191" s="5" t="n">
@@ -9402,7 +9263,7 @@
       </c>
       <c r="G192" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H192" s="5" t="n">
@@ -9448,7 +9309,7 @@
       </c>
       <c r="G193" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H193" s="5" t="n">
@@ -9494,7 +9355,7 @@
       </c>
       <c r="G194" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H194" s="5" t="n">
@@ -9540,7 +9401,7 @@
       </c>
       <c r="G195" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H195" s="5" t="n">
@@ -9586,7 +9447,7 @@
       </c>
       <c r="G196" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H196" s="5" t="n">
@@ -9632,7 +9493,7 @@
       </c>
       <c r="G197" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H197" s="5" t="n">
@@ -9678,7 +9539,7 @@
       </c>
       <c r="G198" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H198" s="5" t="n">
@@ -9724,7 +9585,7 @@
       </c>
       <c r="G199" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H199" s="5" t="n">
@@ -9770,7 +9631,7 @@
       </c>
       <c r="G200" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H200" s="5" t="n">
@@ -9816,7 +9677,7 @@
       </c>
       <c r="G201" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H201" s="5" t="n">
@@ -9862,7 +9723,7 @@
       </c>
       <c r="G202" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H202" s="5" t="n">
@@ -9908,7 +9769,7 @@
       </c>
       <c r="G203" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H203" s="5" t="n">
@@ -9954,7 +9815,7 @@
       </c>
       <c r="G204" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H204" s="5" t="n">
@@ -10000,7 +9861,7 @@
       </c>
       <c r="G205" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H205" s="5" t="n">
@@ -10092,7 +9953,7 @@
       </c>
       <c r="G207" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H207" s="5" t="n">
@@ -10138,7 +9999,7 @@
       </c>
       <c r="G208" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H208" s="5" t="n">
@@ -10184,7 +10045,7 @@
       </c>
       <c r="G209" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H209" s="5" t="n">
@@ -10230,7 +10091,7 @@
       </c>
       <c r="G210" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H210" s="5" t="n">
@@ -10276,7 +10137,7 @@
       </c>
       <c r="G211" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H211" s="5" t="n">
@@ -10322,7 +10183,7 @@
       </c>
       <c r="G212" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H212" s="5" t="n">
@@ -10368,7 +10229,7 @@
       </c>
       <c r="G213" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H213" s="5" t="n">
@@ -10414,7 +10275,7 @@
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H214" s="5" t="n">
@@ -10460,7 +10321,7 @@
       </c>
       <c r="G215" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H215" s="5" t="n">
@@ -10506,7 +10367,7 @@
       </c>
       <c r="G216" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H216" s="5" t="n">
@@ -10552,7 +10413,7 @@
       </c>
       <c r="G217" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H217" s="5" t="n">
@@ -10598,7 +10459,7 @@
       </c>
       <c r="G218" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H218" s="5" t="n">
@@ -10644,7 +10505,7 @@
       </c>
       <c r="G219" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H219" s="5" t="n">
@@ -10690,7 +10551,7 @@
       </c>
       <c r="G220" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H220" s="5" t="n">
@@ -10736,7 +10597,7 @@
       </c>
       <c r="G221" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H221" s="5" t="n">
@@ -10782,7 +10643,7 @@
       </c>
       <c r="G222" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H222" s="5" t="n">
@@ -10828,7 +10689,7 @@
       </c>
       <c r="G223" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H223" s="5" t="n">
@@ -10874,7 +10735,7 @@
       </c>
       <c r="G224" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H224" s="5" t="n">
@@ -10920,7 +10781,7 @@
       </c>
       <c r="G225" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H225" s="5" t="n">
@@ -10966,7 +10827,7 @@
       </c>
       <c r="G226" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H226" s="5" t="n">
@@ -11012,7 +10873,7 @@
       </c>
       <c r="G227" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H227" s="5" t="n">
@@ -11058,7 +10919,7 @@
       </c>
       <c r="G228" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H228" s="5" t="n">
@@ -11104,7 +10965,7 @@
       </c>
       <c r="G229" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H229" s="5" t="n">
@@ -11150,7 +11011,7 @@
       </c>
       <c r="G230" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H230" s="5" t="n">
@@ -11196,7 +11057,7 @@
       </c>
       <c r="G231" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H231" s="5" t="n">
@@ -11242,7 +11103,7 @@
       </c>
       <c r="G232" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H232" s="5" t="n">
@@ -11288,7 +11149,7 @@
       </c>
       <c r="G233" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H233" s="5" t="n">
@@ -11334,7 +11195,7 @@
       </c>
       <c r="G234" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H234" s="5" t="n">
@@ -11380,7 +11241,7 @@
       </c>
       <c r="G235" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H235" s="5" t="n">
@@ -11426,7 +11287,7 @@
       </c>
       <c r="G236" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H236" s="5" t="n">
@@ -11472,7 +11333,7 @@
       </c>
       <c r="G237" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H237" s="5" t="n">
@@ -11564,7 +11425,7 @@
       </c>
       <c r="G239" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H239" s="5" t="n">
@@ -11656,7 +11517,7 @@
       </c>
       <c r="G241" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H241" s="5" t="n">
@@ -11702,7 +11563,7 @@
       </c>
       <c r="G242" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H242" s="5" t="n">
@@ -11748,7 +11609,7 @@
       </c>
       <c r="G243" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H243" s="5" t="n">
@@ -11794,7 +11655,7 @@
       </c>
       <c r="G244" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H244" s="5" t="n">
@@ -11840,7 +11701,7 @@
       </c>
       <c r="G245" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H245" s="5" t="n">
@@ -11886,7 +11747,7 @@
       </c>
       <c r="G246" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H246" s="5" t="n">
@@ -11932,7 +11793,7 @@
       </c>
       <c r="G247" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H247" s="5" t="n">
@@ -11978,7 +11839,7 @@
       </c>
       <c r="G248" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H248" s="5" t="n">
@@ -12024,7 +11885,7 @@
       </c>
       <c r="G249" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H249" s="5" t="n">
@@ -12070,7 +11931,7 @@
       </c>
       <c r="G250" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H250" s="5" t="n">
@@ -12116,7 +11977,7 @@
       </c>
       <c r="G251" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H251" s="5" t="n">
@@ -12162,7 +12023,7 @@
       </c>
       <c r="G252" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H252" s="5" t="n">
@@ -12208,7 +12069,7 @@
       </c>
       <c r="G253" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H253" s="5" t="n">
@@ -12254,7 +12115,7 @@
       </c>
       <c r="G254" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H254" s="5" t="n">
@@ -12300,7 +12161,7 @@
       </c>
       <c r="G255" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H255" s="5" t="n">
@@ -12346,7 +12207,7 @@
       </c>
       <c r="G256" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H256" s="5" t="n">
@@ -12392,7 +12253,7 @@
       </c>
       <c r="G257" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H257" s="5" t="n">
@@ -12438,7 +12299,7 @@
       </c>
       <c r="G258" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H258" s="5" t="n">
@@ -12530,7 +12391,7 @@
       </c>
       <c r="G260" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H260" s="5" t="n">
@@ -12576,7 +12437,7 @@
       </c>
       <c r="G261" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H261" s="5" t="n">
@@ -12668,7 +12529,7 @@
       </c>
       <c r="G263" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H263" s="5" t="n">
@@ -12714,7 +12575,7 @@
       </c>
       <c r="G264" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H264" s="5" t="n">
@@ -12760,7 +12621,7 @@
       </c>
       <c r="G265" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H265" s="5" t="n">
@@ -12806,7 +12667,7 @@
       </c>
       <c r="G266" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H266" s="5" t="n">
@@ -12852,7 +12713,7 @@
       </c>
       <c r="G267" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H267" s="5" t="n">
@@ -12898,7 +12759,7 @@
       </c>
       <c r="G268" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H268" s="5" t="n">
@@ -12944,7 +12805,7 @@
       </c>
       <c r="G269" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H269" s="5" t="n">
@@ -12990,7 +12851,7 @@
       </c>
       <c r="G270" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H270" s="5" t="n">
@@ -13036,7 +12897,7 @@
       </c>
       <c r="G271" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H271" s="5" t="n">
@@ -13082,7 +12943,7 @@
       </c>
       <c r="G272" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H272" s="5" t="n">
@@ -13128,7 +12989,7 @@
       </c>
       <c r="G273" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H273" s="5" t="n">
@@ -13174,7 +13035,7 @@
       </c>
       <c r="G274" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H274" s="5" t="n">
@@ -13220,7 +13081,7 @@
       </c>
       <c r="G275" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H275" s="5" t="n">
@@ -13266,7 +13127,7 @@
       </c>
       <c r="G276" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H276" s="5" t="n">
@@ -13358,7 +13219,7 @@
       </c>
       <c r="G278" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H278" s="5" t="n">
@@ -13404,7 +13265,7 @@
       </c>
       <c r="G279" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H279" s="5" t="n">
@@ -13450,7 +13311,7 @@
       </c>
       <c r="G280" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H280" s="5" t="n">
@@ -13496,7 +13357,7 @@
       </c>
       <c r="G281" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="H281" s="5" t="n">
@@ -13542,7 +13403,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -13588,7 +13449,7 @@
       </c>
       <c r="G283" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H283" s="5" t="n">
@@ -13634,7 +13495,7 @@
       </c>
       <c r="G284" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-18</t>
         </is>
       </c>
       <c r="H284" s="5" t="n">
@@ -13680,7 +13541,7 @@
       </c>
       <c r="G285" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H285" s="5" t="n">
@@ -13726,7 +13587,7 @@
       </c>
       <c r="G286" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H286" s="5" t="n">
@@ -13772,7 +13633,7 @@
       </c>
       <c r="G287" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="H287" s="5" t="n">
@@ -13818,7 +13679,7 @@
       </c>
       <c r="G288" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H288" s="5" t="n">
@@ -13864,7 +13725,7 @@
       </c>
       <c r="G289" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H289" s="5" t="n">
@@ -13910,7 +13771,7 @@
       </c>
       <c r="G290" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-16</t>
         </is>
       </c>
       <c r="H290" s="5" t="n">
@@ -13956,7 +13817,7 @@
       </c>
       <c r="G291" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-17</t>
         </is>
       </c>
       <c r="H291" s="5" t="n">
@@ -14002,7 +13863,7 @@
       </c>
       <c r="G292" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H292" s="5" t="n">
@@ -14048,7 +13909,7 @@
       </c>
       <c r="G293" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H293" s="5" t="n">
@@ -14094,7 +13955,7 @@
       </c>
       <c r="G294" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H294" s="5" t="n">
@@ -14140,7 +14001,7 @@
       </c>
       <c r="G295" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="H295" s="5" t="n">
@@ -14186,7 +14047,7 @@
       </c>
       <c r="G296" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="H296" s="5" t="n">
@@ -14232,7 +14093,7 @@
       </c>
       <c r="G297" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-19</t>
         </is>
       </c>
       <c r="H297" s="5" t="n">
@@ -14278,7 +14139,7 @@
       </c>
       <c r="G298" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H298" s="5" t="n">
@@ -14324,7 +14185,7 @@
       </c>
       <c r="G299" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="H299" s="5" t="n">
@@ -14370,7 +14231,7 @@
       </c>
       <c r="G300" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="H300" s="5" t="n">
@@ -14416,7 +14277,7 @@
       </c>
       <c r="G301" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H301" s="5" t="n">
@@ -14462,7 +14323,7 @@
       </c>
       <c r="G302" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="H302" s="5" t="n">
@@ -14508,7 +14369,7 @@
       </c>
       <c r="G303" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H303" s="5" t="n">
@@ -14554,7 +14415,7 @@
       </c>
       <c r="G304" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-22</t>
         </is>
       </c>
       <c r="H304" s="5" t="n">
@@ -14600,7 +14461,7 @@
       </c>
       <c r="G305" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H305" s="5" t="n">
@@ -14646,7 +14507,7 @@
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
@@ -14692,7 +14553,7 @@
       </c>
       <c r="G307" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-02</t>
         </is>
       </c>
       <c r="H307" s="5" t="n">
@@ -14738,7 +14599,7 @@
       </c>
       <c r="G308" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H308" s="5" t="n">
@@ -14784,7 +14645,7 @@
       </c>
       <c r="G309" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H309" s="5" t="n">
@@ -14830,7 +14691,7 @@
       </c>
       <c r="G310" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H310" s="5" t="n">
@@ -14876,7 +14737,7 @@
       </c>
       <c r="G311" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H311" s="5" t="n">
@@ -14922,7 +14783,7 @@
       </c>
       <c r="G312" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H312" s="5" t="n">
@@ -14968,7 +14829,7 @@
       </c>
       <c r="G313" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="H313" s="5" t="n">
@@ -15014,7 +14875,7 @@
       </c>
       <c r="G314" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H314" s="5" t="n">
@@ -15060,7 +14921,7 @@
       </c>
       <c r="G315" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="H315" s="5" t="n">
@@ -15082,2846 +14943,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:P26"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>南首 - 南首 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>313 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>5 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>301 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>3 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>A8</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>B3</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>B5</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>B6</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>B7</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>B8</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>B9</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 353呎 (2房)
-$1,120万
-$31,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$868万
-$25,374/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$653万
-$24,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$638万
-$24,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$464万
-$23,182/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="G6" s="17" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$630万
-$24,046/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H6" s="18" t="inlineStr"/>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 358呎 (2房)
-$1,039万
-$29,017/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$882万
-$25,781/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K6" s="19" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$681万
-$25,901/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="L6" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$668万
-$25,383/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="M6" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$655万
-$25,404/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="N6" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$457万
-$22,838/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="O6" s="20" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$652万
-$24,878/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="P6" s="18" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$886万
-$25,399/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$798万
-$23,320/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$646万
-$24,556/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$631万
-$24,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$400万
-$19,987/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G7" s="19" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$623万
-$23,786/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H7" s="20" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$688万
-$26,248/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$924万
-$26,322/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="J7" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$803万
-$23,471/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K7" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$654万
-$24,884/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L7" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$654万
-$24,884/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M7" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$648万
-$25,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$400万
-$19,982/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O7" s="17" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$645万
-$24,615/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="P7" s="17" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$676万
-$25,885/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$870万
-$24,924/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$776万
-$22,677/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$584万
-$22,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$571万
-$22,130/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$399万
-$19,950/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$603万
-$23,030/呎
-(26年-07月)</t>
-        </is>
-      </c>
-      <c r="H8" s="20" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$680万
-$25,943/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$888万
-$25,301/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$781万
-$22,836/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K8" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$650万
-$24,697/呎
-(26年-04月)</t>
-        </is>
-      </c>
-      <c r="L8" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$650万
-$24,697/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M8" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$638万
-$24,735/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N8" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$399万
-$19,964/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O8" s="19" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$634万
-$24,206/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="P8" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$590万
-$22,612/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$787万
-$22,549/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$756万
-$22,096/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D9" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$570万
-$21,667/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$558万
-$21,631/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$406万
-$20,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$542万
-$20,686/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H9" s="20" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$673万
-$25,691/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$810万
-$23,084/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$761万
-$22,257/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K9" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$637万
-$24,232/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$637万
-$24,232/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$558万
-$21,631/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$399万
-$19,936/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$568万
-$21,673/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P9" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$576万
-$22,087/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$768万
-$22,009/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$703万
-$20,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$556万
-$21,142/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$545万
-$21,135/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$395万
-$19,734/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G10" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$530万
-$20,244/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H10" s="19" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$663万
-$25,313/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$791万
-$22,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J10" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$715万
-$20,902/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K10" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$630万
-$23,967/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$630万
-$23,967/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$545万
-$21,135/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$397万
-$19,867/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$572万
-$21,839/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P10" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$563万
-$21,562/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$723万
-$20,707/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$702万
-$20,520/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$542万
-$20,617/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$544万
-$21,081/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$402万
-$20,088/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G11" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$510万
-$19,469/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$640万
-$24,425/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$773万
-$22,025/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$700万
-$20,458/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K11" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$556万
-$21,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$556万
-$21,129/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$532万
-$20,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$396万
-$19,816/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$552万
-$21,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P11" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$561万
-$21,494/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$709万
-$20,306/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$674万
-$19,710/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$537万
-$20,402/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$521万
-$20,206/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$392万
-$19,614/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G12" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$497万
-$18,958/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$568万
-$21,677/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$729万
-$20,759/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$686万
-$20,068/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K12" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$527万
-$20,054/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$539万
-$20,490/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$511万
-$19,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$395万
-$19,743/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$528万
-$20,159/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P12" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$529万
-$20,264/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$697万
-$19,960/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$663万
-$19,376/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$509万
-$19,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$512万
-$19,838/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$400万
-$19,989/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G13" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$504万
-$19,253/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$541万
-$20,637/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$716万
-$20,400/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J13" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$675万
-$19,734/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K13" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$528万
-$20,083/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$528万
-$20,083/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$501万
-$19,416/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$390万
-$19,513/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$507万
-$19,362/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P13" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$518万
-$19,863/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$700万
-$20,044/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$651万
-$19,027/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$500万
-$18,998/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$493万
-$19,091/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$390万
-$19,504/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G14" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$499万
-$19,032/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$553万
-$21,114/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$703万
-$20,041/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J14" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$678万
-$19,822/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K14" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$524万
-$19,943/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$519万
-$19,733/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$503万
-$19,507/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$389万
-$19,467/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$498万
-$19,018/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P14" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$509万
-$19,517/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$675万
-$19,330/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$656万
-$19,171/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$509万
-$19,343/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$486万
-$18,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$385万
-$19,274/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G15" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$493万
-$18,814/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$524万
-$19,991/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$693万
-$19,742/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J15" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$661万
-$19,331/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K15" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$500万
-$19,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$500万
-$19,030/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$486万
-$18,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$385万
-$19,237/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$491万
-$18,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P15" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$513万
-$19,650/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$681万
-$19,516/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$655万
-$19,147/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$503万
-$19,108/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$490万
-$19,007/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$393万
-$19,646/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G16" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$473万
-$18,052/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$518万
-$19,758/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I16" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$685万
-$19,503/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J16" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$646万
-$18,903/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K16" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$494万
-$18,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$494万
-$18,798/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$490万
-$19,007/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N16" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$380万
-$19,007/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O16" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$485万
-$18,502/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P16" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$496万
-$19,003/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$661万
-$18,930/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$628万
-$18,376/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="D17" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$493万
-$18,732/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$476万
-$18,439/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$381万
-$19,053/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G17" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$469万
-$17,891/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$502万
-$19,165/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$678万
-$19,323/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J17" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$648万
-$18,940/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K17" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$501万
-$19,032/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L17" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$490万
-$18,627/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M17" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$476万
-$18,439/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N17" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$381万
-$19,058/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O17" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$491万
-$18,728/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P17" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$491万
-$18,830/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$651万
-$18,642/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$619万
-$18,099/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$475万
-$18,046/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$479万
-$18,563/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$376万
-$18,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$463万
-$17,676/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$495万
-$18,881/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$670万
-$19,084/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J18" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$647万
-$18,915/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K18" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$482万
-$18,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L18" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$482万
-$18,344/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M18" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$469万
-$18,168/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N18" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$369万
-$18,428/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O18" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$485万
-$18,495/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P18" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$485万
-$18,601/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$641万
-$18,358/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$609万
-$17,819/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$466万
-$17,704/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$460万
-$17,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$380万
-$18,997/呎
-(25年-03月)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$458万
-$17,462/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$486万
-$18,537/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$661万
-$18,846/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J19" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$639万
-$18,687/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K19" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$473万
-$18,001/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L19" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$473万
-$18,001/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M19" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$460万
-$17,843/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$366万
-$18,280/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O19" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$468万
-$17,873/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P19" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$488万
-$18,710/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$629万
-$18,012/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$598万
-$17,485/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$457万
-$17,364/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$452万
-$17,516/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$364万
-$18,188/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$452万
-$17,248/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$482万
-$18,390/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$651万
-$18,544/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J20" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$616万
-$18,013/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K20" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$464万
-$17,658/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L20" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$464万
-$17,658/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M20" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$452万
-$17,516/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N20" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$371万
-$18,536/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O20" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$462万
-$17,641/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P20" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$481万
-$18,418/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$637万
-$18,246/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$606万
-$17,714/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$453万
-$17,206/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$444万
-$17,191/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$363万
-$18,133/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$451万
-$17,223/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$468万
-$17,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$652万
-$18,583/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J21" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$605万
-$17,679/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K21" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$455万
-$17,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L21" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$455万
-$17,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M21" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$444万
-$17,191/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N21" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$362万
-$18,082/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O21" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$456万
-$17,413/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P21" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$461万
-$17,681/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$605万
-$17,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$575万
-$16,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$450万
-$17,098/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$437万
-$16,920/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$358万
-$17,898/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$441万
-$16,823/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$459万
-$17,505/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$646万
-$18,410/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J22" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$593万
-$17,345/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K22" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$446万
-$16,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L22" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$446万
-$16,976/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M22" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$445万
-$17,233/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N22" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$357万
-$17,848/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O22" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$450万
-$17,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P22" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$452万
-$17,335/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$595万
-$17,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$566万
-$16,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$433万
-$16,451/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$430万
-$16,649/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$353万
-$17,668/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$443万
-$16,916/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$461万
-$17,594/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$615万
-$17,527/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J23" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$584万
-$17,068/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="K23" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$448万
-$17,052/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L23" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$439万
-$16,689/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M23" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$433万
-$16,776/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="N23" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$433万
-$21,641/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O23" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$454万
-$17,325/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P23" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$445万
-$17,046/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$597万
-$17,117/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$554万
-$16,208/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$432万
-$16,430/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$421万
-$16,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$348万
-$17,383/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G24" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$435万
-$16,586/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$444万
-$16,932/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$605万
-$17,228/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J24" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$574万
-$16,791/呎
-(25年-02月)</t>
-        </is>
-      </c>
-      <c r="K24" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$441万
-$16,763/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L24" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$431万
-$16,406/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M24" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$421万
-$16,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$346万
-$17,324/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O24" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$437万
-$16,669/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P24" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$437万
-$16,761/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 349呎 (2房)
-$577万
-$16,523/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 342呎 (2房)
-$541万
-$15,820/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 263呎 (1房)
-$410万
-$15,591/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 258呎 (1房)
-$410万
-$15,890/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 200呎 (开放式)
-$346万
-$17,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G25" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 262呎 (1房)
-$417万
-$15,914/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 262呎 (1房)
-$438万
-$16,704/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 351呎 (2房)
-$601万
-$17,113/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J25" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 342呎 (2房)
-$565万
-$16,514/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K25" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 263呎 (1房)
-$425万
-$16,175/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L25" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 263呎 (1房)
-$425万
-$16,175/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M25" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 258呎 (1房)
-$429万
-$16,632/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 200呎 (开放式)
-$337万
-$16,872/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O25" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 262呎 (1房)
-$446万
-$17,041/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P25" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 261呎 (1房)
-$431万
-$16,532/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A1 | 311呎 (2房)
-$723万
-$23,241/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>A2 | 304呎 (2房)
-$656万
-$21,579/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>A3 | 225呎 (1房)
-$470万
-$20,881/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="inlineStr">
-        <is>
-          <t>A5 | 221呎 (1房)
-$465万
-$21,040/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="16" t="inlineStr">
-        <is>
-          <t>A6 | 178呎 (开放式)
-$452万
-$25,393/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="G26" s="16" t="inlineStr">
-        <is>
-          <t>A7 | 224呎 (1房)
-$585万
-$26,116/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
-        <is>
-          <t>A8 | 224呎 (1房)
-$633万
-$28,259/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="I26" s="16" t="inlineStr">
-        <is>
-          <t>B1 | 313呎 (2房)
-$725万
-$23,163/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="J26" s="16" t="inlineStr">
-        <is>
-          <t>B2 | 304呎 (2房)
-$660万
-$21,711/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="K26" s="16" t="inlineStr">
-        <is>
-          <t>B3 | 225呎 (1房)
-$475万
-$21,111/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="L26" s="16" t="inlineStr">
-        <is>
-          <t>B5 | 225呎 (1房)
-$470万
-$20,889/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="M26" s="16" t="inlineStr">
-        <is>
-          <t>B6 | 220呎 (1房)
-$465万
-$21,136/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="N26" s="16" t="inlineStr">
-        <is>
-          <t>B7 | 178呎 (开放式)
-$458万
-$25,730/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="O26" s="16" t="inlineStr">
-        <is>
-          <t>B8 | 224呎 (1房)
-$520万
-$23,214/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="P26" s="16" t="inlineStr">
-        <is>
-          <t>B9 | 224呎 (1房)
-$618万
-$27,593/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="南首" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,102 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +148,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +229,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -14943,4 +15131,2846 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:P25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>南首 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="J4" s="19" t="inlineStr">
+        <is>
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="K4" s="19" t="inlineStr">
+        <is>
+          <t>B3</t>
+        </is>
+      </c>
+      <c r="L4" s="19" t="inlineStr">
+        <is>
+          <t>B5</t>
+        </is>
+      </c>
+      <c r="M4" s="19" t="inlineStr">
+        <is>
+          <t>B6</t>
+        </is>
+      </c>
+      <c r="N4" s="19" t="inlineStr">
+        <is>
+          <t>B7</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>B8</t>
+        </is>
+      </c>
+      <c r="P4" s="19" t="inlineStr">
+        <is>
+          <t>B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 353呎 (2房)
+$1120万
+$31,728/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$868万
+$25,374/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$653万
+$24,820/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$638万
+$24,728/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$464万
+$23,182/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="G5" s="21" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$630万
+$24,046/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H5" s="22" t="inlineStr"/>
+      <c r="I5" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 358呎 (2房)
+$1039万
+$29,017/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J5" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$882万
+$25,781/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="K5" s="23" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$681万
+$25,901/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="L5" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$668万
+$25,383/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="M5" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$655万
+$25,404/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N5" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$457万
+$22,838/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="O5" s="24" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$652万
+$24,878/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="P5" s="22" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$886万
+$25,399/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$798万
+$23,320/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$646万
+$24,556/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$631万
+$24,462/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$400万
+$19,987/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$623万
+$23,786/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$688万
+$26,248/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$924万
+$26,322/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="J6" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$803万
+$23,471/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="K6" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$654万
+$24,884/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L6" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$654万
+$24,884/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="M6" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$648万
+$25,130/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="N6" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$400万
+$19,982/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O6" s="21" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$645万
+$24,615/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="P6" s="21" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$676万
+$25,885/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$870万
+$24,924/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$776万
+$22,677/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$584万
+$22,188/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$571万
+$22,130/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$399万
+$19,950/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$603万
+$23,030/呎
+(26年-07月)</t>
+        </is>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$680万
+$25,943/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$888万
+$25,301/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="J7" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$781万
+$22,836/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K7" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$650万
+$24,697/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L7" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$650万
+$24,697/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M7" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$638万
+$24,735/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="N7" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$399万
+$19,964/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="O7" s="23" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$634万
+$24,206/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="P7" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$590万
+$22,612/呎
+(25年-07月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$787万
+$22,549/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$756万
+$22,096/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$570万
+$21,667/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$558万
+$21,631/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$406万
+$20,322/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$542万
+$20,686/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$673万
+$25,691/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$810万
+$23,084/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="J8" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$761万
+$22,257/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K8" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$637万
+$24,232/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="L8" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$637万
+$24,232/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$558万
+$21,631/呎
+(25年-10月)</t>
+        </is>
+      </c>
+      <c r="N8" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$399万
+$19,936/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O8" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$568万
+$21,673/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P8" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$576万
+$22,087/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$768万
+$22,009/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$703万
+$20,541/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$556万
+$21,142/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$545万
+$21,135/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$395万
+$19,734/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$530万
+$20,244/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H9" s="23" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$663万
+$25,313/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$791万
+$22,523/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$715万
+$20,902/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K9" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$630万
+$23,967/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="L9" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$630万
+$23,967/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="M9" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$545万
+$21,135/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="N9" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$397万
+$19,867/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O9" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$572万
+$21,839/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P9" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$563万
+$21,562/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$723万
+$20,707/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$702万
+$20,520/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$542万
+$20,617/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$544万
+$21,081/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$402万
+$20,088/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$510万
+$19,469/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H10" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$640万
+$24,425/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$773万
+$22,025/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$700万
+$20,458/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K10" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$556万
+$21,129/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$556万
+$21,129/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$532万
+$20,632/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$396万
+$19,816/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$552万
+$21,071/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P10" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$561万
+$21,494/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$709万
+$20,306/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$674万
+$19,710/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$537万
+$20,402/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$521万
+$20,206/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$392万
+$19,614/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$497万
+$18,958/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H11" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$568万
+$21,677/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$729万
+$20,759/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$686万
+$20,068/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K11" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$527万
+$20,054/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$539万
+$20,490/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$511万
+$19,798/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$395万
+$19,743/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$528万
+$20,159/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P11" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$529万
+$20,264/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$697万
+$19,960/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$663万
+$19,376/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$509万
+$19,358/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$512万
+$19,838/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$400万
+$19,989/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G12" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$504万
+$19,253/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H12" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$541万
+$20,637/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$716万
+$20,400/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$675万
+$19,734/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K12" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$528万
+$20,083/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$528万
+$20,083/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$501万
+$19,416/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$390万
+$19,513/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$507万
+$19,362/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P12" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$518万
+$19,863/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$700万
+$20,044/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$651万
+$19,027/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$500万
+$18,998/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$493万
+$19,091/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$390万
+$19,504/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G13" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$499万
+$19,032/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H13" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$553万
+$21,114/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$703万
+$20,041/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$678万
+$19,822/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K13" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$524万
+$19,943/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$519万
+$19,733/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M13" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$503万
+$19,507/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$389万
+$19,467/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$498万
+$19,018/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P13" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$509万
+$19,517/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$675万
+$19,330/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$656万
+$19,171/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$509万
+$19,343/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$486万
+$18,821/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$385万
+$19,274/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$493万
+$18,814/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H14" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$524万
+$19,991/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$693万
+$19,742/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J14" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$661万
+$19,331/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K14" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$500万
+$19,030/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$500万
+$19,030/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M14" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$486万
+$18,821/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$385万
+$19,237/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$491万
+$18,730/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P14" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$513万
+$19,650/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$681万
+$19,516/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$655万
+$19,147/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$503万
+$19,108/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$490万
+$19,007/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$393万
+$19,646/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$473万
+$18,052/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H15" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$518万
+$19,758/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$685万
+$19,503/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J15" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$646万
+$18,903/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K15" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$494万
+$18,798/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$494万
+$18,798/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M15" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$490万
+$19,007/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$380万
+$19,007/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$485万
+$18,502/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P15" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$496万
+$19,003/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$661万
+$18,930/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$628万
+$18,376/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$493万
+$18,732/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$476万
+$18,439/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$381万
+$19,053/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$469万
+$17,891/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H16" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$502万
+$19,165/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$678万
+$19,323/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J16" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$648万
+$18,940/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K16" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$501万
+$19,032/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$490万
+$18,627/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M16" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$476万
+$18,439/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$381万
+$19,058/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$491万
+$18,728/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P16" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$491万
+$18,830/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$651万
+$18,642/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$619万
+$18,099/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$475万
+$18,046/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$479万
+$18,563/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$376万
+$18,823/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$463万
+$17,676/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$495万
+$18,881/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$670万
+$19,084/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J17" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$647万
+$18,915/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K17" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$482万
+$18,344/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L17" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$482万
+$18,344/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M17" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$469万
+$18,168/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N17" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$369万
+$18,428/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O17" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$485万
+$18,495/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P17" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$485万
+$18,601/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$641万
+$18,358/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$609万
+$17,819/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$466万
+$17,704/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$460万
+$17,843/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$380万
+$18,997/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$458万
+$17,462/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$486万
+$18,537/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$661万
+$18,846/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J18" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$639万
+$18,687/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K18" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$473万
+$18,001/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$473万
+$18,001/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M18" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$460万
+$17,843/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N18" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$366万
+$18,280/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O18" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$468万
+$17,873/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P18" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$488万
+$18,710/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$629万
+$18,012/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$598万
+$17,485/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$457万
+$17,364/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$452万
+$17,516/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$364万
+$18,188/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$452万
+$17,248/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$482万
+$18,390/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$651万
+$18,544/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J19" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$616万
+$18,013/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K19" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$464万
+$17,658/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$464万
+$17,658/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M19" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$452万
+$17,516/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N19" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$371万
+$18,536/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O19" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$462万
+$17,641/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P19" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$481万
+$18,418/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$637万
+$18,246/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$606万
+$17,714/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$453万
+$17,206/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$444万
+$17,191/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$363万
+$18,133/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$451万
+$17,223/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$468万
+$17,848/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$652万
+$18,583/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="J20" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$605万
+$17,679/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K20" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$455万
+$17,316/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L20" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$455万
+$17,316/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M20" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$444万
+$17,191/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N20" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$362万
+$18,082/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O20" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$456万
+$17,413/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P20" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$461万
+$17,681/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$605万
+$17,324/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$575万
+$16,821/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$450万
+$17,098/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$437万
+$16,920/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$358万
+$17,898/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$441万
+$16,823/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$459万
+$17,505/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I21" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$646万
+$18,410/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J21" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$593万
+$17,345/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K21" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$446万
+$16,976/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L21" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$446万
+$16,976/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M21" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$445万
+$17,233/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N21" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$357万
+$17,848/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O21" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$450万
+$17,185/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P21" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$452万
+$17,335/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$595万
+$17,040/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$566万
+$16,541/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$433万
+$16,451/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$430万
+$16,649/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$353万
+$17,668/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$443万
+$16,916/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$461万
+$17,594/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I22" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$615万
+$17,527/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J22" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$584万
+$17,068/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="K22" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$448万
+$17,052/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L22" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$439万
+$16,689/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M22" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$433万
+$16,776/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$433万
+$21,641/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O22" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$454万
+$17,325/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P22" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$445万
+$17,046/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$597万
+$17,117/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$554万
+$16,208/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$432万
+$16,430/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$421万
+$16,324/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F23" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$348万
+$17,383/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G23" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$435万
+$16,586/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$444万
+$16,932/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I23" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$605万
+$17,228/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J23" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$574万
+$16,791/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$441万
+$16,763/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$431万
+$16,406/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M23" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$421万
+$16,324/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$346万
+$17,324/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="O23" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$437万
+$16,669/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="P23" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$437万
+$16,761/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 349呎 (2房)
+$577万
+$16,523/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 342呎 (2房)
+$541万
+$15,820/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 263呎 (1房)
+$410万
+$15,591/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 258呎 (1房)
+$410万
+$15,890/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 200呎 (开放式)
+$346万
+$17,296/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 262呎 (1房)
+$417万
+$15,914/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 262呎 (1房)
+$438万
+$16,704/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 351呎 (2房)
+$601万
+$17,113/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="J24" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 342呎 (2房)
+$565万
+$16,514/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="K24" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 263呎 (1房)
+$425万
+$16,175/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 263呎 (1房)
+$425万
+$16,175/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="M24" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 258呎 (1房)
+$429万
+$16,632/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 200呎 (开放式)
+$337万
+$16,872/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="O24" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 262呎 (1房)
+$446万
+$17,041/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="P24" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 261呎 (1房)
+$431万
+$16,532/呎
+(25年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A1 | 311呎 (2房)
+$723万
+$23,241/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>A2 | 304呎 (2房)
+$656万
+$21,579/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>A3 | 225呎 (1房)
+$470万
+$20,881/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="inlineStr">
+        <is>
+          <t>A5 | 221呎 (1房)
+$465万
+$21,040/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="F25" s="20" t="inlineStr">
+        <is>
+          <t>A6 | 178呎 (开放式)
+$452万
+$25,393/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>A7 | 224呎 (1房)
+$585万
+$26,116/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
+        <is>
+          <t>A8 | 224呎 (1房)
+$633万
+$28,259/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="I25" s="20" t="inlineStr">
+        <is>
+          <t>B1 | 313呎 (2房)
+$725万
+$23,163/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="J25" s="20" t="inlineStr">
+        <is>
+          <t>B2 | 304呎 (2房)
+$660万
+$21,711/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="K25" s="20" t="inlineStr">
+        <is>
+          <t>B3 | 225呎 (1房)
+$475万
+$21,111/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="L25" s="20" t="inlineStr">
+        <is>
+          <t>B5 | 225呎 (1房)
+$470万
+$20,889/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="M25" s="20" t="inlineStr">
+        <is>
+          <t>B6 | 220呎 (1房)
+$465万
+$21,136/呎
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="N25" s="20" t="inlineStr">
+        <is>
+          <t>B7 | 178呎 (开放式)
+$458万
+$25,730/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="O25" s="20" t="inlineStr">
+        <is>
+          <t>B8 | 224呎 (1房)
+$520万
+$23,214/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="P25" s="20" t="inlineStr">
+        <is>
+          <t>B9 | 224呎 (1房)
+$618万
+$27,593/呎
+(26年-04月)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -662,7 +662,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -849,7 +849,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -15405,7 +15405,7 @@
           <t>B6 | 258呎 (1房)
 $655万
 $25,404/呎
-(26年-06月)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -652,7 +652,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J315"/>
+  <dimension ref="A1:N315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -665,6 +665,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -722,6 +726,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -768,6 +792,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>5996560</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>22888</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -814,6 +854,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>4567700</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>22838</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -860,6 +916,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>6554200</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>25404</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -906,6 +978,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>6675700</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>25383</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -952,6 +1040,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>6267040</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>23829</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -998,6 +1102,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>8817000</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>25781</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1044,6 +1164,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>10388000</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>29017</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1090,6 +1226,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>5796000</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>22122</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1136,6 +1288,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>4636300</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>23182</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1182,6 +1350,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6379800</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>24728</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1228,6 +1412,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6527700</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>24820</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1274,6 +1474,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>8677900</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>25374</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1320,6 +1536,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>31728</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1366,6 +1598,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6215520</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>23814</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1412,6 +1660,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>5933080</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>22645</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1458,6 +1722,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>3996400</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>19982</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1504,6 +1784,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>6483600</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>25130</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1550,6 +1846,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>6544400</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>24884</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1596,6 +1908,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>6544400</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>24884</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1642,6 +1970,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>8027000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>23471</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1688,6 +2032,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>8499880</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>24216</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1734,6 +2094,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>6326840</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>24148</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1780,6 +2156,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>5733440</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>21883</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1826,6 +2218,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>3997400</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>19987</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1872,6 +2280,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>6311200</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>24462</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1918,6 +2342,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>6458200</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>24556</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1964,6 +2404,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>7975400</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>23320</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2010,6 +2466,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>8864100</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>25399</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2056,6 +2528,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5901800</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>22612</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2102,6 +2590,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>5834640</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>22270</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2148,6 +2652,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>3992800</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>19964</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2194,6 +2714,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>6381700</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>24735</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2240,6 +2776,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>6495400</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>24697</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2286,6 +2838,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>6495400</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>24697</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2332,6 +2900,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>7809800</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>22836</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2378,6 +2962,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>8880700</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>25301</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2424,6 +3024,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6253240</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>23867</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2470,6 +3086,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6033800</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>23030</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2516,6 +3148,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>3990000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>19950</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2562,6 +3210,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>5709500</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>22130</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2608,6 +3272,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5835500</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>22188</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2654,6 +3334,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>7755600</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>22677</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2700,6 +3396,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>8698400</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>24924</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2746,6 +3458,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>5764700</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>22087</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2792,6 +3520,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>5678200</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>21673</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2838,6 +3582,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>3987200</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>19936</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2884,6 +3644,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>5580700</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>21631</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2930,6 +3706,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>6372900</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>24232</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2976,6 +3768,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>6372900</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>24232</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3022,6 +3830,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>7612000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>22257</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3068,6 +3892,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>8102400</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>23084</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3114,6 +3954,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>6192520</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>23636</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3160,6 +4016,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>5419700</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>20686</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3206,6 +4078,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>4064500</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>20322</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3252,6 +4140,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>5580700</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>21631</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3298,6 +4202,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>5698400</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>21667</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3344,6 +4264,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>7556800</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>22096</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3390,6 +4326,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>7869600</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>22549</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3436,6 +4388,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>5627600</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>21562</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3482,6 +4450,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>5721800</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>21839</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3528,6 +4512,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>3973400</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>19867</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3574,6 +4574,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>5452800</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>21135</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3620,6 +4636,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>6303300</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>23967</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3666,6 +4698,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>6303300</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>23967</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3712,6 +4760,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>7148400</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>20902</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3758,6 +4822,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>7905500</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>22523</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3804,6 +4884,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>6101440</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23288</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>120天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3850,6 +4946,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>5303800</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>20244</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3896,6 +5008,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>3946800</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>19734</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3942,6 +5070,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>5452800</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>21135</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3988,6 +5132,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>5560400</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>21142</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4034,6 +5194,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>7025100</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>20541</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4080,6 +5256,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>7681000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>22009</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4126,6 +5318,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5609900</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>21494</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4172,6 +5380,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5520600</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>21071</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4218,6 +5442,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>3963300</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>19816</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4264,6 +5504,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>5323100</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>20632</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4310,6 +5566,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>5556800</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>21129</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4356,6 +5628,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>5556800</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>21129</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4402,6 +5690,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>6996600</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>20458</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4448,6 +5752,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>7730700</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>22025</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4494,6 +5814,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>6399400</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>24425</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4540,6 +5876,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>5101000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>19469</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4586,6 +5938,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>4017500</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>20088</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4632,6 +6000,22 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>5438800</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>21081</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4678,6 +6062,22 @@
       </c>
       <c r="J88" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>5422400</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>20617</v>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4724,6 +6124,22 @@
       </c>
       <c r="J89" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>7018000</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>20520</v>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4770,6 +6186,22 @@
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>7226600</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>20707</v>
+      </c>
+      <c r="M90" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4816,6 +6248,22 @@
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>5289000</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>20264</v>
+      </c>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4862,6 +6310,22 @@
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>5281700</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>20159</v>
+      </c>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4908,6 +6372,22 @@
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>3948600</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>19743</v>
+      </c>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4954,6 +6434,22 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>5107800</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>19798</v>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5000,6 +6496,22 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>5389000</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>20490</v>
+      </c>
+      <c r="M95" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5046,6 +6558,22 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>5274300</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>20054</v>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5092,6 +6620,22 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>6863200</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>20068</v>
+      </c>
+      <c r="M97" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5138,6 +6682,22 @@
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>7286400</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>20759</v>
+      </c>
+      <c r="M98" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5184,6 +6744,22 @@
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>5679400</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>21677</v>
+      </c>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5230,6 +6806,22 @@
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>4967000</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>18958</v>
+      </c>
+      <c r="M100" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5276,6 +6868,22 @@
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>3922800</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>19614</v>
+      </c>
+      <c r="M101" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5322,6 +6930,22 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>5213200</v>
+      </c>
+      <c r="L102" s="5" t="n">
+        <v>20206</v>
+      </c>
+      <c r="M102" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5368,6 +6992,22 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K103" s="5" t="n">
+        <v>5365600</v>
+      </c>
+      <c r="L103" s="5" t="n">
+        <v>20402</v>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5414,6 +7054,22 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K104" s="5" t="n">
+        <v>6740800</v>
+      </c>
+      <c r="L104" s="5" t="n">
+        <v>19710</v>
+      </c>
+      <c r="M104" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5460,6 +7116,22 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K105" s="5" t="n">
+        <v>7086700</v>
+      </c>
+      <c r="L105" s="5" t="n">
+        <v>20306</v>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5506,6 +7178,22 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K106" s="5" t="n">
+        <v>5184200</v>
+      </c>
+      <c r="L106" s="5" t="n">
+        <v>19863</v>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5552,6 +7240,22 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K107" s="5" t="n">
+        <v>5072800</v>
+      </c>
+      <c r="L107" s="5" t="n">
+        <v>19362</v>
+      </c>
+      <c r="M107" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5598,6 +7302,22 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K108" s="5" t="n">
+        <v>3902600</v>
+      </c>
+      <c r="L108" s="5" t="n">
+        <v>19513</v>
+      </c>
+      <c r="M108" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5644,6 +7364,22 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K109" s="5" t="n">
+        <v>5009400</v>
+      </c>
+      <c r="L109" s="5" t="n">
+        <v>19416</v>
+      </c>
+      <c r="M109" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5690,6 +7426,22 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K110" s="5" t="n">
+        <v>5281800</v>
+      </c>
+      <c r="L110" s="5" t="n">
+        <v>20083</v>
+      </c>
+      <c r="M110" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5736,6 +7488,22 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K111" s="5" t="n">
+        <v>5281800</v>
+      </c>
+      <c r="L111" s="5" t="n">
+        <v>20083</v>
+      </c>
+      <c r="M111" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5782,6 +7550,22 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" s="5" t="n">
+        <v>6749100</v>
+      </c>
+      <c r="L112" s="5" t="n">
+        <v>19734</v>
+      </c>
+      <c r="M112" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5828,6 +7612,22 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K113" s="5" t="n">
+        <v>7160300</v>
+      </c>
+      <c r="L113" s="5" t="n">
+        <v>20400</v>
+      </c>
+      <c r="M113" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5874,6 +7674,22 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K114" s="5" t="n">
+        <v>5406800</v>
+      </c>
+      <c r="L114" s="5" t="n">
+        <v>20637</v>
+      </c>
+      <c r="M114" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5920,6 +7736,22 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K115" s="5" t="n">
+        <v>5044300</v>
+      </c>
+      <c r="L115" s="5" t="n">
+        <v>19253</v>
+      </c>
+      <c r="M115" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -5966,6 +7798,22 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K116" s="5" t="n">
+        <v>3997800</v>
+      </c>
+      <c r="L116" s="5" t="n">
+        <v>19989</v>
+      </c>
+      <c r="M116" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6012,6 +7860,22 @@
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K117" s="5" t="n">
+        <v>5118300</v>
+      </c>
+      <c r="L117" s="5" t="n">
+        <v>19838</v>
+      </c>
+      <c r="M117" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6058,6 +7922,22 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K118" s="5" t="n">
+        <v>5091200</v>
+      </c>
+      <c r="L118" s="5" t="n">
+        <v>19358</v>
+      </c>
+      <c r="M118" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6104,6 +7984,22 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K119" s="5" t="n">
+        <v>6626700</v>
+      </c>
+      <c r="L119" s="5" t="n">
+        <v>19376</v>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6150,6 +8046,22 @@
       </c>
       <c r="J120" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K120" s="5" t="n">
+        <v>6966200</v>
+      </c>
+      <c r="L120" s="5" t="n">
+        <v>19960</v>
+      </c>
+      <c r="M120" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6196,6 +8108,22 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K121" s="5" t="n">
+        <v>5094000</v>
+      </c>
+      <c r="L121" s="5" t="n">
+        <v>19517</v>
+      </c>
+      <c r="M121" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6242,6 +8170,22 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K122" s="5" t="n">
+        <v>4982700</v>
+      </c>
+      <c r="L122" s="5" t="n">
+        <v>19018</v>
+      </c>
+      <c r="M122" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6288,6 +8232,22 @@
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K123" s="5" t="n">
+        <v>3893400</v>
+      </c>
+      <c r="L123" s="5" t="n">
+        <v>19467</v>
+      </c>
+      <c r="M123" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N123" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6334,6 +8294,22 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K124" s="5" t="n">
+        <v>5032700</v>
+      </c>
+      <c r="L124" s="5" t="n">
+        <v>19507</v>
+      </c>
+      <c r="M124" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N124" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6380,6 +8356,22 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K125" s="5" t="n">
+        <v>5189700</v>
+      </c>
+      <c r="L125" s="5" t="n">
+        <v>19733</v>
+      </c>
+      <c r="M125" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N125" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6426,6 +8418,22 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K126" s="5" t="n">
+        <v>5244900</v>
+      </c>
+      <c r="L126" s="5" t="n">
+        <v>19943</v>
+      </c>
+      <c r="M126" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N126" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6472,6 +8480,22 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K127" s="5" t="n">
+        <v>6779200</v>
+      </c>
+      <c r="L127" s="5" t="n">
+        <v>19822</v>
+      </c>
+      <c r="M127" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N127" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6518,6 +8542,22 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K128" s="5" t="n">
+        <v>7034300</v>
+      </c>
+      <c r="L128" s="5" t="n">
+        <v>20041</v>
+      </c>
+      <c r="M128" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N128" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6564,6 +8604,22 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K129" s="5" t="n">
+        <v>5531800</v>
+      </c>
+      <c r="L129" s="5" t="n">
+        <v>21114</v>
+      </c>
+      <c r="M129" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N129" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6610,6 +8666,22 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K130" s="5" t="n">
+        <v>4986400</v>
+      </c>
+      <c r="L130" s="5" t="n">
+        <v>19032</v>
+      </c>
+      <c r="M130" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N130" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6656,6 +8728,22 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K131" s="5" t="n">
+        <v>3900800</v>
+      </c>
+      <c r="L131" s="5" t="n">
+        <v>19504</v>
+      </c>
+      <c r="M131" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N131" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6702,6 +8790,22 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K132" s="5" t="n">
+        <v>4925600</v>
+      </c>
+      <c r="L132" s="5" t="n">
+        <v>19091</v>
+      </c>
+      <c r="M132" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N132" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6748,6 +8852,22 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K133" s="5" t="n">
+        <v>4996500</v>
+      </c>
+      <c r="L133" s="5" t="n">
+        <v>18998</v>
+      </c>
+      <c r="M133" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N133" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6794,6 +8914,22 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K134" s="5" t="n">
+        <v>6507100</v>
+      </c>
+      <c r="L134" s="5" t="n">
+        <v>19027</v>
+      </c>
+      <c r="M134" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N134" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6840,6 +8976,22 @@
       </c>
       <c r="J135" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K135" s="5" t="n">
+        <v>6995400</v>
+      </c>
+      <c r="L135" s="5" t="n">
+        <v>20044</v>
+      </c>
+      <c r="M135" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N135" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6886,6 +9038,22 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K136" s="5" t="n">
+        <v>5128600</v>
+      </c>
+      <c r="L136" s="5" t="n">
+        <v>19650</v>
+      </c>
+      <c r="M136" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N136" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6932,6 +9100,22 @@
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K137" s="5" t="n">
+        <v>4907200</v>
+      </c>
+      <c r="L137" s="5" t="n">
+        <v>18730</v>
+      </c>
+      <c r="M137" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N137" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -6978,6 +9162,22 @@
       </c>
       <c r="J138" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K138" s="5" t="n">
+        <v>3847400</v>
+      </c>
+      <c r="L138" s="5" t="n">
+        <v>19237</v>
+      </c>
+      <c r="M138" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N138" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7024,6 +9224,22 @@
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K139" s="5" t="n">
+        <v>4855700</v>
+      </c>
+      <c r="L139" s="5" t="n">
+        <v>18821</v>
+      </c>
+      <c r="M139" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N139" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7070,6 +9286,22 @@
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K140" s="5" t="n">
+        <v>5004800</v>
+      </c>
+      <c r="L140" s="5" t="n">
+        <v>19030</v>
+      </c>
+      <c r="M140" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N140" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7116,6 +9348,22 @@
       </c>
       <c r="J141" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K141" s="5" t="n">
+        <v>5004800</v>
+      </c>
+      <c r="L141" s="5" t="n">
+        <v>19030</v>
+      </c>
+      <c r="M141" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N141" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7162,6 +9410,22 @@
       </c>
       <c r="J142" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K142" s="5" t="n">
+        <v>6611300</v>
+      </c>
+      <c r="L142" s="5" t="n">
+        <v>19331</v>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7208,6 +9472,22 @@
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K143" s="5" t="n">
+        <v>6929400</v>
+      </c>
+      <c r="L143" s="5" t="n">
+        <v>19742</v>
+      </c>
+      <c r="M143" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N143" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7254,6 +9534,22 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K144" s="5" t="n">
+        <v>5237600</v>
+      </c>
+      <c r="L144" s="5" t="n">
+        <v>19991</v>
+      </c>
+      <c r="M144" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N144" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7300,6 +9596,22 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K145" s="5" t="n">
+        <v>4929300</v>
+      </c>
+      <c r="L145" s="5" t="n">
+        <v>18814</v>
+      </c>
+      <c r="M145" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N145" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7346,6 +9658,22 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K146" s="5" t="n">
+        <v>3854800</v>
+      </c>
+      <c r="L146" s="5" t="n">
+        <v>19274</v>
+      </c>
+      <c r="M146" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N146" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7392,6 +9720,22 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K147" s="5" t="n">
+        <v>4855700</v>
+      </c>
+      <c r="L147" s="5" t="n">
+        <v>18821</v>
+      </c>
+      <c r="M147" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N147" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7438,6 +9782,22 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K148" s="5" t="n">
+        <v>5087200</v>
+      </c>
+      <c r="L148" s="5" t="n">
+        <v>19343</v>
+      </c>
+      <c r="M148" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N148" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7484,6 +9844,22 @@
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K149" s="5" t="n">
+        <v>6556500</v>
+      </c>
+      <c r="L149" s="5" t="n">
+        <v>19171</v>
+      </c>
+      <c r="M149" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N149" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7530,6 +9906,22 @@
       </c>
       <c r="J150" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K150" s="5" t="n">
+        <v>6746300</v>
+      </c>
+      <c r="L150" s="5" t="n">
+        <v>19330</v>
+      </c>
+      <c r="M150" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N150" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7576,6 +9968,22 @@
       </c>
       <c r="J151" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K151" s="5" t="n">
+        <v>4959700</v>
+      </c>
+      <c r="L151" s="5" t="n">
+        <v>19003</v>
+      </c>
+      <c r="M151" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N151" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7622,6 +10030,22 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K152" s="5" t="n">
+        <v>4847400</v>
+      </c>
+      <c r="L152" s="5" t="n">
+        <v>18502</v>
+      </c>
+      <c r="M152" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N152" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7668,6 +10092,22 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K153" s="5" t="n">
+        <v>3801400</v>
+      </c>
+      <c r="L153" s="5" t="n">
+        <v>19007</v>
+      </c>
+      <c r="M153" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N153" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7714,6 +10154,22 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K154" s="5" t="n">
+        <v>4903900</v>
+      </c>
+      <c r="L154" s="5" t="n">
+        <v>19007</v>
+      </c>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7760,6 +10216,22 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K155" s="5" t="n">
+        <v>4944000</v>
+      </c>
+      <c r="L155" s="5" t="n">
+        <v>18798</v>
+      </c>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7806,6 +10278,22 @@
       </c>
       <c r="J156" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K156" s="5" t="n">
+        <v>4944000</v>
+      </c>
+      <c r="L156" s="5" t="n">
+        <v>18798</v>
+      </c>
+      <c r="M156" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N156" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7852,6 +10340,22 @@
       </c>
       <c r="J157" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K157" s="5" t="n">
+        <v>6464800</v>
+      </c>
+      <c r="L157" s="5" t="n">
+        <v>18903</v>
+      </c>
+      <c r="M157" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N157" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7898,6 +10402,22 @@
       </c>
       <c r="J158" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K158" s="5" t="n">
+        <v>6845700</v>
+      </c>
+      <c r="L158" s="5" t="n">
+        <v>19503</v>
+      </c>
+      <c r="M158" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N158" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7944,6 +10464,22 @@
       </c>
       <c r="J159" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K159" s="5" t="n">
+        <v>5176500</v>
+      </c>
+      <c r="L159" s="5" t="n">
+        <v>19758</v>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -7990,6 +10526,22 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K160" s="5" t="n">
+        <v>4729700</v>
+      </c>
+      <c r="L160" s="5" t="n">
+        <v>18052</v>
+      </c>
+      <c r="M160" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N160" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8036,6 +10588,22 @@
       </c>
       <c r="J161" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K161" s="5" t="n">
+        <v>3929200</v>
+      </c>
+      <c r="L161" s="5" t="n">
+        <v>19646</v>
+      </c>
+      <c r="M161" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N161" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8082,6 +10650,22 @@
       </c>
       <c r="J162" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K162" s="5" t="n">
+        <v>4903900</v>
+      </c>
+      <c r="L162" s="5" t="n">
+        <v>19007</v>
+      </c>
+      <c r="M162" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N162" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8128,6 +10712,22 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" s="5" t="n">
+        <v>5025500</v>
+      </c>
+      <c r="L163" s="5" t="n">
+        <v>19108</v>
+      </c>
+      <c r="M163" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N163" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8174,6 +10774,22 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" s="5" t="n">
+        <v>6548300</v>
+      </c>
+      <c r="L164" s="5" t="n">
+        <v>19147</v>
+      </c>
+      <c r="M164" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N164" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8220,6 +10836,22 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" s="5" t="n">
+        <v>6811200</v>
+      </c>
+      <c r="L165" s="5" t="n">
+        <v>19516</v>
+      </c>
+      <c r="M165" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8266,6 +10898,22 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K166" s="5" t="n">
+        <v>4914600</v>
+      </c>
+      <c r="L166" s="5" t="n">
+        <v>18830</v>
+      </c>
+      <c r="M166" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N166" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8312,6 +10960,22 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K167" s="5" t="n">
+        <v>4906800</v>
+      </c>
+      <c r="L167" s="5" t="n">
+        <v>18728</v>
+      </c>
+      <c r="M167" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N167" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8358,6 +11022,22 @@
       </c>
       <c r="J168" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K168" s="5" t="n">
+        <v>3811700</v>
+      </c>
+      <c r="L168" s="5" t="n">
+        <v>19058</v>
+      </c>
+      <c r="M168" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N168" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8404,6 +11084,22 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="5" t="n">
+        <v>4757300</v>
+      </c>
+      <c r="L169" s="5" t="n">
+        <v>18439</v>
+      </c>
+      <c r="M169" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8450,6 +11146,22 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="5" t="n">
+        <v>4899000</v>
+      </c>
+      <c r="L170" s="5" t="n">
+        <v>18627</v>
+      </c>
+      <c r="M170" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8496,6 +11208,22 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="5" t="n">
+        <v>5005500</v>
+      </c>
+      <c r="L171" s="5" t="n">
+        <v>19032</v>
+      </c>
+      <c r="M171" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8542,6 +11270,22 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="5" t="n">
+        <v>6477400</v>
+      </c>
+      <c r="L172" s="5" t="n">
+        <v>18940</v>
+      </c>
+      <c r="M172" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8588,6 +11332,22 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="5" t="n">
+        <v>6782200</v>
+      </c>
+      <c r="L173" s="5" t="n">
+        <v>19323</v>
+      </c>
+      <c r="M173" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8634,6 +11394,22 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="5" t="n">
+        <v>5021300</v>
+      </c>
+      <c r="L174" s="5" t="n">
+        <v>19165</v>
+      </c>
+      <c r="M174" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8680,6 +11456,22 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="5" t="n">
+        <v>4687400</v>
+      </c>
+      <c r="L175" s="5" t="n">
+        <v>17891</v>
+      </c>
+      <c r="M175" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8726,6 +11518,22 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="5" t="n">
+        <v>3810600</v>
+      </c>
+      <c r="L176" s="5" t="n">
+        <v>19053</v>
+      </c>
+      <c r="M176" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8772,6 +11580,22 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="5" t="n">
+        <v>4757300</v>
+      </c>
+      <c r="L177" s="5" t="n">
+        <v>18439</v>
+      </c>
+      <c r="M177" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8818,6 +11642,22 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="5" t="n">
+        <v>4926500</v>
+      </c>
+      <c r="L178" s="5" t="n">
+        <v>18732</v>
+      </c>
+      <c r="M178" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8864,6 +11704,22 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="5" t="n">
+        <v>6284500</v>
+      </c>
+      <c r="L179" s="5" t="n">
+        <v>18376</v>
+      </c>
+      <c r="M179" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8910,6 +11766,22 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="5" t="n">
+        <v>6606500</v>
+      </c>
+      <c r="L180" s="5" t="n">
+        <v>18930</v>
+      </c>
+      <c r="M180" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -8956,6 +11828,22 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="5" t="n">
+        <v>4854800</v>
+      </c>
+      <c r="L181" s="5" t="n">
+        <v>18601</v>
+      </c>
+      <c r="M181" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9002,6 +11890,22 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="5" t="n">
+        <v>4845700</v>
+      </c>
+      <c r="L182" s="5" t="n">
+        <v>18495</v>
+      </c>
+      <c r="M182" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9048,6 +11952,22 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="5" t="n">
+        <v>3685500</v>
+      </c>
+      <c r="L183" s="5" t="n">
+        <v>18428</v>
+      </c>
+      <c r="M183" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9094,6 +12014,22 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" s="5" t="n">
+        <v>4687400</v>
+      </c>
+      <c r="L184" s="5" t="n">
+        <v>18168</v>
+      </c>
+      <c r="M184" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9140,6 +12076,22 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" s="5" t="n">
+        <v>4824400</v>
+      </c>
+      <c r="L185" s="5" t="n">
+        <v>18344</v>
+      </c>
+      <c r="M185" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9186,6 +12138,22 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" s="5" t="n">
+        <v>4824400</v>
+      </c>
+      <c r="L186" s="5" t="n">
+        <v>18344</v>
+      </c>
+      <c r="M186" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9232,6 +12200,22 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K187" s="5" t="n">
+        <v>6469000</v>
+      </c>
+      <c r="L187" s="5" t="n">
+        <v>18915</v>
+      </c>
+      <c r="M187" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N187" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9278,6 +12262,22 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K188" s="5" t="n">
+        <v>6698500</v>
+      </c>
+      <c r="L188" s="5" t="n">
+        <v>19084</v>
+      </c>
+      <c r="M188" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N188" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9324,6 +12324,22 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K189" s="5" t="n">
+        <v>4946800</v>
+      </c>
+      <c r="L189" s="5" t="n">
+        <v>18881</v>
+      </c>
+      <c r="M189" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N189" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9370,6 +12386,22 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K190" s="5" t="n">
+        <v>4631200</v>
+      </c>
+      <c r="L190" s="5" t="n">
+        <v>17676</v>
+      </c>
+      <c r="M190" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N190" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9416,6 +12448,22 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K191" s="5" t="n">
+        <v>3764600</v>
+      </c>
+      <c r="L191" s="5" t="n">
+        <v>18823</v>
+      </c>
+      <c r="M191" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N191" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9462,6 +12510,22 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K192" s="5" t="n">
+        <v>4789300</v>
+      </c>
+      <c r="L192" s="5" t="n">
+        <v>18563</v>
+      </c>
+      <c r="M192" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N192" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9508,6 +12572,22 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K193" s="5" t="n">
+        <v>4746200</v>
+      </c>
+      <c r="L193" s="5" t="n">
+        <v>18046</v>
+      </c>
+      <c r="M193" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N193" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9554,6 +12634,22 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K194" s="5" t="n">
+        <v>6189700</v>
+      </c>
+      <c r="L194" s="5" t="n">
+        <v>18099</v>
+      </c>
+      <c r="M194" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N194" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9600,6 +12696,22 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K195" s="5" t="n">
+        <v>6506200</v>
+      </c>
+      <c r="L195" s="5" t="n">
+        <v>18642</v>
+      </c>
+      <c r="M195" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N195" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9646,6 +12758,22 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K196" s="5" t="n">
+        <v>4883300</v>
+      </c>
+      <c r="L196" s="5" t="n">
+        <v>18710</v>
+      </c>
+      <c r="M196" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N196" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9692,6 +12820,22 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K197" s="5" t="n">
+        <v>4682800</v>
+      </c>
+      <c r="L197" s="5" t="n">
+        <v>17873</v>
+      </c>
+      <c r="M197" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N197" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9738,6 +12882,22 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K198" s="5" t="n">
+        <v>3656000</v>
+      </c>
+      <c r="L198" s="5" t="n">
+        <v>18280</v>
+      </c>
+      <c r="M198" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N198" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9784,6 +12944,22 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K199" s="5" t="n">
+        <v>4603600</v>
+      </c>
+      <c r="L199" s="5" t="n">
+        <v>17843</v>
+      </c>
+      <c r="M199" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N199" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9830,6 +13006,22 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K200" s="5" t="n">
+        <v>4734300</v>
+      </c>
+      <c r="L200" s="5" t="n">
+        <v>18001</v>
+      </c>
+      <c r="M200" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N200" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9876,6 +13068,22 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K201" s="5" t="n">
+        <v>4734300</v>
+      </c>
+      <c r="L201" s="5" t="n">
+        <v>18001</v>
+      </c>
+      <c r="M201" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N201" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9922,6 +13130,22 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K202" s="5" t="n">
+        <v>6391000</v>
+      </c>
+      <c r="L202" s="5" t="n">
+        <v>18687</v>
+      </c>
+      <c r="M202" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N202" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -9968,6 +13192,22 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K203" s="5" t="n">
+        <v>6614800</v>
+      </c>
+      <c r="L203" s="5" t="n">
+        <v>18846</v>
+      </c>
+      <c r="M203" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N203" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10014,6 +13254,22 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K204" s="5" t="n">
+        <v>4856600</v>
+      </c>
+      <c r="L204" s="5" t="n">
+        <v>18537</v>
+      </c>
+      <c r="M204" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N204" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10060,6 +13316,22 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K205" s="5" t="n">
+        <v>4575100</v>
+      </c>
+      <c r="L205" s="5" t="n">
+        <v>17462</v>
+      </c>
+      <c r="M205" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N205" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10106,6 +13378,22 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K206" s="5" t="n">
+        <v>3799400</v>
+      </c>
+      <c r="L206" s="5" t="n">
+        <v>18997</v>
+      </c>
+      <c r="M206" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N206" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10152,6 +13440,22 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K207" s="5" t="n">
+        <v>4603600</v>
+      </c>
+      <c r="L207" s="5" t="n">
+        <v>17843</v>
+      </c>
+      <c r="M207" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N207" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10198,6 +13502,22 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K208" s="5" t="n">
+        <v>4656100</v>
+      </c>
+      <c r="L208" s="5" t="n">
+        <v>17704</v>
+      </c>
+      <c r="M208" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N208" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10244,6 +13564,22 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K209" s="5" t="n">
+        <v>6094000</v>
+      </c>
+      <c r="L209" s="5" t="n">
+        <v>17819</v>
+      </c>
+      <c r="M209" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N209" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10290,6 +13626,22 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K210" s="5" t="n">
+        <v>6406800</v>
+      </c>
+      <c r="L210" s="5" t="n">
+        <v>18358</v>
+      </c>
+      <c r="M210" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N210" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10336,6 +13688,22 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K211" s="5" t="n">
+        <v>4807100</v>
+      </c>
+      <c r="L211" s="5" t="n">
+        <v>18418</v>
+      </c>
+      <c r="M211" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N211" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10382,6 +13750,22 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K212" s="5" t="n">
+        <v>4622000</v>
+      </c>
+      <c r="L212" s="5" t="n">
+        <v>17641</v>
+      </c>
+      <c r="M212" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N212" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10428,6 +13812,22 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K213" s="5" t="n">
+        <v>3707300</v>
+      </c>
+      <c r="L213" s="5" t="n">
+        <v>18536</v>
+      </c>
+      <c r="M213" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N213" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10474,6 +13874,22 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K214" s="5" t="n">
+        <v>4519000</v>
+      </c>
+      <c r="L214" s="5" t="n">
+        <v>17516</v>
+      </c>
+      <c r="M214" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N214" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10520,6 +13936,22 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K215" s="5" t="n">
+        <v>4644100</v>
+      </c>
+      <c r="L215" s="5" t="n">
+        <v>17658</v>
+      </c>
+      <c r="M215" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N215" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10566,6 +13998,22 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K216" s="5" t="n">
+        <v>4644100</v>
+      </c>
+      <c r="L216" s="5" t="n">
+        <v>17658</v>
+      </c>
+      <c r="M216" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N216" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10612,6 +14060,22 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K217" s="5" t="n">
+        <v>6160300</v>
+      </c>
+      <c r="L217" s="5" t="n">
+        <v>18013</v>
+      </c>
+      <c r="M217" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N217" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10658,6 +14122,22 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K218" s="5" t="n">
+        <v>6509000</v>
+      </c>
+      <c r="L218" s="5" t="n">
+        <v>18544</v>
+      </c>
+      <c r="M218" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N218" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10704,6 +14184,22 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K219" s="5" t="n">
+        <v>4818300</v>
+      </c>
+      <c r="L219" s="5" t="n">
+        <v>18390</v>
+      </c>
+      <c r="M219" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N219" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10750,6 +14246,22 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K220" s="5" t="n">
+        <v>4519000</v>
+      </c>
+      <c r="L220" s="5" t="n">
+        <v>17248</v>
+      </c>
+      <c r="M220" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N220" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10796,6 +14308,22 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K221" s="5" t="n">
+        <v>3637600</v>
+      </c>
+      <c r="L221" s="5" t="n">
+        <v>18188</v>
+      </c>
+      <c r="M221" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N221" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10842,6 +14370,22 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K222" s="5" t="n">
+        <v>4519000</v>
+      </c>
+      <c r="L222" s="5" t="n">
+        <v>17516</v>
+      </c>
+      <c r="M222" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N222" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10888,6 +14432,22 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K223" s="5" t="n">
+        <v>4566800</v>
+      </c>
+      <c r="L223" s="5" t="n">
+        <v>17364</v>
+      </c>
+      <c r="M223" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N223" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10934,6 +14494,22 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K224" s="5" t="n">
+        <v>5980000</v>
+      </c>
+      <c r="L224" s="5" t="n">
+        <v>17485</v>
+      </c>
+      <c r="M224" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N224" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -10980,6 +14556,22 @@
       </c>
       <c r="J225" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K225" s="5" t="n">
+        <v>6286300</v>
+      </c>
+      <c r="L225" s="5" t="n">
+        <v>18012</v>
+      </c>
+      <c r="M225" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N225" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11026,6 +14618,22 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K226" s="5" t="n">
+        <v>4614700</v>
+      </c>
+      <c r="L226" s="5" t="n">
+        <v>17681</v>
+      </c>
+      <c r="M226" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N226" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11072,6 +14680,22 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K227" s="5" t="n">
+        <v>4562200</v>
+      </c>
+      <c r="L227" s="5" t="n">
+        <v>17413</v>
+      </c>
+      <c r="M227" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N227" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11118,6 +14742,22 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K228" s="5" t="n">
+        <v>3616500</v>
+      </c>
+      <c r="L228" s="5" t="n">
+        <v>18082</v>
+      </c>
+      <c r="M228" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N228" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11164,6 +14804,22 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K229" s="5" t="n">
+        <v>4435300</v>
+      </c>
+      <c r="L229" s="5" t="n">
+        <v>17191</v>
+      </c>
+      <c r="M229" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N229" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11210,6 +14866,22 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" s="5" t="n">
+        <v>4554000</v>
+      </c>
+      <c r="L230" s="5" t="n">
+        <v>17316</v>
+      </c>
+      <c r="M230" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11256,6 +14928,22 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K231" s="5" t="n">
+        <v>4554000</v>
+      </c>
+      <c r="L231" s="5" t="n">
+        <v>17316</v>
+      </c>
+      <c r="M231" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N231" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11302,6 +14990,22 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K232" s="5" t="n">
+        <v>6046200</v>
+      </c>
+      <c r="L232" s="5" t="n">
+        <v>17679</v>
+      </c>
+      <c r="M232" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11348,6 +15052,22 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K233" s="5" t="n">
+        <v>6522600</v>
+      </c>
+      <c r="L233" s="5" t="n">
+        <v>18583</v>
+      </c>
+      <c r="M233" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N233" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11394,6 +15114,22 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" s="5" t="n">
+        <v>4676300</v>
+      </c>
+      <c r="L234" s="5" t="n">
+        <v>17848</v>
+      </c>
+      <c r="M234" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N234" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11440,6 +15176,22 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>4512300</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>17223</v>
+      </c>
+      <c r="M235" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N235" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11486,6 +15238,22 @@
       </c>
       <c r="J236" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K236" s="5" t="n">
+        <v>3626600</v>
+      </c>
+      <c r="L236" s="5" t="n">
+        <v>18133</v>
+      </c>
+      <c r="M236" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N236" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11532,6 +15300,22 @@
       </c>
       <c r="J237" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K237" s="5" t="n">
+        <v>4435300</v>
+      </c>
+      <c r="L237" s="5" t="n">
+        <v>17191</v>
+      </c>
+      <c r="M237" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N237" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11578,6 +15362,22 @@
       </c>
       <c r="J238" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K238" s="5" t="n">
+        <v>4525300</v>
+      </c>
+      <c r="L238" s="5" t="n">
+        <v>17206</v>
+      </c>
+      <c r="M238" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11624,6 +15424,22 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K239" s="5" t="n">
+        <v>6058100</v>
+      </c>
+      <c r="L239" s="5" t="n">
+        <v>17714</v>
+      </c>
+      <c r="M239" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N239" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11670,6 +15486,22 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K240" s="5" t="n">
+        <v>6367800</v>
+      </c>
+      <c r="L240" s="5" t="n">
+        <v>18246</v>
+      </c>
+      <c r="M240" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N240" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11716,6 +15548,22 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K241" s="5" t="n">
+        <v>4524500</v>
+      </c>
+      <c r="L241" s="5" t="n">
+        <v>17335</v>
+      </c>
+      <c r="M241" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11762,6 +15610,22 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K242" s="5" t="n">
+        <v>4502400</v>
+      </c>
+      <c r="L242" s="5" t="n">
+        <v>17185</v>
+      </c>
+      <c r="M242" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N242" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11808,6 +15672,22 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K243" s="5" t="n">
+        <v>3569600</v>
+      </c>
+      <c r="L243" s="5" t="n">
+        <v>17848</v>
+      </c>
+      <c r="M243" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N243" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11854,6 +15734,22 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K244" s="5" t="n">
+        <v>4446200</v>
+      </c>
+      <c r="L244" s="5" t="n">
+        <v>17233</v>
+      </c>
+      <c r="M244" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N244" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11900,6 +15796,22 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" s="5" t="n">
+        <v>4464700</v>
+      </c>
+      <c r="L245" s="5" t="n">
+        <v>16976</v>
+      </c>
+      <c r="M245" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N245" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11946,6 +15858,22 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K246" s="5" t="n">
+        <v>4464700</v>
+      </c>
+      <c r="L246" s="5" t="n">
+        <v>16976</v>
+      </c>
+      <c r="M246" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N246" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -11992,6 +15920,22 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" s="5" t="n">
+        <v>5932100</v>
+      </c>
+      <c r="L247" s="5" t="n">
+        <v>17345</v>
+      </c>
+      <c r="M247" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N247" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12038,6 +15982,22 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K248" s="5" t="n">
+        <v>6461900</v>
+      </c>
+      <c r="L248" s="5" t="n">
+        <v>18410</v>
+      </c>
+      <c r="M248" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N248" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12084,6 +16044,22 @@
       </c>
       <c r="J249" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K249" s="5" t="n">
+        <v>4586200</v>
+      </c>
+      <c r="L249" s="5" t="n">
+        <v>17505</v>
+      </c>
+      <c r="M249" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N249" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12130,6 +16106,22 @@
       </c>
       <c r="J250" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>4407700</v>
+      </c>
+      <c r="L250" s="5" t="n">
+        <v>16823</v>
+      </c>
+      <c r="M250" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N250" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12176,6 +16168,22 @@
       </c>
       <c r="J251" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K251" s="5" t="n">
+        <v>3579700</v>
+      </c>
+      <c r="L251" s="5" t="n">
+        <v>17898</v>
+      </c>
+      <c r="M251" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N251" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12222,6 +16230,22 @@
       </c>
       <c r="J252" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K252" s="5" t="n">
+        <v>4365400</v>
+      </c>
+      <c r="L252" s="5" t="n">
+        <v>16920</v>
+      </c>
+      <c r="M252" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N252" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12268,6 +16292,22 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K253" s="5" t="n">
+        <v>4496900</v>
+      </c>
+      <c r="L253" s="5" t="n">
+        <v>17098</v>
+      </c>
+      <c r="M253" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N253" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12314,6 +16354,22 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K254" s="5" t="n">
+        <v>5752700</v>
+      </c>
+      <c r="L254" s="5" t="n">
+        <v>16821</v>
+      </c>
+      <c r="M254" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N254" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12360,6 +16416,22 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" s="5" t="n">
+        <v>6046200</v>
+      </c>
+      <c r="L255" s="5" t="n">
+        <v>17324</v>
+      </c>
+      <c r="M255" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N255" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12406,6 +16478,22 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K256" s="5" t="n">
+        <v>4449100</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>17046</v>
+      </c>
+      <c r="M256" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N256" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12452,6 +16540,22 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K257" s="5" t="n">
+        <v>4539200</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>17325</v>
+      </c>
+      <c r="M257" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N257" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12498,6 +16602,22 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K258" s="5" t="n">
+        <v>4328200</v>
+      </c>
+      <c r="L258" s="5" t="n">
+        <v>21641</v>
+      </c>
+      <c r="M258" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N258" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12544,6 +16664,22 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K259" s="5" t="n">
+        <v>4328200</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>16776</v>
+      </c>
+      <c r="M259" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N259" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12590,6 +16726,22 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K260" s="5" t="n">
+        <v>4389300</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>16689</v>
+      </c>
+      <c r="M260" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N260" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12636,6 +16788,22 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>4484700</v>
+      </c>
+      <c r="L261" s="5" t="n">
+        <v>17052</v>
+      </c>
+      <c r="M261" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N261" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12682,6 +16850,22 @@
       </c>
       <c r="J262" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K262" s="5" t="n">
+        <v>5837400</v>
+      </c>
+      <c r="L262" s="5" t="n">
+        <v>17068</v>
+      </c>
+      <c r="M262" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N262" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12728,6 +16912,22 @@
       </c>
       <c r="J263" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>6152000</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>17527</v>
+      </c>
+      <c r="M263" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N263" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12774,6 +16974,22 @@
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>4609700</v>
+      </c>
+      <c r="L264" s="5" t="n">
+        <v>17594</v>
+      </c>
+      <c r="M264" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N264" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12820,6 +17036,22 @@
       </c>
       <c r="J265" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>4432100</v>
+      </c>
+      <c r="L265" s="5" t="n">
+        <v>16916</v>
+      </c>
+      <c r="M265" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N265" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12866,6 +17098,22 @@
       </c>
       <c r="J266" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K266" s="5" t="n">
+        <v>3533700</v>
+      </c>
+      <c r="L266" s="5" t="n">
+        <v>17668</v>
+      </c>
+      <c r="M266" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N266" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12912,6 +17160,22 @@
       </c>
       <c r="J267" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K267" s="5" t="n">
+        <v>4295400</v>
+      </c>
+      <c r="L267" s="5" t="n">
+        <v>16649</v>
+      </c>
+      <c r="M267" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N267" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -12958,6 +17222,22 @@
       </c>
       <c r="J268" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K268" s="5" t="n">
+        <v>4326700</v>
+      </c>
+      <c r="L268" s="5" t="n">
+        <v>16451</v>
+      </c>
+      <c r="M268" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N268" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13004,6 +17284,22 @@
       </c>
       <c r="J269" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K269" s="5" t="n">
+        <v>5657000</v>
+      </c>
+      <c r="L269" s="5" t="n">
+        <v>16541</v>
+      </c>
+      <c r="M269" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N269" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13050,6 +17346,22 @@
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K270" s="5" t="n">
+        <v>5946800</v>
+      </c>
+      <c r="L270" s="5" t="n">
+        <v>17040</v>
+      </c>
+      <c r="M270" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N270" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13096,6 +17408,22 @@
       </c>
       <c r="J271" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K271" s="5" t="n">
+        <v>4374600</v>
+      </c>
+      <c r="L271" s="5" t="n">
+        <v>16761</v>
+      </c>
+      <c r="M271" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N271" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13142,6 +17470,22 @@
       </c>
       <c r="J272" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K272" s="5" t="n">
+        <v>4367200</v>
+      </c>
+      <c r="L272" s="5" t="n">
+        <v>16669</v>
+      </c>
+      <c r="M272" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N272" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13188,6 +17532,22 @@
       </c>
       <c r="J273" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K273" s="5" t="n">
+        <v>3464700</v>
+      </c>
+      <c r="L273" s="5" t="n">
+        <v>17324</v>
+      </c>
+      <c r="M273" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N273" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13234,6 +17594,22 @@
       </c>
       <c r="J274" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K274" s="5" t="n">
+        <v>4211700</v>
+      </c>
+      <c r="L274" s="5" t="n">
+        <v>16324</v>
+      </c>
+      <c r="M274" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N274" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13280,6 +17656,22 @@
       </c>
       <c r="J275" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K275" s="5" t="n">
+        <v>4314800</v>
+      </c>
+      <c r="L275" s="5" t="n">
+        <v>16406</v>
+      </c>
+      <c r="M275" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N275" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13326,6 +17718,22 @@
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" s="5" t="n">
+        <v>4408600</v>
+      </c>
+      <c r="L276" s="5" t="n">
+        <v>16763</v>
+      </c>
+      <c r="M276" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13372,6 +17780,22 @@
       </c>
       <c r="J277" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" s="5" t="n">
+        <v>5742600</v>
+      </c>
+      <c r="L277" s="5" t="n">
+        <v>16791</v>
+      </c>
+      <c r="M277" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13418,6 +17842,22 @@
       </c>
       <c r="J278" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" s="5" t="n">
+        <v>6047100</v>
+      </c>
+      <c r="L278" s="5" t="n">
+        <v>17228</v>
+      </c>
+      <c r="M278" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13464,6 +17904,22 @@
       </c>
       <c r="J279" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" s="5" t="n">
+        <v>4436200</v>
+      </c>
+      <c r="L279" s="5" t="n">
+        <v>16932</v>
+      </c>
+      <c r="M279" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13510,6 +17966,22 @@
       </c>
       <c r="J280" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" s="5" t="n">
+        <v>4345600</v>
+      </c>
+      <c r="L280" s="5" t="n">
+        <v>16586</v>
+      </c>
+      <c r="M280" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13556,6 +18028,22 @@
       </c>
       <c r="J281" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" s="5" t="n">
+        <v>3476600</v>
+      </c>
+      <c r="L281" s="5" t="n">
+        <v>17383</v>
+      </c>
+      <c r="M281" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13602,6 +18090,22 @@
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" s="5" t="n">
+        <v>4211700</v>
+      </c>
+      <c r="L282" s="5" t="n">
+        <v>16324</v>
+      </c>
+      <c r="M282" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13648,6 +18152,22 @@
       </c>
       <c r="J283" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" s="5" t="n">
+        <v>4321100</v>
+      </c>
+      <c r="L283" s="5" t="n">
+        <v>16430</v>
+      </c>
+      <c r="M283" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13694,6 +18214,22 @@
       </c>
       <c r="J284" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" s="5" t="n">
+        <v>5543000</v>
+      </c>
+      <c r="L284" s="5" t="n">
+        <v>16208</v>
+      </c>
+      <c r="M284" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13740,6 +18276,22 @@
       </c>
       <c r="J285" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K285" s="5" t="n">
+        <v>5973700</v>
+      </c>
+      <c r="L285" s="5" t="n">
+        <v>17117</v>
+      </c>
+      <c r="M285" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N285" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13786,6 +18338,22 @@
       </c>
       <c r="J286" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K286" s="5" t="n">
+        <v>4314800</v>
+      </c>
+      <c r="L286" s="5" t="n">
+        <v>16532</v>
+      </c>
+      <c r="M286" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N286" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13832,6 +18400,22 @@
       </c>
       <c r="J287" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K287" s="5" t="n">
+        <v>4464700</v>
+      </c>
+      <c r="L287" s="5" t="n">
+        <v>17041</v>
+      </c>
+      <c r="M287" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N287" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13878,6 +18462,22 @@
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K288" s="5" t="n">
+        <v>3374500</v>
+      </c>
+      <c r="L288" s="5" t="n">
+        <v>16872</v>
+      </c>
+      <c r="M288" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N288" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13924,6 +18524,22 @@
       </c>
       <c r="J289" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K289" s="5" t="n">
+        <v>4291100</v>
+      </c>
+      <c r="L289" s="5" t="n">
+        <v>16632</v>
+      </c>
+      <c r="M289" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N289" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -13970,6 +18586,22 @@
       </c>
       <c r="J290" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K290" s="5" t="n">
+        <v>4254000</v>
+      </c>
+      <c r="L290" s="5" t="n">
+        <v>16175</v>
+      </c>
+      <c r="M290" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N290" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14016,6 +18648,22 @@
       </c>
       <c r="J291" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K291" s="5" t="n">
+        <v>4254000</v>
+      </c>
+      <c r="L291" s="5" t="n">
+        <v>16175</v>
+      </c>
+      <c r="M291" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N291" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14062,6 +18710,22 @@
       </c>
       <c r="J292" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K292" s="5" t="n">
+        <v>5647800</v>
+      </c>
+      <c r="L292" s="5" t="n">
+        <v>16514</v>
+      </c>
+      <c r="M292" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N292" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14108,6 +18772,22 @@
       </c>
       <c r="J293" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K293" s="5" t="n">
+        <v>6006800</v>
+      </c>
+      <c r="L293" s="5" t="n">
+        <v>17113</v>
+      </c>
+      <c r="M293" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N293" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14154,6 +18834,22 @@
       </c>
       <c r="J294" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K294" s="5" t="n">
+        <v>4376400</v>
+      </c>
+      <c r="L294" s="5" t="n">
+        <v>16704</v>
+      </c>
+      <c r="M294" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N294" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14200,6 +18896,22 @@
       </c>
       <c r="J295" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K295" s="5" t="n">
+        <v>4169400</v>
+      </c>
+      <c r="L295" s="5" t="n">
+        <v>15914</v>
+      </c>
+      <c r="M295" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N295" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14246,6 +18958,22 @@
       </c>
       <c r="J296" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K296" s="5" t="n">
+        <v>3459200</v>
+      </c>
+      <c r="L296" s="5" t="n">
+        <v>17296</v>
+      </c>
+      <c r="M296" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N296" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14292,6 +19020,22 @@
       </c>
       <c r="J297" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K297" s="5" t="n">
+        <v>4099500</v>
+      </c>
+      <c r="L297" s="5" t="n">
+        <v>15890</v>
+      </c>
+      <c r="M297" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N297" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14338,6 +19082,22 @@
       </c>
       <c r="J298" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K298" s="5" t="n">
+        <v>4100400</v>
+      </c>
+      <c r="L298" s="5" t="n">
+        <v>15591</v>
+      </c>
+      <c r="M298" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N298" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14384,6 +19144,22 @@
       </c>
       <c r="J299" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K299" s="5" t="n">
+        <v>5410500</v>
+      </c>
+      <c r="L299" s="5" t="n">
+        <v>15820</v>
+      </c>
+      <c r="M299" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N299" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14430,6 +19206,22 @@
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" s="5" t="n">
+        <v>5766500</v>
+      </c>
+      <c r="L300" s="5" t="n">
+        <v>16523</v>
+      </c>
+      <c r="M300" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N300" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14476,6 +19268,22 @@
       </c>
       <c r="J301" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" s="5" t="n">
+        <v>6180800</v>
+      </c>
+      <c r="L301" s="5" t="n">
+        <v>27593</v>
+      </c>
+      <c r="M301" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N301" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14522,6 +19330,22 @@
       </c>
       <c r="J302" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" s="5" t="n">
+        <v>5200000</v>
+      </c>
+      <c r="L302" s="5" t="n">
+        <v>23214</v>
+      </c>
+      <c r="M302" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N302" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14568,6 +19392,22 @@
       </c>
       <c r="J303" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" s="5" t="n">
+        <v>4580000</v>
+      </c>
+      <c r="L303" s="5" t="n">
+        <v>25730</v>
+      </c>
+      <c r="M303" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N303" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14614,6 +19454,22 @@
       </c>
       <c r="J304" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" s="5" t="n">
+        <v>4650000</v>
+      </c>
+      <c r="L304" s="5" t="n">
+        <v>21136</v>
+      </c>
+      <c r="M304" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N304" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14660,6 +19516,22 @@
       </c>
       <c r="J305" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" s="5" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="L305" s="5" t="n">
+        <v>20889</v>
+      </c>
+      <c r="M305" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N305" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14706,6 +19578,22 @@
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" s="5" t="n">
+        <v>4750000</v>
+      </c>
+      <c r="L306" s="5" t="n">
+        <v>21111</v>
+      </c>
+      <c r="M306" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N306" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14752,6 +19640,22 @@
       </c>
       <c r="J307" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" s="5" t="n">
+        <v>6600000</v>
+      </c>
+      <c r="L307" s="5" t="n">
+        <v>21711</v>
+      </c>
+      <c r="M307" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N307" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14798,6 +19702,22 @@
       </c>
       <c r="J308" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" s="5" t="n">
+        <v>7250000</v>
+      </c>
+      <c r="L308" s="5" t="n">
+        <v>23163</v>
+      </c>
+      <c r="M308" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N308" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14844,6 +19764,22 @@
       </c>
       <c r="J309" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" s="5" t="n">
+        <v>6330000</v>
+      </c>
+      <c r="L309" s="5" t="n">
+        <v>28259</v>
+      </c>
+      <c r="M309" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N309" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14890,6 +19826,22 @@
       </c>
       <c r="J310" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" s="5" t="n">
+        <v>5850000</v>
+      </c>
+      <c r="L310" s="5" t="n">
+        <v>26116</v>
+      </c>
+      <c r="M310" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N310" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14936,6 +19888,22 @@
       </c>
       <c r="J311" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" s="5" t="n">
+        <v>4520000</v>
+      </c>
+      <c r="L311" s="5" t="n">
+        <v>25393</v>
+      </c>
+      <c r="M311" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N311" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -14982,6 +19950,22 @@
       </c>
       <c r="J312" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" s="5" t="n">
+        <v>4649800</v>
+      </c>
+      <c r="L312" s="5" t="n">
+        <v>21040</v>
+      </c>
+      <c r="M312" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N312" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15028,6 +20012,22 @@
       </c>
       <c r="J313" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" s="5" t="n">
+        <v>4698300</v>
+      </c>
+      <c r="L313" s="5" t="n">
+        <v>20881</v>
+      </c>
+      <c r="M313" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N313" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15074,6 +20074,22 @@
       </c>
       <c r="J314" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" s="5" t="n">
+        <v>6560000</v>
+      </c>
+      <c r="L314" s="5" t="n">
+        <v>21579</v>
+      </c>
+      <c r="M314" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N314" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -15120,13 +20136,29 @@
       </c>
       <c r="J315" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" s="5" t="n">
+        <v>7228000</v>
+      </c>
+      <c r="L315" s="5" t="n">
+        <v>23241</v>
+      </c>
+      <c r="M315" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N315" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -15324,7 +20356,7 @@
           <t>A1 | 353呎 (2房)
 $1120万
 $31,728/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -15332,7 +20364,7 @@
           <t>A2 | 342呎 (2房)
 $868万
 $25,374/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -15340,7 +20372,7 @@
           <t>A3 | 263呎 (1房)
 $653万
 $24,820/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -15348,7 +20380,7 @@
           <t>A5 | 258呎 (1房)
 $638万
 $24,728/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -15356,7 +20388,7 @@
           <t>A6 | 200呎 (开放式)
 $464万
 $23,182/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -15373,7 +20405,7 @@
           <t>B1 | 358呎 (2房)
 $1039万
 $29,017/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -15381,7 +20413,7 @@
           <t>B2 | 342呎 (2房)
 $882万
 $25,781/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K5" s="23" t="inlineStr">
@@ -15397,7 +20429,7 @@
           <t>B5 | 263呎 (1房)
 $668万
 $25,383/呎
-(26年-06月)</t>
+(26年-06月-19日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -15405,7 +20437,7 @@
           <t>B6 | 258呎 (1房)
 $655万
 $25,404/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -15413,7 +20445,7 @@
           <t>B7 | 200呎 (开放式)
 $457万
 $22,838/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="O5" s="24" t="inlineStr">
@@ -15437,7 +20469,7 @@
           <t>A1 | 349呎 (2房)
 $886万
 $25,399/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -15445,7 +20477,7 @@
           <t>A2 | 342呎 (2房)
 $798万
 $23,320/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -15453,7 +20485,7 @@
           <t>A3 | 263呎 (1房)
 $646万
 $24,556/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -15461,7 +20493,7 @@
           <t>A5 | 258呎 (1房)
 $631万
 $24,462/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -15469,7 +20501,7 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,987/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="G6" s="23" t="inlineStr">
@@ -15501,7 +20533,7 @@
           <t>B2 | 342呎 (2房)
 $803万
 $23,471/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -15509,7 +20541,7 @@
           <t>B3 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -15517,7 +20549,7 @@
           <t>B5 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -15525,7 +20557,7 @@
           <t>B6 | 258呎 (1房)
 $648万
 $25,130/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -15533,7 +20565,7 @@
           <t>B7 | 200呎 (开放式)
 $400万
 $19,982/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="O6" s="21" t="inlineStr">
@@ -15564,7 +20596,7 @@
           <t>A1 | 349呎 (2房)
 $870万
 $24,924/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -15572,7 +20604,7 @@
           <t>A2 | 342呎 (2房)
 $776万
 $22,677/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -15580,7 +20612,7 @@
           <t>A3 | 263呎 (1房)
 $584万
 $22,188/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -15588,7 +20620,7 @@
           <t>A5 | 258呎 (1房)
 $571万
 $22,130/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -15596,7 +20628,7 @@
           <t>A6 | 200呎 (开放式)
 $399万
 $19,950/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -15604,7 +20636,7 @@
           <t>A7 | 262呎 (1房)
 $603万
 $23,030/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="H7" s="24" t="inlineStr">
@@ -15620,7 +20652,7 @@
           <t>B1 | 351呎 (2房)
 $888万
 $25,301/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -15628,7 +20660,7 @@
           <t>B2 | 342呎 (2房)
 $781万
 $22,836/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -15636,7 +20668,7 @@
           <t>B3 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-04月)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -15644,7 +20676,7 @@
           <t>B5 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -15652,7 +20684,7 @@
           <t>B6 | 258呎 (1房)
 $638万
 $24,735/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -15660,7 +20692,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,964/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="O7" s="23" t="inlineStr">
@@ -15676,7 +20708,7 @@
           <t>B9 | 261呎 (1房)
 $590万
 $22,612/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -15691,7 +20723,7 @@
           <t>A1 | 349呎 (2房)
 $787万
 $22,549/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -15699,7 +20731,7 @@
           <t>A2 | 342呎 (2房)
 $756万
 $22,096/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -15707,7 +20739,7 @@
           <t>A3 | 263呎 (1房)
 $570万
 $21,667/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -15715,7 +20747,7 @@
           <t>A5 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -15723,7 +20755,7 @@
           <t>A6 | 200呎 (开放式)
 $406万
 $20,322/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -15731,7 +20763,7 @@
           <t>A7 | 262呎 (1房)
 $542万
 $20,686/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H8" s="24" t="inlineStr">
@@ -15747,7 +20779,7 @@
           <t>B1 | 351呎 (2房)
 $810万
 $23,084/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -15755,7 +20787,7 @@
           <t>B2 | 342呎 (2房)
 $761万
 $22,257/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -15763,7 +20795,7 @@
           <t>B3 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -15771,7 +20803,7 @@
           <t>B5 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -15779,7 +20811,7 @@
           <t>B6 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -15787,7 +20819,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,936/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -15795,7 +20827,7 @@
           <t>B8 | 262呎 (1房)
 $568万
 $21,673/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -15803,7 +20835,7 @@
           <t>B9 | 261呎 (1房)
 $576万
 $22,087/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -15818,7 +20850,7 @@
           <t>A1 | 349呎 (2房)
 $768万
 $22,009/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -15826,7 +20858,7 @@
           <t>A2 | 342呎 (2房)
 $703万
 $20,541/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -15834,7 +20866,7 @@
           <t>A3 | 263呎 (1房)
 $556万
 $21,142/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -15842,7 +20874,7 @@
           <t>A5 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -15850,7 +20882,7 @@
           <t>A6 | 200呎 (开放式)
 $395万
 $19,734/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -15858,7 +20890,7 @@
           <t>A7 | 262呎 (1房)
 $530万
 $20,244/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H9" s="23" t="inlineStr">
@@ -15874,7 +20906,7 @@
           <t>B1 | 351呎 (2房)
 $791万
 $22,523/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -15882,7 +20914,7 @@
           <t>B2 | 342呎 (2房)
 $715万
 $20,902/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -15890,7 +20922,7 @@
           <t>B3 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -15898,7 +20930,7 @@
           <t>B5 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -15906,7 +20938,7 @@
           <t>B6 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -15914,7 +20946,7 @@
           <t>B7 | 200呎 (开放式)
 $397万
 $19,867/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -15922,7 +20954,7 @@
           <t>B8 | 262呎 (1房)
 $572万
 $21,839/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -15930,7 +20962,7 @@
           <t>B9 | 261呎 (1房)
 $563万
 $21,562/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -15945,7 +20977,7 @@
           <t>A1 | 349呎 (2房)
 $723万
 $20,707/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -15953,7 +20985,7 @@
           <t>A2 | 342呎 (2房)
 $702万
 $20,520/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -15961,7 +20993,7 @@
           <t>A3 | 263呎 (1房)
 $542万
 $20,617/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -15969,7 +21001,7 @@
           <t>A5 | 258呎 (1房)
 $544万
 $21,081/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -15977,7 +21009,7 @@
           <t>A6 | 200呎 (开放式)
 $402万
 $20,088/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -15985,7 +21017,7 @@
           <t>A7 | 262呎 (1房)
 $510万
 $19,469/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -15993,7 +21025,7 @@
           <t>A8 | 262呎 (1房)
 $640万
 $24,425/呎
-(26年-06月)</t>
+(26年-06月-29日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -16001,7 +21033,7 @@
           <t>B1 | 351呎 (2房)
 $773万
 $22,025/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -16009,7 +21041,7 @@
           <t>B2 | 342呎 (2房)
 $700万
 $20,458/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -16017,7 +21049,7 @@
           <t>B3 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -16025,7 +21057,7 @@
           <t>B5 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -16033,7 +21065,7 @@
           <t>B6 | 258呎 (1房)
 $532万
 $20,632/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -16041,7 +21073,7 @@
           <t>B7 | 200呎 (开放式)
 $396万
 $19,816/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
@@ -16049,7 +21081,7 @@
           <t>B8 | 262呎 (1房)
 $552万
 $21,071/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr">
@@ -16057,7 +21089,7 @@
           <t>B9 | 261呎 (1房)
 $561万
 $21,494/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -16072,7 +21104,7 @@
           <t>A1 | 349呎 (2房)
 $709万
 $20,306/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -16080,7 +21112,7 @@
           <t>A2 | 342呎 (2房)
 $674万
 $19,710/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -16088,7 +21120,7 @@
           <t>A3 | 263呎 (1房)
 $537万
 $20,402/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -16096,7 +21128,7 @@
           <t>A5 | 258呎 (1房)
 $521万
 $20,206/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -16104,7 +21136,7 @@
           <t>A6 | 200呎 (开放式)
 $392万
 $19,614/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -16112,7 +21144,7 @@
           <t>A7 | 262呎 (1房)
 $497万
 $18,958/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -16120,7 +21152,7 @@
           <t>A8 | 262呎 (1房)
 $568万
 $21,677/呎
-(25年-03月)</t>
+(25年-03月-07日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -16128,7 +21160,7 @@
           <t>B1 | 351呎 (2房)
 $729万
 $20,759/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -16136,7 +21168,7 @@
           <t>B2 | 342呎 (2房)
 $686万
 $20,068/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -16144,7 +21176,7 @@
           <t>B3 | 263呎 (1房)
 $527万
 $20,054/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -16152,7 +21184,7 @@
           <t>B5 | 263呎 (1房)
 $539万
 $20,490/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -16160,7 +21192,7 @@
           <t>B6 | 258呎 (1房)
 $511万
 $19,798/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -16168,7 +21200,7 @@
           <t>B7 | 200呎 (开放式)
 $395万
 $19,743/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
@@ -16176,7 +21208,7 @@
           <t>B8 | 262呎 (1房)
 $528万
 $20,159/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
@@ -16184,7 +21216,7 @@
           <t>B9 | 261呎 (1房)
 $529万
 $20,264/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -16199,7 +21231,7 @@
           <t>A1 | 349呎 (2房)
 $697万
 $19,960/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -16207,7 +21239,7 @@
           <t>A2 | 342呎 (2房)
 $663万
 $19,376/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -16215,7 +21247,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,358/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -16223,7 +21255,7 @@
           <t>A5 | 258呎 (1房)
 $512万
 $19,838/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -16231,7 +21263,7 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,989/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -16239,7 +21271,7 @@
           <t>A7 | 262呎 (1房)
 $504万
 $19,253/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -16247,7 +21279,7 @@
           <t>A8 | 262呎 (1房)
 $541万
 $20,637/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -16255,7 +21287,7 @@
           <t>B1 | 351呎 (2房)
 $716万
 $20,400/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -16263,7 +21295,7 @@
           <t>B2 | 342呎 (2房)
 $675万
 $19,734/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -16271,7 +21303,7 @@
           <t>B3 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -16279,7 +21311,7 @@
           <t>B5 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -16287,7 +21319,7 @@
           <t>B6 | 258呎 (1房)
 $501万
 $19,416/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -16295,7 +21327,7 @@
           <t>B7 | 200呎 (开放式)
 $390万
 $19,513/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -16303,7 +21335,7 @@
           <t>B8 | 262呎 (1房)
 $507万
 $19,362/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr">
@@ -16311,7 +21343,7 @@
           <t>B9 | 261呎 (1房)
 $518万
 $19,863/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -16326,7 +21358,7 @@
           <t>A1 | 349呎 (2房)
 $700万
 $20,044/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -16334,7 +21366,7 @@
           <t>A2 | 342呎 (2房)
 $651万
 $19,027/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -16342,7 +21374,7 @@
           <t>A3 | 263呎 (1房)
 $500万
 $18,998/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -16350,7 +21382,7 @@
           <t>A5 | 258呎 (1房)
 $493万
 $19,091/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -16358,7 +21390,7 @@
           <t>A6 | 200呎 (开放式)
 $390万
 $19,504/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -16366,7 +21398,7 @@
           <t>A7 | 262呎 (1房)
 $499万
 $19,032/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -16374,7 +21406,7 @@
           <t>A8 | 262呎 (1房)
 $553万
 $21,114/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -16382,7 +21414,7 @@
           <t>B1 | 351呎 (2房)
 $703万
 $20,041/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -16390,7 +21422,7 @@
           <t>B2 | 342呎 (2房)
 $678万
 $19,822/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -16398,7 +21430,7 @@
           <t>B3 | 263呎 (1房)
 $524万
 $19,943/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -16406,7 +21438,7 @@
           <t>B5 | 263呎 (1房)
 $519万
 $19,733/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -16414,7 +21446,7 @@
           <t>B6 | 258呎 (1房)
 $503万
 $19,507/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -16422,7 +21454,7 @@
           <t>B7 | 200呎 (开放式)
 $389万
 $19,467/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -16430,7 +21462,7 @@
           <t>B8 | 262呎 (1房)
 $498万
 $19,018/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr">
@@ -16438,7 +21470,7 @@
           <t>B9 | 261呎 (1房)
 $509万
 $19,517/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -16453,7 +21485,7 @@
           <t>A1 | 349呎 (2房)
 $675万
 $19,330/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -16461,7 +21493,7 @@
           <t>A2 | 342呎 (2房)
 $656万
 $19,171/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -16469,7 +21501,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,343/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -16477,7 +21509,7 @@
           <t>A5 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -16485,7 +21517,7 @@
           <t>A6 | 200呎 (开放式)
 $385万
 $19,274/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -16493,7 +21525,7 @@
           <t>A7 | 262呎 (1房)
 $493万
 $18,814/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -16501,7 +21533,7 @@
           <t>A8 | 262呎 (1房)
 $524万
 $19,991/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -16509,7 +21541,7 @@
           <t>B1 | 351呎 (2房)
 $693万
 $19,742/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -16517,7 +21549,7 @@
           <t>B2 | 342呎 (2房)
 $661万
 $19,331/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -16525,7 +21557,7 @@
           <t>B3 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -16533,7 +21565,7 @@
           <t>B5 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -16541,7 +21573,7 @@
           <t>B6 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -16549,7 +21581,7 @@
           <t>B7 | 200呎 (开放式)
 $385万
 $19,237/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
@@ -16557,7 +21589,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,730/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr">
@@ -16565,7 +21597,7 @@
           <t>B9 | 261呎 (1房)
 $513万
 $19,650/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -16580,7 +21612,7 @@
           <t>A1 | 349呎 (2房)
 $681万
 $19,516/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -16588,7 +21620,7 @@
           <t>A2 | 342呎 (2房)
 $655万
 $19,147/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -16596,7 +21628,7 @@
           <t>A3 | 263呎 (1房)
 $503万
 $19,108/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -16604,7 +21636,7 @@
           <t>A5 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -16612,7 +21644,7 @@
           <t>A6 | 200呎 (开放式)
 $393万
 $19,646/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -16620,7 +21652,7 @@
           <t>A7 | 262呎 (1房)
 $473万
 $18,052/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -16628,7 +21660,7 @@
           <t>A8 | 262呎 (1房)
 $518万
 $19,758/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -16636,7 +21668,7 @@
           <t>B1 | 351呎 (2房)
 $685万
 $19,503/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -16644,7 +21676,7 @@
           <t>B2 | 342呎 (2房)
 $646万
 $18,903/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -16652,7 +21684,7 @@
           <t>B3 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -16660,7 +21692,7 @@
           <t>B5 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -16668,7 +21700,7 @@
           <t>B6 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -16676,7 +21708,7 @@
           <t>B7 | 200呎 (开放式)
 $380万
 $19,007/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -16684,7 +21716,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,502/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr">
@@ -16692,7 +21724,7 @@
           <t>B9 | 261呎 (1房)
 $496万
 $19,003/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -16707,7 +21739,7 @@
           <t>A1 | 349呎 (2房)
 $661万
 $18,930/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -16715,7 +21747,7 @@
           <t>A2 | 342呎 (2房)
 $628万
 $18,376/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -16723,7 +21755,7 @@
           <t>A3 | 263呎 (1房)
 $493万
 $18,732/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -16731,7 +21763,7 @@
           <t>A5 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -16739,7 +21771,7 @@
           <t>A6 | 200呎 (开放式)
 $381万
 $19,053/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -16747,7 +21779,7 @@
           <t>A7 | 262呎 (1房)
 $469万
 $17,891/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -16755,7 +21787,7 @@
           <t>A8 | 262呎 (1房)
 $502万
 $19,165/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -16763,7 +21795,7 @@
           <t>B1 | 351呎 (2房)
 $678万
 $19,323/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -16771,7 +21803,7 @@
           <t>B2 | 342呎 (2房)
 $648万
 $18,940/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -16779,7 +21811,7 @@
           <t>B3 | 263呎 (1房)
 $501万
 $19,032/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -16787,7 +21819,7 @@
           <t>B5 | 263呎 (1房)
 $490万
 $18,627/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -16795,7 +21827,7 @@
           <t>B6 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -16803,7 +21835,7 @@
           <t>B7 | 200呎 (开放式)
 $381万
 $19,058/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -16811,7 +21843,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,728/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr">
@@ -16819,7 +21851,7 @@
           <t>B9 | 261呎 (1房)
 $491万
 $18,830/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -16834,7 +21866,7 @@
           <t>A1 | 349呎 (2房)
 $651万
 $18,642/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -16842,7 +21874,7 @@
           <t>A2 | 342呎 (2房)
 $619万
 $18,099/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -16850,7 +21882,7 @@
           <t>A3 | 263呎 (1房)
 $475万
 $18,046/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -16858,7 +21890,7 @@
           <t>A5 | 258呎 (1房)
 $479万
 $18,563/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -16866,7 +21898,7 @@
           <t>A6 | 200呎 (开放式)
 $376万
 $18,823/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -16874,7 +21906,7 @@
           <t>A7 | 262呎 (1房)
 $463万
 $17,676/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -16882,7 +21914,7 @@
           <t>A8 | 262呎 (1房)
 $495万
 $18,881/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -16890,7 +21922,7 @@
           <t>B1 | 351呎 (2房)
 $670万
 $19,084/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -16898,7 +21930,7 @@
           <t>B2 | 342呎 (2房)
 $647万
 $18,915/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -16906,7 +21938,7 @@
           <t>B3 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -16914,7 +21946,7 @@
           <t>B5 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -16922,7 +21954,7 @@
           <t>B6 | 258呎 (1房)
 $469万
 $18,168/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -16930,7 +21962,7 @@
           <t>B7 | 200呎 (开放式)
 $369万
 $18,428/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
@@ -16938,7 +21970,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,495/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
@@ -16946,7 +21978,7 @@
           <t>B9 | 261呎 (1房)
 $485万
 $18,601/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -16961,7 +21993,7 @@
           <t>A1 | 349呎 (2房)
 $641万
 $18,358/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -16969,7 +22001,7 @@
           <t>A2 | 342呎 (2房)
 $609万
 $17,819/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -16977,7 +22009,7 @@
           <t>A3 | 263呎 (1房)
 $466万
 $17,704/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -16985,7 +22017,7 @@
           <t>A5 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -16993,7 +22025,7 @@
           <t>A6 | 200呎 (开放式)
 $380万
 $18,997/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -17001,7 +22033,7 @@
           <t>A7 | 262呎 (1房)
 $458万
 $17,462/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -17009,7 +22041,7 @@
           <t>A8 | 262呎 (1房)
 $486万
 $18,537/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -17017,7 +22049,7 @@
           <t>B1 | 351呎 (2房)
 $661万
 $18,846/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -17025,7 +22057,7 @@
           <t>B2 | 342呎 (2房)
 $639万
 $18,687/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -17033,7 +22065,7 @@
           <t>B3 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -17041,7 +22073,7 @@
           <t>B5 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -17049,7 +22081,7 @@
           <t>B6 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -17057,7 +22089,7 @@
           <t>B7 | 200呎 (开放式)
 $366万
 $18,280/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -17065,7 +22097,7 @@
           <t>B8 | 262呎 (1房)
 $468万
 $17,873/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr">
@@ -17073,7 +22105,7 @@
           <t>B9 | 261呎 (1房)
 $488万
 $18,710/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -17088,7 +22120,7 @@
           <t>A1 | 349呎 (2房)
 $629万
 $18,012/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -17096,7 +22128,7 @@
           <t>A2 | 342呎 (2房)
 $598万
 $17,485/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -17104,7 +22136,7 @@
           <t>A3 | 263呎 (1房)
 $457万
 $17,364/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -17112,7 +22144,7 @@
           <t>A5 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -17120,7 +22152,7 @@
           <t>A6 | 200呎 (开放式)
 $364万
 $18,188/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -17128,7 +22160,7 @@
           <t>A7 | 262呎 (1房)
 $452万
 $17,248/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -17136,7 +22168,7 @@
           <t>A8 | 262呎 (1房)
 $482万
 $18,390/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -17144,7 +22176,7 @@
           <t>B1 | 351呎 (2房)
 $651万
 $18,544/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -17152,7 +22184,7 @@
           <t>B2 | 342呎 (2房)
 $616万
 $18,013/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -17160,7 +22192,7 @@
           <t>B3 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -17168,7 +22200,7 @@
           <t>B5 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -17176,7 +22208,7 @@
           <t>B6 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -17184,7 +22216,7 @@
           <t>B7 | 200呎 (开放式)
 $371万
 $18,536/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -17192,7 +22224,7 @@
           <t>B8 | 262呎 (1房)
 $462万
 $17,641/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr">
@@ -17200,7 +22232,7 @@
           <t>B9 | 261呎 (1房)
 $481万
 $18,418/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -17215,7 +22247,7 @@
           <t>A1 | 349呎 (2房)
 $637万
 $18,246/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -17223,7 +22255,7 @@
           <t>A2 | 342呎 (2房)
 $606万
 $17,714/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -17231,7 +22263,7 @@
           <t>A3 | 263呎 (1房)
 $453万
 $17,206/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -17239,7 +22271,7 @@
           <t>A5 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -17247,7 +22279,7 @@
           <t>A6 | 200呎 (开放式)
 $363万
 $18,133/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -17255,7 +22287,7 @@
           <t>A7 | 262呎 (1房)
 $451万
 $17,223/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -17263,7 +22295,7 @@
           <t>A8 | 262呎 (1房)
 $468万
 $17,848/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -17271,7 +22303,7 @@
           <t>B1 | 351呎 (2房)
 $652万
 $18,583/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -17279,7 +22311,7 @@
           <t>B2 | 342呎 (2房)
 $605万
 $17,679/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -17287,7 +22319,7 @@
           <t>B3 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -17295,7 +22327,7 @@
           <t>B5 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -17303,7 +22335,7 @@
           <t>B6 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -17311,7 +22343,7 @@
           <t>B7 | 200呎 (开放式)
 $362万
 $18,082/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -17319,7 +22351,7 @@
           <t>B8 | 262呎 (1房)
 $456万
 $17,413/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr">
@@ -17327,7 +22359,7 @@
           <t>B9 | 261呎 (1房)
 $461万
 $17,681/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -17342,7 +22374,7 @@
           <t>A1 | 349呎 (2房)
 $605万
 $17,324/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -17350,7 +22382,7 @@
           <t>A2 | 342呎 (2房)
 $575万
 $16,821/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -17358,7 +22390,7 @@
           <t>A3 | 263呎 (1房)
 $450万
 $17,098/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -17366,7 +22398,7 @@
           <t>A5 | 258呎 (1房)
 $437万
 $16,920/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -17374,7 +22406,7 @@
           <t>A6 | 200呎 (开放式)
 $358万
 $17,898/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -17382,7 +22414,7 @@
           <t>A7 | 262呎 (1房)
 $441万
 $16,823/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -17390,7 +22422,7 @@
           <t>A8 | 262呎 (1房)
 $459万
 $17,505/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -17398,7 +22430,7 @@
           <t>B1 | 351呎 (2房)
 $646万
 $18,410/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -17406,7 +22438,7 @@
           <t>B2 | 342呎 (2房)
 $593万
 $17,345/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -17414,7 +22446,7 @@
           <t>B3 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -17422,7 +22454,7 @@
           <t>B5 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -17430,7 +22462,7 @@
           <t>B6 | 258呎 (1房)
 $445万
 $17,233/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -17438,7 +22470,7 @@
           <t>B7 | 200呎 (开放式)
 $357万
 $17,848/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
@@ -17446,7 +22478,7 @@
           <t>B8 | 262呎 (1房)
 $450万
 $17,185/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr">
@@ -17454,7 +22486,7 @@
           <t>B9 | 261呎 (1房)
 $452万
 $17,335/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -17469,7 +22501,7 @@
           <t>A1 | 349呎 (2房)
 $595万
 $17,040/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -17477,7 +22509,7 @@
           <t>A2 | 342呎 (2房)
 $566万
 $16,541/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -17485,7 +22517,7 @@
           <t>A3 | 263呎 (1房)
 $433万
 $16,451/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -17493,7 +22525,7 @@
           <t>A5 | 258呎 (1房)
 $430万
 $16,649/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -17501,7 +22533,7 @@
           <t>A6 | 200呎 (开放式)
 $353万
 $17,668/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -17509,7 +22541,7 @@
           <t>A7 | 262呎 (1房)
 $443万
 $16,916/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -17517,7 +22549,7 @@
           <t>A8 | 262呎 (1房)
 $461万
 $17,594/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -17525,7 +22557,7 @@
           <t>B1 | 351呎 (2房)
 $615万
 $17,527/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -17533,7 +22565,7 @@
           <t>B2 | 342呎 (2房)
 $584万
 $17,068/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -17541,7 +22573,7 @@
           <t>B3 | 263呎 (1房)
 $448万
 $17,052/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -17549,7 +22581,7 @@
           <t>B5 | 263呎 (1房)
 $439万
 $16,689/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -17557,7 +22589,7 @@
           <t>B6 | 258呎 (1房)
 $433万
 $16,776/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -17565,7 +22597,7 @@
           <t>B7 | 200呎 (开放式)
 $433万
 $21,641/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr">
@@ -17573,7 +22605,7 @@
           <t>B8 | 262呎 (1房)
 $454万
 $17,325/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="P22" s="20" t="inlineStr">
@@ -17581,7 +22613,7 @@
           <t>B9 | 261呎 (1房)
 $445万
 $17,046/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -17596,7 +22628,7 @@
           <t>A1 | 349呎 (2房)
 $597万
 $17,117/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -17604,7 +22636,7 @@
           <t>A2 | 342呎 (2房)
 $554万
 $16,208/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -17612,7 +22644,7 @@
           <t>A3 | 263呎 (1房)
 $432万
 $16,430/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -17620,7 +22652,7 @@
           <t>A5 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -17628,7 +22660,7 @@
           <t>A6 | 200呎 (开放式)
 $348万
 $17,383/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -17636,7 +22668,7 @@
           <t>A7 | 262呎 (1房)
 $435万
 $16,586/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -17644,7 +22676,7 @@
           <t>A8 | 262呎 (1房)
 $444万
 $16,932/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -17652,7 +22684,7 @@
           <t>B1 | 351呎 (2房)
 $605万
 $17,228/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -17660,7 +22692,7 @@
           <t>B2 | 342呎 (2房)
 $574万
 $16,791/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -17668,7 +22700,7 @@
           <t>B3 | 263呎 (1房)
 $441万
 $16,763/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -17676,7 +22708,7 @@
           <t>B5 | 263呎 (1房)
 $431万
 $16,406/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -17684,7 +22716,7 @@
           <t>B6 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -17692,7 +22724,7 @@
           <t>B7 | 200呎 (开放式)
 $346万
 $17,324/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -17700,7 +22732,7 @@
           <t>B8 | 262呎 (1房)
 $437万
 $16,669/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
@@ -17708,7 +22740,7 @@
           <t>B9 | 261呎 (1房)
 $437万
 $16,761/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -17723,7 +22755,7 @@
           <t>A1 | 349呎 (2房)
 $577万
 $16,523/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -17731,7 +22763,7 @@
           <t>A2 | 342呎 (2房)
 $541万
 $15,820/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -17739,7 +22771,7 @@
           <t>A3 | 263呎 (1房)
 $410万
 $15,591/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -17747,7 +22779,7 @@
           <t>A5 | 258呎 (1房)
 $410万
 $15,890/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -17755,7 +22787,7 @@
           <t>A6 | 200呎 (开放式)
 $346万
 $17,296/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -17763,7 +22795,7 @@
           <t>A7 | 262呎 (1房)
 $417万
 $15,914/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -17771,7 +22803,7 @@
           <t>A8 | 262呎 (1房)
 $438万
 $16,704/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -17779,7 +22811,7 @@
           <t>B1 | 351呎 (2房)
 $601万
 $17,113/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -17787,7 +22819,7 @@
           <t>B2 | 342呎 (2房)
 $565万
 $16,514/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -17795,7 +22827,7 @@
           <t>B3 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -17803,7 +22835,7 @@
           <t>B5 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月)</t>
+(25年-03月-16日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -17811,7 +22843,7 @@
           <t>B6 | 258呎 (1房)
 $429万
 $16,632/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -17819,7 +22851,7 @@
           <t>B7 | 200呎 (开放式)
 $337万
 $16,872/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -17827,7 +22859,7 @@
           <t>B8 | 262呎 (1房)
 $446万
 $17,041/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr">
@@ -17835,7 +22867,7 @@
           <t>B9 | 261呎 (1房)
 $431万
 $16,532/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -17850,7 +22882,7 @@
           <t>A1 | 311呎 (2房)
 $723万
 $23,241/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -17858,7 +22890,7 @@
           <t>A2 | 304呎 (2房)
 $656万
 $21,579/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -17866,7 +22898,7 @@
           <t>A3 | 225呎 (1房)
 $470万
 $20,881/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -17874,7 +22906,7 @@
           <t>A5 | 221呎 (1房)
 $465万
 $21,040/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -17882,7 +22914,7 @@
           <t>A6 | 178呎 (开放式)
 $452万
 $25,393/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -17890,7 +22922,7 @@
           <t>A7 | 224呎 (1房)
 $585万
 $26,116/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -17898,7 +22930,7 @@
           <t>A8 | 224呎 (1房)
 $633万
 $28,259/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -17906,7 +22938,7 @@
           <t>B1 | 313呎 (2房)
 $725万
 $23,163/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -17914,7 +22946,7 @@
           <t>B2 | 304呎 (2房)
 $660万
 $21,711/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -17922,7 +22954,7 @@
           <t>B3 | 225呎 (1房)
 $475万
 $21,111/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -17930,7 +22962,7 @@
           <t>B5 | 225呎 (1房)
 $470万
 $20,889/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -17938,7 +22970,7 @@
           <t>B6 | 220呎 (1房)
 $465万
 $21,136/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -17946,7 +22978,7 @@
           <t>B7 | 178呎 (开放式)
 $458万
 $25,730/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr">
@@ -17954,7 +22986,7 @@
           <t>B8 | 224呎 (1房)
 $520万
 $23,214/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr">
@@ -17962,7 +22994,7 @@
           <t>B9 | 224呎 (1房)
 $618万
 $27,593/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -667,7 +667,7 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -792,18 +792,18 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>5996560</v>
+        <v>6387640</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>22888</v>
+        <v>24380</v>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -1040,18 +1040,18 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>6267040</v>
+        <v>6675760</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>23829</v>
+        <v>25383</v>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1226,18 +1226,18 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5796000</v>
+        <v>6174000</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>22122</v>
+        <v>23565</v>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1598,18 +1598,18 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>6215520</v>
+        <v>6620880</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>23814</v>
+        <v>25367</v>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -1660,18 +1660,18 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>5933080</v>
+        <v>6320020</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>22645</v>
+        <v>24122</v>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2032,18 +2032,18 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>8499880</v>
+        <v>9054220</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>24216</v>
+        <v>25795</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2094,18 +2094,18 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>6326840</v>
+        <v>6739460</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>24148</v>
+        <v>25723</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2156,18 +2156,18 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>5733440</v>
+        <v>6107360</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>21883</v>
+        <v>23311</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2590,18 +2590,18 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>5834640</v>
+        <v>6215160</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>22270</v>
+        <v>23722</v>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3024,18 +3024,18 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>6253240</v>
+        <v>6661060</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>23867</v>
+        <v>25424</v>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -3954,18 +3954,18 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>6192520</v>
+        <v>6596380</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>23636</v>
+        <v>25177</v>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -4884,18 +4884,18 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>2%</t>
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>6101440</v>
+        <v>6499360</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>23288</v>
+        <v>24807</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>120天現金付款計劃</t>
+          <t>90天現金付款計劃</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -122,18 +122,18 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
       <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -275,16 +275,16 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -776,7 +776,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H4" s="5" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1210,7 +1210,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>暂停销售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
@@ -2016,34 +2016,34 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>9239000</v>
+        <v>9054200</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>26322</v>
+        <v>25795</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>9054220</v>
+        <v>9054200</v>
       </c>
       <c r="L23" s="5" t="n">
         <v>25795</v>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -4868,34 +4868,34 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
-        <v>6632000</v>
+        <v>6499300</v>
       </c>
       <c r="I69" s="5" t="n">
-        <v>25313</v>
+        <v>24806</v>
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K69" s="5" t="n">
-        <v>6499360</v>
+        <v>6499300</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>24807</v>
+        <v>24806</v>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N69" s="3" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -20239,22 +20239,22 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>303</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F3" s="18" t="inlineStr">
@@ -20396,7 +20396,7 @@
           <t>A7 | 262呎 (1房)
 $630万
 $24,046/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr"/>
@@ -20416,7 +20416,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="K5" s="23" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>B3 | 263呎 (1房)
 $681万
@@ -20429,7 +20429,7 @@
           <t>B5 | 263呎 (1房)
 $668万
 $25,383/呎
-(26年-06月-19日)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -20445,15 +20445,15 @@
           <t>B7 | 200呎 (开放式)
 $457万
 $22,838/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="O5" s="24" t="inlineStr">
+(26年-07月-19日)</t>
+        </is>
+      </c>
+      <c r="O5" s="21" t="inlineStr">
         <is>
           <t>B8 | 262呎 (1房)
 $652万
 $24,878/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="P5" s="22" t="inlineStr"/>
@@ -20504,7 +20504,7 @@
 (25年-04月-14日)</t>
         </is>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="21" t="inlineStr">
         <is>
           <t>A7 | 262呎 (1房)
 $623万
@@ -20512,7 +20512,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="H6" s="24" t="inlineStr">
+      <c r="H6" s="23" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
 $688万
@@ -20520,12 +20520,12 @@
 (已定价未售)</t>
         </is>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>B1 | 351呎 (2房)
-$924万
-$26,322/呎
-(在售)</t>
+$905万
+$25,795/呎
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -20568,7 +20568,7 @@
 (25年-04月-27日)</t>
         </is>
       </c>
-      <c r="O6" s="21" t="inlineStr">
+      <c r="O6" s="24" t="inlineStr">
         <is>
           <t>B8 | 262呎 (1房)
 $645万
@@ -20581,7 +20581,7 @@
           <t>B9 | 261呎 (1房)
 $676万
 $25,885/呎
-(暂停销售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -20639,12 +20639,12 @@
 (26年-07月-05日)</t>
         </is>
       </c>
-      <c r="H7" s="24" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
 $680万
 $25,943/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I7" s="20" t="inlineStr">
@@ -20695,7 +20695,7 @@
 (25年-05月-07日)</t>
         </is>
       </c>
-      <c r="O7" s="23" t="inlineStr">
+      <c r="O7" s="21" t="inlineStr">
         <is>
           <t>B8 | 262呎 (1房)
 $634万
@@ -20766,12 +20766,12 @@
 (25年-03月-23日)</t>
         </is>
       </c>
-      <c r="H8" s="24" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
 $673万
 $25,691/呎
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="I8" s="20" t="inlineStr">
@@ -20893,12 +20893,12 @@
 (25年-03月-24日)</t>
         </is>
       </c>
-      <c r="H9" s="23" t="inlineStr">
+      <c r="H9" s="20" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
-$663万
-$25,313/呎
-(在售)</t>
+$650万
+$24,806/呎
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -21025,7 +21025,7 @@
           <t>A8 | 262呎 (1房)
 $640万
 $24,425/呎
-(26年-06月-29日)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -2140,34 +2140,34 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
-        <v>6232000</v>
+        <v>6107300</v>
       </c>
       <c r="I25" s="5" t="n">
-        <v>23786</v>
+        <v>23310</v>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>6107360</v>
+        <v>6107300</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>23311</v>
+        <v>23310</v>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20356,7 +20356,7 @@
           <t>A1 | 353呎 (2房)
 $1120万
 $31,728/呎
-(26年-04月-28日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -20364,7 +20364,7 @@
           <t>A2 | 342呎 (2房)
 $868万
 $25,374/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -20372,7 +20372,7 @@
           <t>A3 | 263呎 (1房)
 $653万
 $24,820/呎
-(26年-05月-13日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -20380,7 +20380,7 @@
           <t>A5 | 258呎 (1房)
 $638万
 $24,728/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -20388,7 +20388,7 @@
           <t>A6 | 200呎 (开放式)
 $464万
 $23,182/呎
-(26年-06月-25日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -20405,7 +20405,7 @@
           <t>B1 | 358呎 (2房)
 $1039万
 $29,017/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -20413,7 +20413,7 @@
           <t>B2 | 342呎 (2房)
 $882万
 $25,781/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -20429,7 +20429,7 @@
           <t>B5 | 263呎 (1房)
 $668万
 $25,383/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -20437,7 +20437,7 @@
           <t>B6 | 258呎 (1房)
 $655万
 $25,404/呎
-(26年-07月-08日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -20445,7 +20445,7 @@
           <t>B7 | 200呎 (开放式)
 $457万
 $22,838/呎
-(26年-07月-19日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -20469,7 +20469,7 @@
           <t>A1 | 349呎 (2房)
 $886万
 $25,399/呎
-(26年-05月-05日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -20477,7 +20477,7 @@
           <t>A2 | 342呎 (2房)
 $798万
 $23,320/呎
-(25年-11月-05日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -20485,7 +20485,7 @@
           <t>A3 | 263呎 (1房)
 $646万
 $24,556/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -20493,7 +20493,7 @@
           <t>A5 | 258呎 (1房)
 $631万
 $24,462/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -20501,15 +20501,15 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,987/呎
-(25年-04月-14日)</t>
-        </is>
-      </c>
-      <c r="G6" s="21" t="inlineStr">
+(25年-04月)</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
         <is>
           <t>A7 | 262呎 (1房)
-$623万
-$23,786/呎
-(在售)</t>
+$611万
+$23,310/呎
+(26年-07月)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -20525,7 +20525,7 @@
           <t>B1 | 351呎 (2房)
 $905万
 $25,795/呎
-(26年-07月-17日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -20533,7 +20533,7 @@
           <t>B2 | 342呎 (2房)
 $803万
 $23,471/呎
-(25年-11月-19日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -20541,7 +20541,7 @@
           <t>B3 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-05月-03日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -20549,7 +20549,7 @@
           <t>B5 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-07月-06日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -20557,7 +20557,7 @@
           <t>B6 | 258呎 (1房)
 $648万
 $25,130/呎
-(26年-06月-01日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -20565,7 +20565,7 @@
           <t>B7 | 200呎 (开放式)
 $400万
 $19,982/呎
-(25年-04月-27日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -20596,7 +20596,7 @@
           <t>A1 | 349呎 (2房)
 $870万
 $24,924/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -20604,7 +20604,7 @@
           <t>A2 | 342呎 (2房)
 $776万
 $22,677/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -20612,7 +20612,7 @@
           <t>A3 | 263呎 (1房)
 $584万
 $22,188/呎
-(25年-05月-11日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -20620,7 +20620,7 @@
           <t>A5 | 258呎 (1房)
 $571万
 $22,130/呎
-(25年-11月-06日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -20628,7 +20628,7 @@
           <t>A6 | 200呎 (开放式)
 $399万
 $19,950/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -20636,7 +20636,7 @@
           <t>A7 | 262呎 (1房)
 $603万
 $23,030/呎
-(26年-07月-05日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -20652,7 +20652,7 @@
           <t>B1 | 351呎 (2房)
 $888万
 $25,301/呎
-(26年-05月-11日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -20660,7 +20660,7 @@
           <t>B2 | 342呎 (2房)
 $781万
 $22,836/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -20668,7 +20668,7 @@
           <t>B3 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-04月-10日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -20676,7 +20676,7 @@
           <t>B5 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -20684,7 +20684,7 @@
           <t>B6 | 258呎 (1房)
 $638万
 $24,735/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -20692,7 +20692,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,964/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -20708,7 +20708,7 @@
           <t>B9 | 261呎 (1房)
 $590万
 $22,612/呎
-(25年-07月-22日)</t>
+(25年-07月)</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20723,7 @@
           <t>A1 | 349呎 (2房)
 $787万
 $22,549/呎
-(25年-10月-27日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -20731,7 +20731,7 @@
           <t>A2 | 342呎 (2房)
 $756万
 $22,096/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -20739,7 +20739,7 @@
           <t>A3 | 263呎 (1房)
 $570万
 $21,667/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -20747,7 +20747,7 @@
           <t>A5 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -20755,7 +20755,7 @@
           <t>A6 | 200呎 (开放式)
 $406万
 $20,322/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -20763,7 +20763,7 @@
           <t>A7 | 262呎 (1房)
 $542万
 $20,686/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -20779,7 +20779,7 @@
           <t>B1 | 351呎 (2房)
 $810万
 $23,084/呎
-(25年-08月-26日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -20787,7 +20787,7 @@
           <t>B2 | 342呎 (2房)
 $761万
 $22,257/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -20795,7 +20795,7 @@
           <t>B3 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月-26日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -20803,7 +20803,7 @@
           <t>B5 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -20811,7 +20811,7 @@
           <t>B6 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-10月-16日)</t>
+(25年-10月)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -20819,7 +20819,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,936/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -20827,7 +20827,7 @@
           <t>B8 | 262呎 (1房)
 $568万
 $21,673/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -20835,7 +20835,7 @@
           <t>B9 | 261呎 (1房)
 $576万
 $22,087/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20850,7 @@
           <t>A1 | 349呎 (2房)
 $768万
 $22,009/呎
-(25年-11月-02日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -20858,7 +20858,7 @@
           <t>A2 | 342呎 (2房)
 $703万
 $20,541/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -20866,7 +20866,7 @@
           <t>A3 | 263呎 (1房)
 $556万
 $21,142/呎
-(25年-04月-09日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -20874,7 +20874,7 @@
           <t>A5 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -20882,7 +20882,7 @@
           <t>A6 | 200呎 (开放式)
 $395万
 $19,734/呎
-(25年-04月-06日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -20890,7 +20890,7 @@
           <t>A7 | 262呎 (1房)
 $530万
 $20,244/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -20898,7 +20898,7 @@
           <t>A8 | 262呎 (1房)
 $650万
 $24,806/呎
-(26年-07月-13日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -20906,7 +20906,7 @@
           <t>B1 | 351呎 (2房)
 $791万
 $22,523/呎
-(25年-06月-19日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -20914,7 +20914,7 @@
           <t>B2 | 342呎 (2房)
 $715万
 $20,902/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -20922,7 +20922,7 @@
           <t>B3 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -20930,7 +20930,7 @@
           <t>B5 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月-04日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -20938,7 +20938,7 @@
           <t>B6 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-04月-13日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -20946,7 +20946,7 @@
           <t>B7 | 200呎 (开放式)
 $397万
 $19,867/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -20954,7 +20954,7 @@
           <t>B8 | 262呎 (1房)
 $572万
 $21,839/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -20962,7 +20962,7 @@
           <t>B9 | 261呎 (1房)
 $563万
 $21,562/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -20977,7 +20977,7 @@
           <t>A1 | 349呎 (2房)
 $723万
 $20,707/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -20985,7 +20985,7 @@
           <t>A2 | 342呎 (2房)
 $702万
 $20,520/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -20993,7 +20993,7 @@
           <t>A3 | 263呎 (1房)
 $542万
 $20,617/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -21001,7 +21001,7 @@
           <t>A5 | 258呎 (1房)
 $544万
 $21,081/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -21009,7 +21009,7 @@
           <t>A6 | 200呎 (开放式)
 $402万
 $20,088/呎
-(25年-04月-09日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -21017,7 +21017,7 @@
           <t>A7 | 262呎 (1房)
 $510万
 $19,469/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -21025,7 +21025,7 @@
           <t>A8 | 262呎 (1房)
 $640万
 $24,425/呎
-(26年-07月-16日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -21033,7 +21033,7 @@
           <t>B1 | 351呎 (2房)
 $773万
 $22,025/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -21041,7 +21041,7 @@
           <t>B2 | 342呎 (2房)
 $700万
 $20,458/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -21049,7 +21049,7 @@
           <t>B3 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月-24日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -21057,7 +21057,7 @@
           <t>B5 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -21065,7 +21065,7 @@
           <t>B6 | 258呎 (1房)
 $532万
 $20,632/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -21073,7 +21073,7 @@
           <t>B7 | 200呎 (开放式)
 $396万
 $19,816/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
@@ -21081,7 +21081,7 @@
           <t>B8 | 262呎 (1房)
 $552万
 $21,071/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr">
@@ -21089,7 +21089,7 @@
           <t>B9 | 261呎 (1房)
 $561万
 $21,494/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21104,7 @@
           <t>A1 | 349呎 (2房)
 $709万
 $20,306/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -21112,7 +21112,7 @@
           <t>A2 | 342呎 (2房)
 $674万
 $19,710/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -21120,7 +21120,7 @@
           <t>A3 | 263呎 (1房)
 $537万
 $20,402/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -21128,7 +21128,7 @@
           <t>A5 | 258呎 (1房)
 $521万
 $20,206/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -21136,7 +21136,7 @@
           <t>A6 | 200呎 (开放式)
 $392万
 $19,614/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -21144,7 +21144,7 @@
           <t>A7 | 262呎 (1房)
 $497万
 $18,958/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -21152,7 +21152,7 @@
           <t>A8 | 262呎 (1房)
 $568万
 $21,677/呎
-(25年-03月-07日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -21160,7 +21160,7 @@
           <t>B1 | 351呎 (2房)
 $729万
 $20,759/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -21168,7 +21168,7 @@
           <t>B2 | 342呎 (2房)
 $686万
 $20,068/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -21176,7 +21176,7 @@
           <t>B3 | 263呎 (1房)
 $527万
 $20,054/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -21184,7 +21184,7 @@
           <t>B5 | 263呎 (1房)
 $539万
 $20,490/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -21192,7 +21192,7 @@
           <t>B6 | 258呎 (1房)
 $511万
 $19,798/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -21200,7 +21200,7 @@
           <t>B7 | 200呎 (开放式)
 $395万
 $19,743/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
@@ -21208,7 +21208,7 @@
           <t>B8 | 262呎 (1房)
 $528万
 $20,159/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
@@ -21216,7 +21216,7 @@
           <t>B9 | 261呎 (1房)
 $529万
 $20,264/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21231,7 +21231,7 @@
           <t>A1 | 349呎 (2房)
 $697万
 $19,960/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -21239,7 +21239,7 @@
           <t>A2 | 342呎 (2房)
 $663万
 $19,376/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -21247,7 +21247,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,358/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -21255,7 +21255,7 @@
           <t>A5 | 258呎 (1房)
 $512万
 $19,838/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -21263,7 +21263,7 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,989/呎
-(25年-04月-09日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -21271,7 +21271,7 @@
           <t>A7 | 262呎 (1房)
 $504万
 $19,253/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -21279,7 +21279,7 @@
           <t>A8 | 262呎 (1房)
 $541万
 $20,637/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -21287,7 +21287,7 @@
           <t>B1 | 351呎 (2房)
 $716万
 $20,400/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -21295,7 +21295,7 @@
           <t>B2 | 342呎 (2房)
 $675万
 $19,734/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -21303,7 +21303,7 @@
           <t>B3 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -21311,7 +21311,7 @@
           <t>B5 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>B6 | 258呎 (1房)
 $501万
 $19,416/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -21327,7 +21327,7 @@
           <t>B7 | 200呎 (开放式)
 $390万
 $19,513/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -21335,7 +21335,7 @@
           <t>B8 | 262呎 (1房)
 $507万
 $19,362/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr">
@@ -21343,7 +21343,7 @@
           <t>B9 | 261呎 (1房)
 $518万
 $19,863/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21358,7 +21358,7 @@
           <t>A1 | 349呎 (2房)
 $700万
 $20,044/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -21366,7 +21366,7 @@
           <t>A2 | 342呎 (2房)
 $651万
 $19,027/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -21374,7 +21374,7 @@
           <t>A3 | 263呎 (1房)
 $500万
 $18,998/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -21382,7 +21382,7 @@
           <t>A5 | 258呎 (1房)
 $493万
 $19,091/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -21390,7 +21390,7 @@
           <t>A6 | 200呎 (开放式)
 $390万
 $19,504/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -21398,7 +21398,7 @@
           <t>A7 | 262呎 (1房)
 $499万
 $19,032/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -21406,7 +21406,7 @@
           <t>A8 | 262呎 (1房)
 $553万
 $21,114/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -21414,7 +21414,7 @@
           <t>B1 | 351呎 (2房)
 $703万
 $20,041/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -21422,7 +21422,7 @@
           <t>B2 | 342呎 (2房)
 $678万
 $19,822/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -21430,7 +21430,7 @@
           <t>B3 | 263呎 (1房)
 $524万
 $19,943/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -21438,7 +21438,7 @@
           <t>B5 | 263呎 (1房)
 $519万
 $19,733/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -21446,7 +21446,7 @@
           <t>B6 | 258呎 (1房)
 $503万
 $19,507/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -21454,7 +21454,7 @@
           <t>B7 | 200呎 (开放式)
 $389万
 $19,467/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -21462,7 +21462,7 @@
           <t>B8 | 262呎 (1房)
 $498万
 $19,018/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr">
@@ -21470,7 +21470,7 @@
           <t>B9 | 261呎 (1房)
 $509万
 $19,517/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21485,7 +21485,7 @@
           <t>A1 | 349呎 (2房)
 $675万
 $19,330/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -21493,7 +21493,7 @@
           <t>A2 | 342呎 (2房)
 $656万
 $19,171/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -21501,7 +21501,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,343/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -21509,7 +21509,7 @@
           <t>A5 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -21517,7 +21517,7 @@
           <t>A6 | 200呎 (开放式)
 $385万
 $19,274/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -21525,7 +21525,7 @@
           <t>A7 | 262呎 (1房)
 $493万
 $18,814/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -21533,7 +21533,7 @@
           <t>A8 | 262呎 (1房)
 $524万
 $19,991/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -21541,7 +21541,7 @@
           <t>B1 | 351呎 (2房)
 $693万
 $19,742/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -21549,7 +21549,7 @@
           <t>B2 | 342呎 (2房)
 $661万
 $19,331/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -21557,7 +21557,7 @@
           <t>B3 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -21565,7 +21565,7 @@
           <t>B5 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -21573,7 +21573,7 @@
           <t>B6 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -21581,7 +21581,7 @@
           <t>B7 | 200呎 (开放式)
 $385万
 $19,237/呎
-(25年-04月-14日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
@@ -21589,7 +21589,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,730/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr">
@@ -21597,7 +21597,7 @@
           <t>B9 | 261呎 (1房)
 $513万
 $19,650/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
           <t>A1 | 349呎 (2房)
 $681万
 $19,516/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -21620,7 +21620,7 @@
           <t>A2 | 342呎 (2房)
 $655万
 $19,147/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -21628,7 +21628,7 @@
           <t>A3 | 263呎 (1房)
 $503万
 $19,108/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -21636,7 +21636,7 @@
           <t>A5 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -21644,7 +21644,7 @@
           <t>A6 | 200呎 (开放式)
 $393万
 $19,646/呎
-(25年-04月-06日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -21652,7 +21652,7 @@
           <t>A7 | 262呎 (1房)
 $473万
 $18,052/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -21660,7 +21660,7 @@
           <t>A8 | 262呎 (1房)
 $518万
 $19,758/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -21668,7 +21668,7 @@
           <t>B1 | 351呎 (2房)
 $685万
 $19,503/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -21676,7 +21676,7 @@
           <t>B2 | 342呎 (2房)
 $646万
 $18,903/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -21684,7 +21684,7 @@
           <t>B3 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -21692,7 +21692,7 @@
           <t>B5 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -21700,7 +21700,7 @@
           <t>B6 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -21708,7 +21708,7 @@
           <t>B7 | 200呎 (开放式)
 $380万
 $19,007/呎
-(25年-04月-08日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -21716,7 +21716,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,502/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr">
@@ -21724,7 +21724,7 @@
           <t>B9 | 261呎 (1房)
 $496万
 $19,003/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21739,7 +21739,7 @@
           <t>A1 | 349呎 (2房)
 $661万
 $18,930/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -21747,7 +21747,7 @@
           <t>A2 | 342呎 (2房)
 $628万
 $18,376/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -21755,7 +21755,7 @@
           <t>A3 | 263呎 (1房)
 $493万
 $18,732/呎
-(25年-04月-02日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -21763,7 +21763,7 @@
           <t>A5 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -21771,7 +21771,7 @@
           <t>A6 | 200呎 (开放式)
 $381万
 $19,053/呎
-(25年-04月-07日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -21779,7 +21779,7 @@
           <t>A7 | 262呎 (1房)
 $469万
 $17,891/呎
-(25年-03月-13日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -21787,7 +21787,7 @@
           <t>A8 | 262呎 (1房)
 $502万
 $19,165/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -21795,7 +21795,7 @@
           <t>B1 | 351呎 (2房)
 $678万
 $19,323/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -21803,7 +21803,7 @@
           <t>B2 | 342呎 (2房)
 $648万
 $18,940/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -21811,7 +21811,7 @@
           <t>B3 | 263呎 (1房)
 $501万
 $19,032/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -21819,7 +21819,7 @@
           <t>B5 | 263呎 (1房)
 $490万
 $18,627/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -21827,7 +21827,7 @@
           <t>B6 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -21835,7 +21835,7 @@
           <t>B7 | 200呎 (开放式)
 $381万
 $19,058/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -21843,7 +21843,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,728/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr">
@@ -21851,7 +21851,7 @@
           <t>B9 | 261呎 (1房)
 $491万
 $18,830/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21866,7 +21866,7 @@
           <t>A1 | 349呎 (2房)
 $651万
 $18,642/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -21874,7 +21874,7 @@
           <t>A2 | 342呎 (2房)
 $619万
 $18,099/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -21882,7 +21882,7 @@
           <t>A3 | 263呎 (1房)
 $475万
 $18,046/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -21890,7 +21890,7 @@
           <t>A5 | 258呎 (1房)
 $479万
 $18,563/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -21898,7 +21898,7 @@
           <t>A6 | 200呎 (开放式)
 $376万
 $18,823/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -21906,7 +21906,7 @@
           <t>A7 | 262呎 (1房)
 $463万
 $17,676/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -21914,7 +21914,7 @@
           <t>A8 | 262呎 (1房)
 $495万
 $18,881/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -21922,7 +21922,7 @@
           <t>B1 | 351呎 (2房)
 $670万
 $19,084/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -21930,7 +21930,7 @@
           <t>B2 | 342呎 (2房)
 $647万
 $18,915/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -21938,7 +21938,7 @@
           <t>B3 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -21946,7 +21946,7 @@
           <t>B5 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -21954,7 +21954,7 @@
           <t>B6 | 258呎 (1房)
 $469万
 $18,168/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -21962,7 +21962,7 @@
           <t>B7 | 200呎 (开放式)
 $369万
 $18,428/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
@@ -21970,7 +21970,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,495/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
@@ -21978,7 +21978,7 @@
           <t>B9 | 261呎 (1房)
 $485万
 $18,601/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
           <t>A1 | 349呎 (2房)
 $641万
 $18,358/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -22001,7 +22001,7 @@
           <t>A2 | 342呎 (2房)
 $609万
 $17,819/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -22009,7 +22009,7 @@
           <t>A3 | 263呎 (1房)
 $466万
 $17,704/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -22017,7 +22017,7 @@
           <t>A5 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -22025,7 +22025,7 @@
           <t>A6 | 200呎 (开放式)
 $380万
 $18,997/呎
-(25年-03月-12日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -22033,7 +22033,7 @@
           <t>A7 | 262呎 (1房)
 $458万
 $17,462/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -22041,7 +22041,7 @@
           <t>A8 | 262呎 (1房)
 $486万
 $18,537/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -22049,7 +22049,7 @@
           <t>B1 | 351呎 (2房)
 $661万
 $18,846/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -22057,7 +22057,7 @@
           <t>B2 | 342呎 (2房)
 $639万
 $18,687/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -22065,7 +22065,7 @@
           <t>B3 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -22073,7 +22073,7 @@
           <t>B5 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -22081,7 +22081,7 @@
           <t>B6 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -22089,7 +22089,7 @@
           <t>B7 | 200呎 (开放式)
 $366万
 $18,280/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -22097,7 +22097,7 @@
           <t>B8 | 262呎 (1房)
 $468万
 $17,873/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr">
@@ -22105,7 +22105,7 @@
           <t>B9 | 261呎 (1房)
 $488万
 $18,710/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -22120,7 +22120,7 @@
           <t>A1 | 349呎 (2房)
 $629万
 $18,012/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -22128,7 +22128,7 @@
           <t>A2 | 342呎 (2房)
 $598万
 $17,485/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -22136,7 +22136,7 @@
           <t>A3 | 263呎 (1房)
 $457万
 $17,364/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -22144,7 +22144,7 @@
           <t>A5 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -22152,7 +22152,7 @@
           <t>A6 | 200呎 (开放式)
 $364万
 $18,188/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -22160,7 +22160,7 @@
           <t>A7 | 262呎 (1房)
 $452万
 $17,248/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -22168,7 +22168,7 @@
           <t>A8 | 262呎 (1房)
 $482万
 $18,390/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -22176,7 +22176,7 @@
           <t>B1 | 351呎 (2房)
 $651万
 $18,544/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -22184,7 +22184,7 @@
           <t>B2 | 342呎 (2房)
 $616万
 $18,013/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -22192,7 +22192,7 @@
           <t>B3 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -22200,7 +22200,7 @@
           <t>B5 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -22208,7 +22208,7 @@
           <t>B6 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -22216,7 +22216,7 @@
           <t>B7 | 200呎 (开放式)
 $371万
 $18,536/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -22224,7 +22224,7 @@
           <t>B8 | 262呎 (1房)
 $462万
 $17,641/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr">
@@ -22232,7 +22232,7 @@
           <t>B9 | 261呎 (1房)
 $481万
 $18,418/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -22247,7 +22247,7 @@
           <t>A1 | 349呎 (2房)
 $637万
 $18,246/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -22255,7 +22255,7 @@
           <t>A2 | 342呎 (2房)
 $606万
 $17,714/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -22263,7 +22263,7 @@
           <t>A3 | 263呎 (1房)
 $453万
 $17,206/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -22271,7 +22271,7 @@
           <t>A5 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -22279,7 +22279,7 @@
           <t>A6 | 200呎 (开放式)
 $363万
 $18,133/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -22287,7 +22287,7 @@
           <t>A7 | 262呎 (1房)
 $451万
 $17,223/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -22295,7 +22295,7 @@
           <t>A8 | 262呎 (1房)
 $468万
 $17,848/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -22303,7 +22303,7 @@
           <t>B1 | 351呎 (2房)
 $652万
 $18,583/呎
-(25年-04月-01日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -22311,7 +22311,7 @@
           <t>B2 | 342呎 (2房)
 $605万
 $17,679/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -22319,7 +22319,7 @@
           <t>B3 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -22327,7 +22327,7 @@
           <t>B5 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -22335,7 +22335,7 @@
           <t>B6 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -22343,7 +22343,7 @@
           <t>B7 | 200呎 (开放式)
 $362万
 $18,082/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -22351,7 +22351,7 @@
           <t>B8 | 262呎 (1房)
 $456万
 $17,413/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr">
@@ -22359,7 +22359,7 @@
           <t>B9 | 261呎 (1房)
 $461万
 $17,681/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
           <t>A1 | 349呎 (2房)
 $605万
 $17,324/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -22382,7 +22382,7 @@
           <t>A2 | 342呎 (2房)
 $575万
 $16,821/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -22390,7 +22390,7 @@
           <t>A3 | 263呎 (1房)
 $450万
 $17,098/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -22398,7 +22398,7 @@
           <t>A5 | 258呎 (1房)
 $437万
 $16,920/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -22406,7 +22406,7 @@
           <t>A6 | 200呎 (开放式)
 $358万
 $17,898/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -22414,7 +22414,7 @@
           <t>A7 | 262呎 (1房)
 $441万
 $16,823/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -22422,7 +22422,7 @@
           <t>A8 | 262呎 (1房)
 $459万
 $17,505/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -22430,7 +22430,7 @@
           <t>B1 | 351呎 (2房)
 $646万
 $18,410/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -22438,7 +22438,7 @@
           <t>B2 | 342呎 (2房)
 $593万
 $17,345/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -22446,7 +22446,7 @@
           <t>B3 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -22454,7 +22454,7 @@
           <t>B5 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -22462,7 +22462,7 @@
           <t>B6 | 258呎 (1房)
 $445万
 $17,233/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -22470,7 +22470,7 @@
           <t>B7 | 200呎 (开放式)
 $357万
 $17,848/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
@@ -22478,7 +22478,7 @@
           <t>B8 | 262呎 (1房)
 $450万
 $17,185/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr">
@@ -22486,7 +22486,7 @@
           <t>B9 | 261呎 (1房)
 $452万
 $17,335/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -22501,7 +22501,7 @@
           <t>A1 | 349呎 (2房)
 $595万
 $17,040/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -22509,7 +22509,7 @@
           <t>A2 | 342呎 (2房)
 $566万
 $16,541/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -22517,7 +22517,7 @@
           <t>A3 | 263呎 (1房)
 $433万
 $16,451/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -22525,7 +22525,7 @@
           <t>A5 | 258呎 (1房)
 $430万
 $16,649/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -22533,7 +22533,7 @@
           <t>A6 | 200呎 (开放式)
 $353万
 $17,668/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -22541,7 +22541,7 @@
           <t>A7 | 262呎 (1房)
 $443万
 $16,916/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -22549,7 +22549,7 @@
           <t>A8 | 262呎 (1房)
 $461万
 $17,594/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -22557,7 +22557,7 @@
           <t>B1 | 351呎 (2房)
 $615万
 $17,527/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -22565,7 +22565,7 @@
           <t>B2 | 342呎 (2房)
 $584万
 $17,068/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -22573,7 +22573,7 @@
           <t>B3 | 263呎 (1房)
 $448万
 $17,052/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -22581,7 +22581,7 @@
           <t>B5 | 263呎 (1房)
 $439万
 $16,689/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -22589,7 +22589,7 @@
           <t>B6 | 258呎 (1房)
 $433万
 $16,776/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -22597,7 +22597,7 @@
           <t>B7 | 200呎 (开放式)
 $433万
 $21,641/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr">
@@ -22605,7 +22605,7 @@
           <t>B8 | 262呎 (1房)
 $454万
 $17,325/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P22" s="20" t="inlineStr">
@@ -22613,7 +22613,7 @@
           <t>B9 | 261呎 (1房)
 $445万
 $17,046/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
           <t>A1 | 349呎 (2房)
 $597万
 $17,117/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -22636,7 +22636,7 @@
           <t>A2 | 342呎 (2房)
 $554万
 $16,208/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -22644,7 +22644,7 @@
           <t>A3 | 263呎 (1房)
 $432万
 $16,430/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -22652,7 +22652,7 @@
           <t>A5 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -22660,7 +22660,7 @@
           <t>A6 | 200呎 (开放式)
 $348万
 $17,383/呎
-(25年-03月-31日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -22668,7 +22668,7 @@
           <t>A7 | 262呎 (1房)
 $435万
 $16,586/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -22676,7 +22676,7 @@
           <t>A8 | 262呎 (1房)
 $444万
 $16,932/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -22684,7 +22684,7 @@
           <t>B1 | 351呎 (2房)
 $605万
 $17,228/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -22692,7 +22692,7 @@
           <t>B2 | 342呎 (2房)
 $574万
 $16,791/呎
-(25年-02月-28日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -22700,7 +22700,7 @@
           <t>B3 | 263呎 (1房)
 $441万
 $16,763/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -22708,7 +22708,7 @@
           <t>B5 | 263呎 (1房)
 $431万
 $16,406/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -22716,7 +22716,7 @@
           <t>B6 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -22724,7 +22724,7 @@
           <t>B7 | 200呎 (开放式)
 $346万
 $17,324/呎
-(25年-04月-02日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -22732,7 +22732,7 @@
           <t>B8 | 262呎 (1房)
 $437万
 $16,669/呎
-(25年-03月-18日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
@@ -22740,7 +22740,7 @@
           <t>B9 | 261呎 (1房)
 $437万
 $16,761/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
           <t>A1 | 349呎 (2房)
 $577万
 $16,523/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -22763,7 +22763,7 @@
           <t>A2 | 342呎 (2房)
 $541万
 $15,820/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -22771,7 +22771,7 @@
           <t>A3 | 263呎 (1房)
 $410万
 $15,591/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -22779,7 +22779,7 @@
           <t>A5 | 258呎 (1房)
 $410万
 $15,890/呎
-(25年-03月-19日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -22787,7 +22787,7 @@
           <t>A6 | 200呎 (开放式)
 $346万
 $17,296/呎
-(25年-03月-25日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -22795,7 +22795,7 @@
           <t>A7 | 262呎 (1房)
 $417万
 $15,914/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -22803,7 +22803,7 @@
           <t>A8 | 262呎 (1房)
 $438万
 $16,704/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -22811,7 +22811,7 @@
           <t>B1 | 351呎 (2房)
 $601万
 $17,113/呎
-(25年-03月-24日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -22819,7 +22819,7 @@
           <t>B2 | 342呎 (2房)
 $565万
 $16,514/呎
-(25年-03月-20日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -22827,7 +22827,7 @@
           <t>B3 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月-17日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -22835,7 +22835,7 @@
           <t>B5 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月-16日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -22843,7 +22843,7 @@
           <t>B6 | 258呎 (1房)
 $429万
 $16,632/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -22851,7 +22851,7 @@
           <t>B7 | 200呎 (开放式)
 $337万
 $16,872/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -22859,7 +22859,7 @@
           <t>B8 | 262呎 (1房)
 $446万
 $17,041/呎
-(25年-04月-01日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr">
@@ -22867,7 +22867,7 @@
           <t>B9 | 261呎 (1房)
 $431万
 $16,532/呎
-(25年-03月-23日)</t>
+(25年-03月)</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
           <t>A1 | 311呎 (2房)
 $723万
 $23,241/呎
-(25年-04月-13日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -22890,7 +22890,7 @@
           <t>A2 | 304呎 (2房)
 $656万
 $21,579/呎
-(25年-03月-26日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -22898,7 +22898,7 @@
           <t>A3 | 225呎 (1房)
 $470万
 $20,881/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -22906,7 +22906,7 @@
           <t>A5 | 221呎 (1房)
 $465万
 $21,040/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -22914,7 +22914,7 @@
           <t>A6 | 178呎 (开放式)
 $452万
 $25,393/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -22922,7 +22922,7 @@
           <t>A7 | 224呎 (1房)
 $585万
 $26,116/呎
-(26年-04月-15日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -22930,7 +22930,7 @@
           <t>A8 | 224呎 (1房)
 $633万
 $28,259/呎
-(26年-04月-08日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -22938,7 +22938,7 @@
           <t>B1 | 313呎 (2房)
 $725万
 $23,163/呎
-(25年-07月-08日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -22946,7 +22946,7 @@
           <t>B2 | 304呎 (2房)
 $660万
 $21,711/呎
-(25年-04月-02日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -22954,7 +22954,7 @@
           <t>B3 | 225呎 (1房)
 $475万
 $21,111/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -22962,7 +22962,7 @@
           <t>B5 | 225呎 (1房)
 $470万
 $20,889/呎
-(25年-04月-10日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -22970,7 +22970,7 @@
           <t>B6 | 220呎 (1房)
 $465万
 $21,136/呎
-(25年-04月-22日)</t>
+(25年-04月)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -22978,7 +22978,7 @@
           <t>B7 | 178呎 (开放式)
 $458万
 $25,730/呎
-(26年-04月-13日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr">
@@ -22986,7 +22986,7 @@
           <t>B8 | 224呎 (1房)
 $520万
 $23,214/呎
-(25年-05月-07日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr">
@@ -22994,7 +22994,7 @@
           <t>B9 | 224呎 (1房)
 $618万
 $27,593/呎
-(26年-04月-14日)</t>
+(26年-04月)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -20356,7 +20356,7 @@
           <t>A1 | 353呎 (2房)
 $1120万
 $31,728/呎
-(26年-04月)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="C5" s="20" t="inlineStr">
@@ -20364,7 +20364,7 @@
           <t>A2 | 342呎 (2房)
 $868万
 $25,374/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="D5" s="20" t="inlineStr">
@@ -20372,7 +20372,7 @@
           <t>A3 | 263呎 (1房)
 $653万
 $24,820/呎
-(26年-05月)</t>
+(26年-05月-13日)</t>
         </is>
       </c>
       <c r="E5" s="20" t="inlineStr">
@@ -20380,7 +20380,7 @@
           <t>A5 | 258呎 (1房)
 $638万
 $24,728/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="F5" s="20" t="inlineStr">
@@ -20388,7 +20388,7 @@
           <t>A6 | 200呎 (开放式)
 $464万
 $23,182/呎
-(26年-06月)</t>
+(26年-06月-25日)</t>
         </is>
       </c>
       <c r="G5" s="21" t="inlineStr">
@@ -20405,7 +20405,7 @@
           <t>B1 | 358呎 (2房)
 $1039万
 $29,017/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J5" s="20" t="inlineStr">
@@ -20413,7 +20413,7 @@
           <t>B2 | 342呎 (2房)
 $882万
 $25,781/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="K5" s="21" t="inlineStr">
@@ -20429,7 +20429,7 @@
           <t>B5 | 263呎 (1房)
 $668万
 $25,383/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="M5" s="20" t="inlineStr">
@@ -20437,7 +20437,7 @@
           <t>B6 | 258呎 (1房)
 $655万
 $25,404/呎
-(26年-07月)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="N5" s="20" t="inlineStr">
@@ -20445,7 +20445,7 @@
           <t>B7 | 200呎 (开放式)
 $457万
 $22,838/呎
-(26年-07月)</t>
+(26年-07月-19日)</t>
         </is>
       </c>
       <c r="O5" s="21" t="inlineStr">
@@ -20469,7 +20469,7 @@
           <t>A1 | 349呎 (2房)
 $886万
 $25,399/呎
-(26年-05月)</t>
+(26年-05月-05日)</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -20477,7 +20477,7 @@
           <t>A2 | 342呎 (2房)
 $798万
 $23,320/呎
-(25年-11月)</t>
+(25年-11月-05日)</t>
         </is>
       </c>
       <c r="D6" s="20" t="inlineStr">
@@ -20485,7 +20485,7 @@
           <t>A3 | 263呎 (1房)
 $646万
 $24,556/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E6" s="20" t="inlineStr">
@@ -20493,7 +20493,7 @@
           <t>A5 | 258呎 (1房)
 $631万
 $24,462/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="F6" s="20" t="inlineStr">
@@ -20501,7 +20501,7 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,987/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="G6" s="20" t="inlineStr">
@@ -20509,7 +20509,7 @@
           <t>A7 | 262呎 (1房)
 $611万
 $23,310/呎
-(26年-07月)</t>
+(26年-07月-18日)</t>
         </is>
       </c>
       <c r="H6" s="23" t="inlineStr">
@@ -20525,7 +20525,7 @@
           <t>B1 | 351呎 (2房)
 $905万
 $25,795/呎
-(26年-07月)</t>
+(26年-07月-17日)</t>
         </is>
       </c>
       <c r="J6" s="20" t="inlineStr">
@@ -20533,7 +20533,7 @@
           <t>B2 | 342呎 (2房)
 $803万
 $23,471/呎
-(25年-11月)</t>
+(25年-11月-19日)</t>
         </is>
       </c>
       <c r="K6" s="20" t="inlineStr">
@@ -20541,7 +20541,7 @@
           <t>B3 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-05月)</t>
+(26年-05月-03日)</t>
         </is>
       </c>
       <c r="L6" s="20" t="inlineStr">
@@ -20549,7 +20549,7 @@
           <t>B5 | 263呎 (1房)
 $654万
 $24,884/呎
-(26年-07月)</t>
+(26年-07月-06日)</t>
         </is>
       </c>
       <c r="M6" s="20" t="inlineStr">
@@ -20557,7 +20557,7 @@
           <t>B6 | 258呎 (1房)
 $648万
 $25,130/呎
-(26年-06月)</t>
+(26年-06月-01日)</t>
         </is>
       </c>
       <c r="N6" s="20" t="inlineStr">
@@ -20565,7 +20565,7 @@
           <t>B7 | 200呎 (开放式)
 $400万
 $19,982/呎
-(25年-04月)</t>
+(25年-04月-27日)</t>
         </is>
       </c>
       <c r="O6" s="24" t="inlineStr">
@@ -20596,7 +20596,7 @@
           <t>A1 | 349呎 (2房)
 $870万
 $24,924/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -20604,7 +20604,7 @@
           <t>A2 | 342呎 (2房)
 $776万
 $22,677/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="D7" s="20" t="inlineStr">
@@ -20612,7 +20612,7 @@
           <t>A3 | 263呎 (1房)
 $584万
 $22,188/呎
-(25年-05月)</t>
+(25年-05月-11日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -20620,7 +20620,7 @@
           <t>A5 | 258呎 (1房)
 $571万
 $22,130/呎
-(25年-11月)</t>
+(25年-11月-06日)</t>
         </is>
       </c>
       <c r="F7" s="20" t="inlineStr">
@@ -20628,7 +20628,7 @@
           <t>A6 | 200呎 (开放式)
 $399万
 $19,950/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="G7" s="20" t="inlineStr">
@@ -20636,7 +20636,7 @@
           <t>A7 | 262呎 (1房)
 $603万
 $23,030/呎
-(26年-07月)</t>
+(26年-07月-05日)</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -20652,7 +20652,7 @@
           <t>B1 | 351呎 (2房)
 $888万
 $25,301/呎
-(26年-05月)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="J7" s="20" t="inlineStr">
@@ -20660,7 +20660,7 @@
           <t>B2 | 342呎 (2房)
 $781万
 $22,836/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="K7" s="20" t="inlineStr">
@@ -20668,7 +20668,7 @@
           <t>B3 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-04月)</t>
+(26年-04月-10日)</t>
         </is>
       </c>
       <c r="L7" s="20" t="inlineStr">
@@ -20676,7 +20676,7 @@
           <t>B5 | 263呎 (1房)
 $650万
 $24,697/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="M7" s="20" t="inlineStr">
@@ -20684,7 +20684,7 @@
           <t>B6 | 258呎 (1房)
 $638万
 $24,735/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="N7" s="20" t="inlineStr">
@@ -20692,7 +20692,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,964/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="O7" s="21" t="inlineStr">
@@ -20708,7 +20708,7 @@
           <t>B9 | 261呎 (1房)
 $590万
 $22,612/呎
-(25年-07月)</t>
+(25年-07月-22日)</t>
         </is>
       </c>
     </row>
@@ -20723,7 +20723,7 @@
           <t>A1 | 349呎 (2房)
 $787万
 $22,549/呎
-(25年-10月)</t>
+(25年-10月-27日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -20731,7 +20731,7 @@
           <t>A2 | 342呎 (2房)
 $756万
 $22,096/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="D8" s="20" t="inlineStr">
@@ -20739,7 +20739,7 @@
           <t>A3 | 263呎 (1房)
 $570万
 $21,667/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -20747,7 +20747,7 @@
           <t>A5 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="F8" s="20" t="inlineStr">
@@ -20755,7 +20755,7 @@
           <t>A6 | 200呎 (开放式)
 $406万
 $20,322/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -20763,7 +20763,7 @@
           <t>A7 | 262呎 (1房)
 $542万
 $20,686/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -20779,7 +20779,7 @@
           <t>B1 | 351呎 (2房)
 $810万
 $23,084/呎
-(25年-08月)</t>
+(25年-08月-26日)</t>
         </is>
       </c>
       <c r="J8" s="20" t="inlineStr">
@@ -20787,7 +20787,7 @@
           <t>B2 | 342呎 (2房)
 $761万
 $22,257/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="K8" s="20" t="inlineStr">
@@ -20795,7 +20795,7 @@
           <t>B3 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月)</t>
+(26年-04月-26日)</t>
         </is>
       </c>
       <c r="L8" s="20" t="inlineStr">
@@ -20803,7 +20803,7 @@
           <t>B5 | 263呎 (1房)
 $637万
 $24,232/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="M8" s="20" t="inlineStr">
@@ -20811,7 +20811,7 @@
           <t>B6 | 258呎 (1房)
 $558万
 $21,631/呎
-(25年-10月)</t>
+(25年-10月-16日)</t>
         </is>
       </c>
       <c r="N8" s="20" t="inlineStr">
@@ -20819,7 +20819,7 @@
           <t>B7 | 200呎 (开放式)
 $399万
 $19,936/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="O8" s="20" t="inlineStr">
@@ -20827,7 +20827,7 @@
           <t>B8 | 262呎 (1房)
 $568万
 $21,673/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="P8" s="20" t="inlineStr">
@@ -20835,7 +20835,7 @@
           <t>B9 | 261呎 (1房)
 $576万
 $22,087/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -20850,7 +20850,7 @@
           <t>A1 | 349呎 (2房)
 $768万
 $22,009/呎
-(25年-11月)</t>
+(25年-11月-02日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -20858,7 +20858,7 @@
           <t>A2 | 342呎 (2房)
 $703万
 $20,541/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="D9" s="20" t="inlineStr">
@@ -20866,7 +20866,7 @@
           <t>A3 | 263呎 (1房)
 $556万
 $21,142/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="E9" s="20" t="inlineStr">
@@ -20874,7 +20874,7 @@
           <t>A5 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -20882,7 +20882,7 @@
           <t>A6 | 200呎 (开放式)
 $395万
 $19,734/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="G9" s="20" t="inlineStr">
@@ -20890,7 +20890,7 @@
           <t>A7 | 262呎 (1房)
 $530万
 $20,244/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H9" s="20" t="inlineStr">
@@ -20898,7 +20898,7 @@
           <t>A8 | 262呎 (1房)
 $650万
 $24,806/呎
-(26年-07月)</t>
+(26年-07月-13日)</t>
         </is>
       </c>
       <c r="I9" s="20" t="inlineStr">
@@ -20906,7 +20906,7 @@
           <t>B1 | 351呎 (2房)
 $791万
 $22,523/呎
-(25年-06月)</t>
+(25年-06月-19日)</t>
         </is>
       </c>
       <c r="J9" s="20" t="inlineStr">
@@ -20914,7 +20914,7 @@
           <t>B2 | 342呎 (2房)
 $715万
 $20,902/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K9" s="20" t="inlineStr">
@@ -20922,7 +20922,7 @@
           <t>B3 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="L9" s="20" t="inlineStr">
@@ -20930,7 +20930,7 @@
           <t>B5 | 263呎 (1房)
 $630万
 $23,967/呎
-(26年-05月)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="M9" s="20" t="inlineStr">
@@ -20938,7 +20938,7 @@
           <t>B6 | 258呎 (1房)
 $545万
 $21,135/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="N9" s="20" t="inlineStr">
@@ -20946,7 +20946,7 @@
           <t>B7 | 200呎 (开放式)
 $397万
 $19,867/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="O9" s="20" t="inlineStr">
@@ -20954,7 +20954,7 @@
           <t>B8 | 262呎 (1房)
 $572万
 $21,839/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="P9" s="20" t="inlineStr">
@@ -20962,7 +20962,7 @@
           <t>B9 | 261呎 (1房)
 $563万
 $21,562/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -20977,7 +20977,7 @@
           <t>A1 | 349呎 (2房)
 $723万
 $20,707/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -20985,7 +20985,7 @@
           <t>A2 | 342呎 (2房)
 $702万
 $20,520/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -20993,7 +20993,7 @@
           <t>A3 | 263呎 (1房)
 $542万
 $20,617/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -21001,7 +21001,7 @@
           <t>A5 | 258呎 (1房)
 $544万
 $21,081/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -21009,7 +21009,7 @@
           <t>A6 | 200呎 (开放式)
 $402万
 $20,088/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="G10" s="20" t="inlineStr">
@@ -21017,7 +21017,7 @@
           <t>A7 | 262呎 (1房)
 $510万
 $19,469/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="H10" s="20" t="inlineStr">
@@ -21025,7 +21025,7 @@
           <t>A8 | 262呎 (1房)
 $640万
 $24,425/呎
-(26年-07月)</t>
+(26年-07月-16日)</t>
         </is>
       </c>
       <c r="I10" s="20" t="inlineStr">
@@ -21033,7 +21033,7 @@
           <t>B1 | 351呎 (2房)
 $773万
 $22,025/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="J10" s="20" t="inlineStr">
@@ -21041,7 +21041,7 @@
           <t>B2 | 342呎 (2房)
 $700万
 $20,458/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K10" s="20" t="inlineStr">
@@ -21049,7 +21049,7 @@
           <t>B3 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月)</t>
+(25年-04月-24日)</t>
         </is>
       </c>
       <c r="L10" s="20" t="inlineStr">
@@ -21057,7 +21057,7 @@
           <t>B5 | 263呎 (1房)
 $556万
 $21,129/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="M10" s="20" t="inlineStr">
@@ -21065,7 +21065,7 @@
           <t>B6 | 258呎 (1房)
 $532万
 $20,632/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N10" s="20" t="inlineStr">
@@ -21073,7 +21073,7 @@
           <t>B7 | 200呎 (开放式)
 $396万
 $19,816/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
@@ -21081,7 +21081,7 @@
           <t>B8 | 262呎 (1房)
 $552万
 $21,071/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="P10" s="20" t="inlineStr">
@@ -21089,7 +21089,7 @@
           <t>B9 | 261呎 (1房)
 $561万
 $21,494/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -21104,7 +21104,7 @@
           <t>A1 | 349呎 (2房)
 $709万
 $20,306/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -21112,7 +21112,7 @@
           <t>A2 | 342呎 (2房)
 $674万
 $19,710/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -21120,7 +21120,7 @@
           <t>A3 | 263呎 (1房)
 $537万
 $20,402/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -21128,7 +21128,7 @@
           <t>A5 | 258呎 (1房)
 $521万
 $20,206/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -21136,7 +21136,7 @@
           <t>A6 | 200呎 (开放式)
 $392万
 $19,614/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="G11" s="20" t="inlineStr">
@@ -21144,7 +21144,7 @@
           <t>A7 | 262呎 (1房)
 $497万
 $18,958/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="H11" s="20" t="inlineStr">
@@ -21152,7 +21152,7 @@
           <t>A8 | 262呎 (1房)
 $568万
 $21,677/呎
-(25年-03月)</t>
+(25年-03月-07日)</t>
         </is>
       </c>
       <c r="I11" s="20" t="inlineStr">
@@ -21160,7 +21160,7 @@
           <t>B1 | 351呎 (2房)
 $729万
 $20,759/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J11" s="20" t="inlineStr">
@@ -21168,7 +21168,7 @@
           <t>B2 | 342呎 (2房)
 $686万
 $20,068/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K11" s="20" t="inlineStr">
@@ -21176,7 +21176,7 @@
           <t>B3 | 263呎 (1房)
 $527万
 $20,054/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="L11" s="20" t="inlineStr">
@@ -21184,7 +21184,7 @@
           <t>B5 | 263呎 (1房)
 $539万
 $20,490/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="M11" s="20" t="inlineStr">
@@ -21192,7 +21192,7 @@
           <t>B6 | 258呎 (1房)
 $511万
 $19,798/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N11" s="20" t="inlineStr">
@@ -21200,7 +21200,7 @@
           <t>B7 | 200呎 (开放式)
 $395万
 $19,743/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="O11" s="20" t="inlineStr">
@@ -21208,7 +21208,7 @@
           <t>B8 | 262呎 (1房)
 $528万
 $20,159/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="P11" s="20" t="inlineStr">
@@ -21216,7 +21216,7 @@
           <t>B9 | 261呎 (1房)
 $529万
 $20,264/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -21231,7 +21231,7 @@
           <t>A1 | 349呎 (2房)
 $697万
 $19,960/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -21239,7 +21239,7 @@
           <t>A2 | 342呎 (2房)
 $663万
 $19,376/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D12" s="20" t="inlineStr">
@@ -21247,7 +21247,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,358/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -21255,7 +21255,7 @@
           <t>A5 | 258呎 (1房)
 $512万
 $19,838/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -21263,7 +21263,7 @@
           <t>A6 | 200呎 (开放式)
 $400万
 $19,989/呎
-(25年-04月)</t>
+(25年-04月-09日)</t>
         </is>
       </c>
       <c r="G12" s="20" t="inlineStr">
@@ -21271,7 +21271,7 @@
           <t>A7 | 262呎 (1房)
 $504万
 $19,253/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">
@@ -21279,7 +21279,7 @@
           <t>A8 | 262呎 (1房)
 $541万
 $20,637/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="I12" s="20" t="inlineStr">
@@ -21287,7 +21287,7 @@
           <t>B1 | 351呎 (2房)
 $716万
 $20,400/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J12" s="20" t="inlineStr">
@@ -21295,7 +21295,7 @@
           <t>B2 | 342呎 (2房)
 $675万
 $19,734/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="K12" s="20" t="inlineStr">
@@ -21303,7 +21303,7 @@
           <t>B3 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="L12" s="20" t="inlineStr">
@@ -21311,7 +21311,7 @@
           <t>B5 | 263呎 (1房)
 $528万
 $20,083/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="M12" s="20" t="inlineStr">
@@ -21319,7 +21319,7 @@
           <t>B6 | 258呎 (1房)
 $501万
 $19,416/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="N12" s="20" t="inlineStr">
@@ -21327,7 +21327,7 @@
           <t>B7 | 200呎 (开放式)
 $390万
 $19,513/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="O12" s="20" t="inlineStr">
@@ -21335,7 +21335,7 @@
           <t>B8 | 262呎 (1房)
 $507万
 $19,362/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P12" s="20" t="inlineStr">
@@ -21343,7 +21343,7 @@
           <t>B9 | 261呎 (1房)
 $518万
 $19,863/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
     </row>
@@ -21358,7 +21358,7 @@
           <t>A1 | 349呎 (2房)
 $700万
 $20,044/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -21366,7 +21366,7 @@
           <t>A2 | 342呎 (2房)
 $651万
 $19,027/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D13" s="20" t="inlineStr">
@@ -21374,7 +21374,7 @@
           <t>A3 | 263呎 (1房)
 $500万
 $18,998/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -21382,7 +21382,7 @@
           <t>A5 | 258呎 (1房)
 $493万
 $19,091/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="F13" s="20" t="inlineStr">
@@ -21390,7 +21390,7 @@
           <t>A6 | 200呎 (开放式)
 $390万
 $19,504/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -21398,7 +21398,7 @@
           <t>A7 | 262呎 (1房)
 $499万
 $19,032/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="H13" s="20" t="inlineStr">
@@ -21406,7 +21406,7 @@
           <t>A8 | 262呎 (1房)
 $553万
 $21,114/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="I13" s="20" t="inlineStr">
@@ -21414,7 +21414,7 @@
           <t>B1 | 351呎 (2房)
 $703万
 $20,041/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J13" s="20" t="inlineStr">
@@ -21422,7 +21422,7 @@
           <t>B2 | 342呎 (2房)
 $678万
 $19,822/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="K13" s="20" t="inlineStr">
@@ -21430,7 +21430,7 @@
           <t>B3 | 263呎 (1房)
 $524万
 $19,943/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="L13" s="20" t="inlineStr">
@@ -21438,7 +21438,7 @@
           <t>B5 | 263呎 (1房)
 $519万
 $19,733/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="M13" s="20" t="inlineStr">
@@ -21446,7 +21446,7 @@
           <t>B6 | 258呎 (1房)
 $503万
 $19,507/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="N13" s="20" t="inlineStr">
@@ -21454,7 +21454,7 @@
           <t>B7 | 200呎 (开放式)
 $389万
 $19,467/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
@@ -21462,7 +21462,7 @@
           <t>B8 | 262呎 (1房)
 $498万
 $19,018/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P13" s="20" t="inlineStr">
@@ -21470,7 +21470,7 @@
           <t>B9 | 261呎 (1房)
 $509万
 $19,517/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -21485,7 +21485,7 @@
           <t>A1 | 349呎 (2房)
 $675万
 $19,330/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -21493,7 +21493,7 @@
           <t>A2 | 342呎 (2房)
 $656万
 $19,171/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
@@ -21501,7 +21501,7 @@
           <t>A3 | 263呎 (1房)
 $509万
 $19,343/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="E14" s="20" t="inlineStr">
@@ -21509,7 +21509,7 @@
           <t>A5 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -21517,7 +21517,7 @@
           <t>A6 | 200呎 (开放式)
 $385万
 $19,274/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G14" s="20" t="inlineStr">
@@ -21525,7 +21525,7 @@
           <t>A7 | 262呎 (1房)
 $493万
 $18,814/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H14" s="20" t="inlineStr">
@@ -21533,7 +21533,7 @@
           <t>A8 | 262呎 (1房)
 $524万
 $19,991/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="I14" s="20" t="inlineStr">
@@ -21541,7 +21541,7 @@
           <t>B1 | 351呎 (2房)
 $693万
 $19,742/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J14" s="20" t="inlineStr">
@@ -21549,7 +21549,7 @@
           <t>B2 | 342呎 (2房)
 $661万
 $19,331/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="K14" s="20" t="inlineStr">
@@ -21557,7 +21557,7 @@
           <t>B3 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="L14" s="20" t="inlineStr">
@@ -21565,7 +21565,7 @@
           <t>B5 | 263呎 (1房)
 $500万
 $19,030/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="M14" s="20" t="inlineStr">
@@ -21573,7 +21573,7 @@
           <t>B6 | 258呎 (1房)
 $486万
 $18,821/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N14" s="20" t="inlineStr">
@@ -21581,7 +21581,7 @@
           <t>B7 | 200呎 (开放式)
 $385万
 $19,237/呎
-(25年-04月)</t>
+(25年-04月-14日)</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
@@ -21589,7 +21589,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,730/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P14" s="20" t="inlineStr">
@@ -21597,7 +21597,7 @@
           <t>B9 | 261呎 (1房)
 $513万
 $19,650/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21612,7 @@
           <t>A1 | 349呎 (2房)
 $681万
 $19,516/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -21620,7 +21620,7 @@
           <t>A2 | 342呎 (2房)
 $655万
 $19,147/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -21628,7 +21628,7 @@
           <t>A3 | 263呎 (1房)
 $503万
 $19,108/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="E15" s="20" t="inlineStr">
@@ -21636,7 +21636,7 @@
           <t>A5 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="F15" s="20" t="inlineStr">
@@ -21644,7 +21644,7 @@
           <t>A6 | 200呎 (开放式)
 $393万
 $19,646/呎
-(25年-04月)</t>
+(25年-04月-06日)</t>
         </is>
       </c>
       <c r="G15" s="20" t="inlineStr">
@@ -21652,7 +21652,7 @@
           <t>A7 | 262呎 (1房)
 $473万
 $18,052/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H15" s="20" t="inlineStr">
@@ -21660,7 +21660,7 @@
           <t>A8 | 262呎 (1房)
 $518万
 $19,758/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="I15" s="20" t="inlineStr">
@@ -21668,7 +21668,7 @@
           <t>B1 | 351呎 (2房)
 $685万
 $19,503/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J15" s="20" t="inlineStr">
@@ -21676,7 +21676,7 @@
           <t>B2 | 342呎 (2房)
 $646万
 $18,903/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -21684,7 +21684,7 @@
           <t>B3 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="L15" s="20" t="inlineStr">
@@ -21692,7 +21692,7 @@
           <t>B5 | 263呎 (1房)
 $494万
 $18,798/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="M15" s="20" t="inlineStr">
@@ -21700,7 +21700,7 @@
           <t>B6 | 258呎 (1房)
 $490万
 $19,007/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="N15" s="20" t="inlineStr">
@@ -21708,7 +21708,7 @@
           <t>B7 | 200呎 (开放式)
 $380万
 $19,007/呎
-(25年-04月)</t>
+(25年-04月-08日)</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
@@ -21716,7 +21716,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,502/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="P15" s="20" t="inlineStr">
@@ -21724,7 +21724,7 @@
           <t>B9 | 261呎 (1房)
 $496万
 $19,003/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -21739,7 +21739,7 @@
           <t>A1 | 349呎 (2房)
 $661万
 $18,930/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -21747,7 +21747,7 @@
           <t>A2 | 342呎 (2房)
 $628万
 $18,376/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
@@ -21755,7 +21755,7 @@
           <t>A3 | 263呎 (1房)
 $493万
 $18,732/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -21763,7 +21763,7 @@
           <t>A5 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -21771,7 +21771,7 @@
           <t>A6 | 200呎 (开放式)
 $381万
 $19,053/呎
-(25年-04月)</t>
+(25年-04月-07日)</t>
         </is>
       </c>
       <c r="G16" s="20" t="inlineStr">
@@ -21779,7 +21779,7 @@
           <t>A7 | 262呎 (1房)
 $469万
 $17,891/呎
-(25年-03月)</t>
+(25年-03月-13日)</t>
         </is>
       </c>
       <c r="H16" s="20" t="inlineStr">
@@ -21787,7 +21787,7 @@
           <t>A8 | 262呎 (1房)
 $502万
 $19,165/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="I16" s="20" t="inlineStr">
@@ -21795,7 +21795,7 @@
           <t>B1 | 351呎 (2房)
 $678万
 $19,323/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J16" s="20" t="inlineStr">
@@ -21803,7 +21803,7 @@
           <t>B2 | 342呎 (2房)
 $648万
 $18,940/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -21811,7 +21811,7 @@
           <t>B3 | 263呎 (1房)
 $501万
 $19,032/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L16" s="20" t="inlineStr">
@@ -21819,7 +21819,7 @@
           <t>B5 | 263呎 (1房)
 $490万
 $18,627/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="M16" s="20" t="inlineStr">
@@ -21827,7 +21827,7 @@
           <t>B6 | 258呎 (1房)
 $476万
 $18,439/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N16" s="20" t="inlineStr">
@@ -21835,7 +21835,7 @@
           <t>B7 | 200呎 (开放式)
 $381万
 $19,058/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
@@ -21843,7 +21843,7 @@
           <t>B8 | 262呎 (1房)
 $491万
 $18,728/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P16" s="20" t="inlineStr">
@@ -21851,7 +21851,7 @@
           <t>B9 | 261呎 (1房)
 $491万
 $18,830/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -21866,7 +21866,7 @@
           <t>A1 | 349呎 (2房)
 $651万
 $18,642/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -21874,7 +21874,7 @@
           <t>A2 | 342呎 (2房)
 $619万
 $18,099/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -21882,7 +21882,7 @@
           <t>A3 | 263呎 (1房)
 $475万
 $18,046/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E17" s="20" t="inlineStr">
@@ -21890,7 +21890,7 @@
           <t>A5 | 258呎 (1房)
 $479万
 $18,563/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="F17" s="20" t="inlineStr">
@@ -21898,7 +21898,7 @@
           <t>A6 | 200呎 (开放式)
 $376万
 $18,823/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="G17" s="20" t="inlineStr">
@@ -21906,7 +21906,7 @@
           <t>A7 | 262呎 (1房)
 $463万
 $17,676/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H17" s="20" t="inlineStr">
@@ -21914,7 +21914,7 @@
           <t>A8 | 262呎 (1房)
 $495万
 $18,881/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="I17" s="20" t="inlineStr">
@@ -21922,7 +21922,7 @@
           <t>B1 | 351呎 (2房)
 $670万
 $19,084/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="J17" s="20" t="inlineStr">
@@ -21930,7 +21930,7 @@
           <t>B2 | 342呎 (2房)
 $647万
 $18,915/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K17" s="20" t="inlineStr">
@@ -21938,7 +21938,7 @@
           <t>B3 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="L17" s="20" t="inlineStr">
@@ -21946,7 +21946,7 @@
           <t>B5 | 263呎 (1房)
 $482万
 $18,344/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="M17" s="20" t="inlineStr">
@@ -21954,7 +21954,7 @@
           <t>B6 | 258呎 (1房)
 $469万
 $18,168/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="N17" s="20" t="inlineStr">
@@ -21962,7 +21962,7 @@
           <t>B7 | 200呎 (开放式)
 $369万
 $18,428/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="O17" s="20" t="inlineStr">
@@ -21970,7 +21970,7 @@
           <t>B8 | 262呎 (1房)
 $485万
 $18,495/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P17" s="20" t="inlineStr">
@@ -21978,7 +21978,7 @@
           <t>B9 | 261呎 (1房)
 $485万
 $18,601/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -21993,7 +21993,7 @@
           <t>A1 | 349呎 (2房)
 $641万
 $18,358/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -22001,7 +22001,7 @@
           <t>A2 | 342呎 (2房)
 $609万
 $17,819/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -22009,7 +22009,7 @@
           <t>A3 | 263呎 (1房)
 $466万
 $17,704/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="E18" s="20" t="inlineStr">
@@ -22017,7 +22017,7 @@
           <t>A5 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F18" s="20" t="inlineStr">
@@ -22025,7 +22025,7 @@
           <t>A6 | 200呎 (开放式)
 $380万
 $18,997/呎
-(25年-03月)</t>
+(25年-03月-12日)</t>
         </is>
       </c>
       <c r="G18" s="20" t="inlineStr">
@@ -22033,7 +22033,7 @@
           <t>A7 | 262呎 (1房)
 $458万
 $17,462/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="H18" s="20" t="inlineStr">
@@ -22041,7 +22041,7 @@
           <t>A8 | 262呎 (1房)
 $486万
 $18,537/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="I18" s="20" t="inlineStr">
@@ -22049,7 +22049,7 @@
           <t>B1 | 351呎 (2房)
 $661万
 $18,846/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="J18" s="20" t="inlineStr">
@@ -22057,7 +22057,7 @@
           <t>B2 | 342呎 (2房)
 $639万
 $18,687/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K18" s="20" t="inlineStr">
@@ -22065,7 +22065,7 @@
           <t>B3 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L18" s="20" t="inlineStr">
@@ -22073,7 +22073,7 @@
           <t>B5 | 263呎 (1房)
 $473万
 $18,001/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="M18" s="20" t="inlineStr">
@@ -22081,7 +22081,7 @@
           <t>B6 | 258呎 (1房)
 $460万
 $17,843/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="N18" s="20" t="inlineStr">
@@ -22089,7 +22089,7 @@
           <t>B7 | 200呎 (开放式)
 $366万
 $18,280/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="O18" s="20" t="inlineStr">
@@ -22097,7 +22097,7 @@
           <t>B8 | 262呎 (1房)
 $468万
 $17,873/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="P18" s="20" t="inlineStr">
@@ -22105,7 +22105,7 @@
           <t>B9 | 261呎 (1房)
 $488万
 $18,710/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -22120,7 +22120,7 @@
           <t>A1 | 349呎 (2房)
 $629万
 $18,012/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -22128,7 +22128,7 @@
           <t>A2 | 342呎 (2房)
 $598万
 $17,485/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="D19" s="20" t="inlineStr">
@@ -22136,7 +22136,7 @@
           <t>A3 | 263呎 (1房)
 $457万
 $17,364/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -22144,7 +22144,7 @@
           <t>A5 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F19" s="20" t="inlineStr">
@@ -22152,7 +22152,7 @@
           <t>A6 | 200呎 (开放式)
 $364万
 $18,188/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="G19" s="20" t="inlineStr">
@@ -22160,7 +22160,7 @@
           <t>A7 | 262呎 (1房)
 $452万
 $17,248/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="H19" s="20" t="inlineStr">
@@ -22168,7 +22168,7 @@
           <t>A8 | 262呎 (1房)
 $482万
 $18,390/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="I19" s="20" t="inlineStr">
@@ -22176,7 +22176,7 @@
           <t>B1 | 351呎 (2房)
 $651万
 $18,544/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="J19" s="20" t="inlineStr">
@@ -22184,7 +22184,7 @@
           <t>B2 | 342呎 (2房)
 $616万
 $18,013/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -22192,7 +22192,7 @@
           <t>B3 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="L19" s="20" t="inlineStr">
@@ -22200,7 +22200,7 @@
           <t>B5 | 263呎 (1房)
 $464万
 $17,658/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="M19" s="20" t="inlineStr">
@@ -22208,7 +22208,7 @@
           <t>B6 | 258呎 (1房)
 $452万
 $17,516/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="N19" s="20" t="inlineStr">
@@ -22216,7 +22216,7 @@
           <t>B7 | 200呎 (开放式)
 $371万
 $18,536/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="O19" s="20" t="inlineStr">
@@ -22224,7 +22224,7 @@
           <t>B8 | 262呎 (1房)
 $462万
 $17,641/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="P19" s="20" t="inlineStr">
@@ -22232,7 +22232,7 @@
           <t>B9 | 261呎 (1房)
 $481万
 $18,418/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -22247,7 +22247,7 @@
           <t>A1 | 349呎 (2房)
 $637万
 $18,246/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -22255,7 +22255,7 @@
           <t>A2 | 342呎 (2房)
 $606万
 $17,714/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -22263,7 +22263,7 @@
           <t>A3 | 263呎 (1房)
 $453万
 $17,206/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="E20" s="20" t="inlineStr">
@@ -22271,7 +22271,7 @@
           <t>A5 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="F20" s="20" t="inlineStr">
@@ -22279,7 +22279,7 @@
           <t>A6 | 200呎 (开放式)
 $363万
 $18,133/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G20" s="20" t="inlineStr">
@@ -22287,7 +22287,7 @@
           <t>A7 | 262呎 (1房)
 $451万
 $17,223/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H20" s="20" t="inlineStr">
@@ -22295,7 +22295,7 @@
           <t>A8 | 262呎 (1房)
 $468万
 $17,848/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="I20" s="20" t="inlineStr">
@@ -22303,7 +22303,7 @@
           <t>B1 | 351呎 (2房)
 $652万
 $18,583/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="J20" s="20" t="inlineStr">
@@ -22311,7 +22311,7 @@
           <t>B2 | 342呎 (2房)
 $605万
 $17,679/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -22319,7 +22319,7 @@
           <t>B3 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="L20" s="20" t="inlineStr">
@@ -22327,7 +22327,7 @@
           <t>B5 | 263呎 (1房)
 $455万
 $17,316/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="M20" s="20" t="inlineStr">
@@ -22335,7 +22335,7 @@
           <t>B6 | 258呎 (1房)
 $444万
 $17,191/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N20" s="20" t="inlineStr">
@@ -22343,7 +22343,7 @@
           <t>B7 | 200呎 (开放式)
 $362万
 $18,082/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="O20" s="20" t="inlineStr">
@@ -22351,7 +22351,7 @@
           <t>B8 | 262呎 (1房)
 $456万
 $17,413/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="P20" s="20" t="inlineStr">
@@ -22359,7 +22359,7 @@
           <t>B9 | 261呎 (1房)
 $461万
 $17,681/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -22374,7 +22374,7 @@
           <t>A1 | 349呎 (2房)
 $605万
 $17,324/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -22382,7 +22382,7 @@
           <t>A2 | 342呎 (2房)
 $575万
 $16,821/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="D21" s="20" t="inlineStr">
@@ -22390,7 +22390,7 @@
           <t>A3 | 263呎 (1房)
 $450万
 $17,098/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="E21" s="20" t="inlineStr">
@@ -22398,7 +22398,7 @@
           <t>A5 | 258呎 (1房)
 $437万
 $16,920/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F21" s="20" t="inlineStr">
@@ -22406,7 +22406,7 @@
           <t>A6 | 200呎 (开放式)
 $358万
 $17,898/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G21" s="20" t="inlineStr">
@@ -22414,7 +22414,7 @@
           <t>A7 | 262呎 (1房)
 $441万
 $16,823/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H21" s="20" t="inlineStr">
@@ -22422,7 +22422,7 @@
           <t>A8 | 262呎 (1房)
 $459万
 $17,505/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="I21" s="20" t="inlineStr">
@@ -22430,7 +22430,7 @@
           <t>B1 | 351呎 (2房)
 $646万
 $18,410/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="J21" s="20" t="inlineStr">
@@ -22438,7 +22438,7 @@
           <t>B2 | 342呎 (2房)
 $593万
 $17,345/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="K21" s="20" t="inlineStr">
@@ -22446,7 +22446,7 @@
           <t>B3 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L21" s="20" t="inlineStr">
@@ -22454,7 +22454,7 @@
           <t>B5 | 263呎 (1房)
 $446万
 $16,976/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="M21" s="20" t="inlineStr">
@@ -22462,7 +22462,7 @@
           <t>B6 | 258呎 (1房)
 $445万
 $17,233/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="N21" s="20" t="inlineStr">
@@ -22470,7 +22470,7 @@
           <t>B7 | 200呎 (开放式)
 $357万
 $17,848/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="O21" s="20" t="inlineStr">
@@ -22478,7 +22478,7 @@
           <t>B8 | 262呎 (1房)
 $450万
 $17,185/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="P21" s="20" t="inlineStr">
@@ -22486,7 +22486,7 @@
           <t>B9 | 261呎 (1房)
 $452万
 $17,335/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
     </row>
@@ -22501,7 +22501,7 @@
           <t>A1 | 349呎 (2房)
 $595万
 $17,040/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -22509,7 +22509,7 @@
           <t>A2 | 342呎 (2房)
 $566万
 $16,541/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -22517,7 +22517,7 @@
           <t>A3 | 263呎 (1房)
 $433万
 $16,451/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E22" s="20" t="inlineStr">
@@ -22525,7 +22525,7 @@
           <t>A5 | 258呎 (1房)
 $430万
 $16,649/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -22533,7 +22533,7 @@
           <t>A6 | 200呎 (开放式)
 $353万
 $17,668/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="G22" s="20" t="inlineStr">
@@ -22541,7 +22541,7 @@
           <t>A7 | 262呎 (1房)
 $443万
 $16,916/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H22" s="20" t="inlineStr">
@@ -22549,7 +22549,7 @@
           <t>A8 | 262呎 (1房)
 $461万
 $17,594/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="I22" s="20" t="inlineStr">
@@ -22557,7 +22557,7 @@
           <t>B1 | 351呎 (2房)
 $615万
 $17,527/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J22" s="20" t="inlineStr">
@@ -22565,7 +22565,7 @@
           <t>B2 | 342呎 (2房)
 $584万
 $17,068/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -22573,7 +22573,7 @@
           <t>B3 | 263呎 (1房)
 $448万
 $17,052/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L22" s="20" t="inlineStr">
@@ -22581,7 +22581,7 @@
           <t>B5 | 263呎 (1房)
 $439万
 $16,689/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="M22" s="20" t="inlineStr">
@@ -22589,7 +22589,7 @@
           <t>B6 | 258呎 (1房)
 $433万
 $16,776/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="N22" s="20" t="inlineStr">
@@ -22597,7 +22597,7 @@
           <t>B7 | 200呎 (开放式)
 $433万
 $21,641/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="O22" s="20" t="inlineStr">
@@ -22605,7 +22605,7 @@
           <t>B8 | 262呎 (1房)
 $454万
 $17,325/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="P22" s="20" t="inlineStr">
@@ -22613,7 +22613,7 @@
           <t>B9 | 261呎 (1房)
 $445万
 $17,046/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -22628,7 +22628,7 @@
           <t>A1 | 349呎 (2房)
 $597万
 $17,117/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -22636,7 +22636,7 @@
           <t>A2 | 342呎 (2房)
 $554万
 $16,208/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -22644,7 +22644,7 @@
           <t>A3 | 263呎 (1房)
 $432万
 $16,430/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E23" s="20" t="inlineStr">
@@ -22652,7 +22652,7 @@
           <t>A5 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -22660,7 +22660,7 @@
           <t>A6 | 200呎 (开放式)
 $348万
 $17,383/呎
-(25年-03月)</t>
+(25年-03月-31日)</t>
         </is>
       </c>
       <c r="G23" s="20" t="inlineStr">
@@ -22668,7 +22668,7 @@
           <t>A7 | 262呎 (1房)
 $435万
 $16,586/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="H23" s="20" t="inlineStr">
@@ -22676,7 +22676,7 @@
           <t>A8 | 262呎 (1房)
 $444万
 $16,932/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="I23" s="20" t="inlineStr">
@@ -22684,7 +22684,7 @@
           <t>B1 | 351呎 (2房)
 $605万
 $17,228/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="J23" s="20" t="inlineStr">
@@ -22692,7 +22692,7 @@
           <t>B2 | 342呎 (2房)
 $574万
 $16,791/呎
-(25年-02月)</t>
+(25年-02月-28日)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -22700,7 +22700,7 @@
           <t>B3 | 263呎 (1房)
 $441万
 $16,763/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="L23" s="20" t="inlineStr">
@@ -22708,7 +22708,7 @@
           <t>B5 | 263呎 (1房)
 $431万
 $16,406/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="M23" s="20" t="inlineStr">
@@ -22716,7 +22716,7 @@
           <t>B6 | 258呎 (1房)
 $421万
 $16,324/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="N23" s="20" t="inlineStr">
@@ -22724,7 +22724,7 @@
           <t>B7 | 200呎 (开放式)
 $346万
 $17,324/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="O23" s="20" t="inlineStr">
@@ -22732,7 +22732,7 @@
           <t>B8 | 262呎 (1房)
 $437万
 $16,669/呎
-(25年-03月)</t>
+(25年-03月-18日)</t>
         </is>
       </c>
       <c r="P23" s="20" t="inlineStr">
@@ -22740,7 +22740,7 @@
           <t>B9 | 261呎 (1房)
 $437万
 $16,761/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -22755,7 +22755,7 @@
           <t>A1 | 349呎 (2房)
 $577万
 $16,523/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -22763,7 +22763,7 @@
           <t>A2 | 342呎 (2房)
 $541万
 $15,820/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -22771,7 +22771,7 @@
           <t>A3 | 263呎 (1房)
 $410万
 $15,591/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -22779,7 +22779,7 @@
           <t>A5 | 258呎 (1房)
 $410万
 $15,890/呎
-(25年-03月)</t>
+(25年-03月-19日)</t>
         </is>
       </c>
       <c r="F24" s="20" t="inlineStr">
@@ -22787,7 +22787,7 @@
           <t>A6 | 200呎 (开放式)
 $346万
 $17,296/呎
-(25年-03月)</t>
+(25年-03月-25日)</t>
         </is>
       </c>
       <c r="G24" s="20" t="inlineStr">
@@ -22795,7 +22795,7 @@
           <t>A7 | 262呎 (1房)
 $417万
 $15,914/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="H24" s="20" t="inlineStr">
@@ -22803,7 +22803,7 @@
           <t>A8 | 262呎 (1房)
 $438万
 $16,704/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="I24" s="20" t="inlineStr">
@@ -22811,7 +22811,7 @@
           <t>B1 | 351呎 (2房)
 $601万
 $17,113/呎
-(25年-03月)</t>
+(25年-03月-24日)</t>
         </is>
       </c>
       <c r="J24" s="20" t="inlineStr">
@@ -22819,7 +22819,7 @@
           <t>B2 | 342呎 (2房)
 $565万
 $16,514/呎
-(25年-03月)</t>
+(25年-03月-20日)</t>
         </is>
       </c>
       <c r="K24" s="20" t="inlineStr">
@@ -22827,7 +22827,7 @@
           <t>B3 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月)</t>
+(25年-03月-17日)</t>
         </is>
       </c>
       <c r="L24" s="20" t="inlineStr">
@@ -22835,7 +22835,7 @@
           <t>B5 | 263呎 (1房)
 $425万
 $16,175/呎
-(25年-03月)</t>
+(25年-03月-16日)</t>
         </is>
       </c>
       <c r="M24" s="20" t="inlineStr">
@@ -22843,7 +22843,7 @@
           <t>B6 | 258呎 (1房)
 $429万
 $16,632/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="N24" s="20" t="inlineStr">
@@ -22851,7 +22851,7 @@
           <t>B7 | 200呎 (开放式)
 $337万
 $16,872/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
       <c r="O24" s="20" t="inlineStr">
@@ -22859,7 +22859,7 @@
           <t>B8 | 262呎 (1房)
 $446万
 $17,041/呎
-(25年-04月)</t>
+(25年-04月-01日)</t>
         </is>
       </c>
       <c r="P24" s="20" t="inlineStr">
@@ -22867,7 +22867,7 @@
           <t>B9 | 261呎 (1房)
 $431万
 $16,532/呎
-(25年-03月)</t>
+(25年-03月-23日)</t>
         </is>
       </c>
     </row>
@@ -22882,7 +22882,7 @@
           <t>A1 | 311呎 (2房)
 $723万
 $23,241/呎
-(25年-04月)</t>
+(25年-04月-13日)</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -22890,7 +22890,7 @@
           <t>A2 | 304呎 (2房)
 $656万
 $21,579/呎
-(25年-03月)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D25" s="20" t="inlineStr">
@@ -22898,7 +22898,7 @@
           <t>A3 | 225呎 (1房)
 $470万
 $20,881/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -22906,7 +22906,7 @@
           <t>A5 | 221呎 (1房)
 $465万
 $21,040/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -22914,7 +22914,7 @@
           <t>A6 | 178呎 (开放式)
 $452万
 $25,393/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="G25" s="20" t="inlineStr">
@@ -22922,7 +22922,7 @@
           <t>A7 | 224呎 (1房)
 $585万
 $26,116/呎
-(26年-04月)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="H25" s="20" t="inlineStr">
@@ -22930,7 +22930,7 @@
           <t>A8 | 224呎 (1房)
 $633万
 $28,259/呎
-(26年-04月)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="I25" s="20" t="inlineStr">
@@ -22938,7 +22938,7 @@
           <t>B1 | 313呎 (2房)
 $725万
 $23,163/呎
-(25年-07月)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="J25" s="20" t="inlineStr">
@@ -22946,7 +22946,7 @@
           <t>B2 | 304呎 (2房)
 $660万
 $21,711/呎
-(25年-04月)</t>
+(25年-04月-02日)</t>
         </is>
       </c>
       <c r="K25" s="20" t="inlineStr">
@@ -22954,7 +22954,7 @@
           <t>B3 | 225呎 (1房)
 $475万
 $21,111/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="L25" s="20" t="inlineStr">
@@ -22962,7 +22962,7 @@
           <t>B5 | 225呎 (1房)
 $470万
 $20,889/呎
-(25年-04月)</t>
+(25年-04月-10日)</t>
         </is>
       </c>
       <c r="M25" s="20" t="inlineStr">
@@ -22970,7 +22970,7 @@
           <t>B6 | 220呎 (1房)
 $465万
 $21,136/呎
-(25年-04月)</t>
+(25年-04月-22日)</t>
         </is>
       </c>
       <c r="N25" s="20" t="inlineStr">
@@ -22978,7 +22978,7 @@
           <t>B7 | 178呎 (开放式)
 $458万
 $25,730/呎
-(26年-04月)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="O25" s="20" t="inlineStr">
@@ -22986,7 +22986,7 @@
           <t>B8 | 224呎 (1房)
 $520万
 $23,214/呎
-(25年-05月)</t>
+(25年-05月-07日)</t>
         </is>
       </c>
       <c r="P25" s="20" t="inlineStr">
@@ -22994,7 +22994,7 @@
           <t>B9 | 224呎 (1房)
 $618万
 $27,593/呎
-(26年-04月)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>

--- a/files/九龙-马头角-南首.xlsx
+++ b/files/九龙-马头角-南首.xlsx
@@ -275,10 +275,10 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1210,23 +1210,23 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>6300000</v>
+        <v>6174000</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>24046</v>
+        <v>23565</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K10" s="5" t="n">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>90天現金付款計劃</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1277,7 +1277,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -20249,7 +20249,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -20388,18 +20388,18 @@
           <t>A6 | 200呎 (开放式)
 $464万
 $23,182/呎
-(26年-06月-25日)</t>
-        </is>
-      </c>
-      <c r="G5" s="21" t="inlineStr">
+(26年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
         <is>
           <t>A7 | 262呎 (1房)
-$630万
-$24,046/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr"/>
+$617万
+$23,565/呎
+(26年-07月-19日)</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr"/>
       <c r="I5" s="20" t="inlineStr">
         <is>
           <t>B1 | 358呎 (2房)
@@ -20416,7 +20416,7 @@
 (26年-05月-28日)</t>
         </is>
       </c>
-      <c r="K5" s="21" t="inlineStr">
+      <c r="K5" s="22" t="inlineStr">
         <is>
           <t>B3 | 263呎 (1房)
 $681万
@@ -20448,7 +20448,7 @@
 (26年-07月-19日)</t>
         </is>
       </c>
-      <c r="O5" s="21" t="inlineStr">
+      <c r="O5" s="22" t="inlineStr">
         <is>
           <t>B8 | 262呎 (1房)
 $652万
@@ -20456,7 +20456,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="P5" s="22" t="inlineStr"/>
+      <c r="P5" s="21" t="inlineStr"/>
     </row>
     <row r="6" ht="58" customHeight="1">
       <c r="A6" s="19" t="inlineStr">
@@ -20576,7 +20576,7 @@
 (暂停销售)</t>
         </is>
       </c>
-      <c r="P6" s="21" t="inlineStr">
+      <c r="P6" s="22" t="inlineStr">
         <is>
           <t>B9 | 261呎 (1房)
 $676万
@@ -20636,10 +20636,10 @@
           <t>A7 | 262呎 (1房)
 $603万
 $23,030/呎
-(26年-07月-05日)</t>
-        </is>
-      </c>
-      <c r="H7" s="21" t="inlineStr">
+(26年-07月-21日)</t>
+        </is>
+      </c>
+      <c r="H7" s="22" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
 $680万
@@ -20695,7 +20695,7 @@
 (25年-05月-07日)</t>
         </is>
       </c>
-      <c r="O7" s="21" t="inlineStr">
+      <c r="O7" s="22" t="inlineStr">
         <is>
           <t>B8 | 262呎 (1房)
 $634万
@@ -20766,7 +20766,7 @@
 (25年-03月-23日)</t>
         </is>
       </c>
-      <c r="H8" s="21" t="inlineStr">
+      <c r="H8" s="22" t="inlineStr">
         <is>
           <t>A8 | 262呎 (1房)
 $673万
